--- a/Experiments_Summary.xlsx
+++ b/Experiments_Summary.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="23">
   <si>
     <t>Model_Name</t>
   </si>
@@ -46,10 +46,43 @@
     <t>Test_Balanced_Accuracy</t>
   </si>
   <si>
+    <t>Learning_Rate_Head</t>
+  </si>
+  <si>
+    <t>Total_Folds</t>
+  </si>
+  <si>
+    <t>Avg_Test_AUROC</t>
+  </si>
+  <si>
+    <t>Avg_Test_F1_Score</t>
+  </si>
+  <si>
+    <t>Avg_Test_Balanced_Accuracy</t>
+  </si>
+  <si>
+    <t>Avg_Test_CIndex</t>
+  </si>
+  <si>
     <t>whole_slice</t>
   </si>
   <si>
     <t>/nas-ctm01/datasets/public/medical_datasets/lung_ct_datasets/nlst/preprocessed_data/protocol_5/2d/ws</t>
+  </si>
+  <si>
+    <t>lung</t>
+  </si>
+  <si>
+    <t>/nas-ctm01/datasets/public/medical_datasets/lung_ct_datasets/nlst/preprocessed_data/protocol_5/2d/lung</t>
+  </si>
+  <si>
+    <t>/nas-ctm01/datasets/public/medical_datasets/lung_ct_datasets/nlst/preprocessed_data/protocol_5/2d/masked</t>
+  </si>
+  <si>
+    <t>masked</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -120,7 +153,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="16">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -140,11 +173,29 @@
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="2" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="4" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -451,22 +502,28 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:P17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="4" max="4" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="5" max="5" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="6" max="6" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="7" max="7" style="9" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="8" max="8" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="9" max="9" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="10" max="10" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="11" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="4" max="4" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="5" max="5" style="13" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="6" max="6" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="7" max="7" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="8" max="8" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="9" max="9" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="10" max="10" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="11" max="11" style="14" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="12" max="12" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="13" max="13" style="12" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="14" max="14" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="15" max="15" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="16" max="16" style="15" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="20.25">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="21">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -497,13 +554,31 @@
       <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
       <c r="A2" s="4" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="C2" s="5">
         <v>0.0001</v>
@@ -528,6 +603,562 @@
       </c>
       <c r="J2" s="5">
         <v>0.629539966583252</v>
+      </c>
+      <c r="K2" s="7"/>
+      <c r="L2" s="8"/>
+      <c r="M2" s="9"/>
+      <c r="N2" s="8"/>
+      <c r="O2" s="8"/>
+      <c r="P2" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+      <c r="A3" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="5">
+        <v>0.00001</v>
+      </c>
+      <c r="D3" s="6">
+        <v>200</v>
+      </c>
+      <c r="E3" s="6">
+        <v>32</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G3" s="6">
+        <v>22</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0.6900726556777954</v>
+      </c>
+      <c r="I3" s="5">
+        <v>0.5128205418586731</v>
+      </c>
+      <c r="J3" s="5">
+        <v>0.6702986359596252</v>
+      </c>
+      <c r="K3" s="7"/>
+      <c r="L3" s="8"/>
+      <c r="M3" s="9"/>
+      <c r="N3" s="8"/>
+      <c r="O3" s="8"/>
+      <c r="P3" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+      <c r="A4" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="5">
+        <v>0.00001</v>
+      </c>
+      <c r="D4" s="6">
+        <v>200</v>
+      </c>
+      <c r="E4" s="6">
+        <v>32</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G4" s="6">
+        <v>22</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0.698143720626831</v>
+      </c>
+      <c r="I4" s="5">
+        <v>0.4347825944423676</v>
+      </c>
+      <c r="J4" s="5">
+        <v>0.6109765768051147</v>
+      </c>
+      <c r="K4" s="7"/>
+      <c r="L4" s="8"/>
+      <c r="M4" s="9"/>
+      <c r="N4" s="8"/>
+      <c r="O4" s="8"/>
+      <c r="P4" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+      <c r="A5" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="5">
+        <v>0.0001</v>
+      </c>
+      <c r="D5" s="6">
+        <v>100</v>
+      </c>
+      <c r="E5" s="6">
+        <v>32</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G5" s="6">
+        <v>22</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0.646489143371582</v>
+      </c>
+      <c r="I5" s="5">
+        <v>0.3888888955116272</v>
+      </c>
+      <c r="J5" s="5">
+        <v>0.598870038986206</v>
+      </c>
+      <c r="K5" s="7"/>
+      <c r="L5" s="8"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="8"/>
+      <c r="O5" s="8"/>
+      <c r="P5" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+      <c r="A6" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="5">
+        <v>0.00001</v>
+      </c>
+      <c r="D6" s="6">
+        <v>200</v>
+      </c>
+      <c r="E6" s="6">
+        <v>32</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G6" s="6">
+        <v>22</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0.6311541795730591</v>
+      </c>
+      <c r="I6" s="5">
+        <v>0.3902438879013062</v>
+      </c>
+      <c r="J6" s="5">
+        <v>0.5887812972068787</v>
+      </c>
+      <c r="K6" s="7"/>
+      <c r="L6" s="8"/>
+      <c r="M6" s="9"/>
+      <c r="N6" s="8"/>
+      <c r="O6" s="8"/>
+      <c r="P6" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+      <c r="A7" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7" s="5">
+        <v>0.00001</v>
+      </c>
+      <c r="D7" s="6">
+        <v>200</v>
+      </c>
+      <c r="E7" s="6">
+        <v>32</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="6">
+        <v>22</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0.6311541795730591</v>
+      </c>
+      <c r="I7" s="5">
+        <v>0.3902438879013062</v>
+      </c>
+      <c r="J7" s="5">
+        <v>0.5887812972068787</v>
+      </c>
+      <c r="K7" s="7"/>
+      <c r="L7" s="8"/>
+      <c r="M7" s="9"/>
+      <c r="N7" s="8"/>
+      <c r="O7" s="8"/>
+      <c r="P7" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+      <c r="A8" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="9"/>
+      <c r="D8" s="6">
+        <v>2</v>
+      </c>
+      <c r="E8" s="6">
+        <v>32</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G8" s="6">
+        <v>22</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0.5423728823661804</v>
+      </c>
+      <c r="I8" s="6">
+        <v>0</v>
+      </c>
+      <c r="J8" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="K8" s="5">
+        <v>0.0001</v>
+      </c>
+      <c r="L8" s="8"/>
+      <c r="M8" s="9"/>
+      <c r="N8" s="8"/>
+      <c r="O8" s="8"/>
+      <c r="P8" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+      <c r="A9" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C9" s="9"/>
+      <c r="D9" s="6">
+        <v>200</v>
+      </c>
+      <c r="E9" s="6">
+        <v>32</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G9" s="6">
+        <v>22</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0.6989508271217346</v>
+      </c>
+      <c r="I9" s="5">
+        <v>0.4255319237709045</v>
+      </c>
+      <c r="J9" s="5">
+        <v>0.6025020480155945</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0.00001</v>
+      </c>
+      <c r="L9" s="8"/>
+      <c r="M9" s="9"/>
+      <c r="N9" s="8"/>
+      <c r="O9" s="8"/>
+      <c r="P9" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+      <c r="A10" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.00001</v>
+      </c>
+      <c r="D10" s="6">
+        <v>200</v>
+      </c>
+      <c r="E10" s="6">
+        <v>32</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G10" s="6">
+        <v>22</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0.6311541795730591</v>
+      </c>
+      <c r="I10" s="5">
+        <v>0.3902438879013062</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0.5887812972068787</v>
+      </c>
+      <c r="K10" s="7"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="9"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+      <c r="A11" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C11" s="5">
+        <v>0.0001</v>
+      </c>
+      <c r="D11" s="6">
+        <v>2</v>
+      </c>
+      <c r="E11" s="6">
+        <v>32</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G11" s="6">
+        <v>22</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.5900000333786011</v>
+      </c>
+      <c r="I11" s="6">
+        <v>0</v>
+      </c>
+      <c r="J11" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="K11" s="7"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="9"/>
+      <c r="N11" s="8"/>
+      <c r="O11" s="8"/>
+      <c r="P11" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+      <c r="A12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="5">
+        <v>0.00001</v>
+      </c>
+      <c r="D12" s="6">
+        <v>100</v>
+      </c>
+      <c r="E12" s="6">
+        <v>32</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="6">
+        <v>22</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0.7233333587646484</v>
+      </c>
+      <c r="I12" s="5">
+        <v>0.5106382966041565</v>
+      </c>
+      <c r="J12" s="5">
+        <v>0.675000011920929</v>
+      </c>
+      <c r="K12" s="7"/>
+      <c r="L12" s="8"/>
+      <c r="M12" s="9"/>
+      <c r="N12" s="8"/>
+      <c r="O12" s="8"/>
+      <c r="P12" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+      <c r="A13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="5">
+        <v>0.0001</v>
+      </c>
+      <c r="D13" s="6">
+        <v>100</v>
+      </c>
+      <c r="E13" s="6">
+        <v>32</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0.2</v>
+      </c>
+      <c r="G13" s="6">
+        <v>22</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.7274999618530273</v>
+      </c>
+      <c r="I13" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="J13" s="5">
+        <v>0.6666666269302368</v>
+      </c>
+      <c r="K13" s="7"/>
+      <c r="L13" s="8"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="8"/>
+      <c r="O13" s="8"/>
+      <c r="P13" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+      <c r="A14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" s="4"/>
+      <c r="C14" s="5">
+        <v>0.0001</v>
+      </c>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="6">
+        <v>22</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="6">
+        <v>3</v>
+      </c>
+      <c r="M14" s="5">
+        <v>0.674999992052714</v>
+      </c>
+      <c r="N14" s="5">
+        <v>0.4004127979278564</v>
+      </c>
+      <c r="O14" s="5">
+        <v>0.6055555542310079</v>
+      </c>
+      <c r="P14" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+      <c r="A15" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="4"/>
+      <c r="C15" s="5">
+        <v>0.0001</v>
+      </c>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="6">
+        <v>22</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="6">
+        <v>3</v>
+      </c>
+      <c r="M15" s="5">
+        <v>0.6874999602635702</v>
+      </c>
+      <c r="N15" s="5">
+        <v>0.4707868993282318</v>
+      </c>
+      <c r="O15" s="5">
+        <v>0.6444444259007772</v>
+      </c>
+      <c r="P15" s="8"/>
+    </row>
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+      <c r="A16" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B16" s="4"/>
+      <c r="C16" s="5">
+        <v>0.00001</v>
+      </c>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="6">
+        <v>22</v>
+      </c>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="6">
+        <v>3</v>
+      </c>
+      <c r="M16" s="5">
+        <v>0.5086419582366943</v>
+      </c>
+      <c r="N16" s="6">
+        <v>0</v>
+      </c>
+      <c r="O16" s="6">
+        <v>0</v>
+      </c>
+      <c r="P16" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+      <c r="A17" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="4"/>
+      <c r="C17" s="5">
+        <v>0.0001</v>
+      </c>
+      <c r="D17" s="10"/>
+      <c r="E17" s="10"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="6">
+        <v>22</v>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="6">
+        <v>3</v>
+      </c>
+      <c r="M17" s="5">
+        <v>0.6929012537002563</v>
+      </c>
+      <c r="N17" s="6">
+        <v>0</v>
+      </c>
+      <c r="O17" s="6">
+        <v>0</v>
+      </c>
+      <c r="P17" s="6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments_Summary.xlsx
+++ b/Experiments_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I12"/>
+  <dimension ref="A1:R15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -474,11 +474,56 @@
           <t>Avg_Test_f1_score</t>
         </is>
       </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Std_Test_AUROC</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Std_Test_CIndex</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Std_Test_IBS</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Std_Test_bal_acc</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Std_Test_f1_score</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Avg_Test_recall</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Std_Test_recall</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Avg_Test_precision</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Std_Test_precision</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>example</t>
+          <t>lung_freezed</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -491,19 +536,52 @@
         <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5910493731498718</v>
+        <v>0.6703703999519348</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5979277094205221</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
+        <v>0.6633813579877218</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.1136300886670748</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0.5944444537162781</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.37977334856987</v>
+      </c>
+      <c r="J2" t="n">
+        <v>0.0388962342977056</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.03971434143693391</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.004466095670342372</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.05457464741403106</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.1022987586187475</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0.5944444537162781</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.05457464741403106</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.5923594633738199</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.0485919095517561</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>example</t>
+          <t>whole_slice_freezed</t>
         </is>
       </c>
       <c r="B3" t="n">
@@ -516,19 +594,52 @@
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5910493731498718</v>
+        <v>0.6743827064832052</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5979277094205221</v>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
+        <v>0.6664139628410339</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.109479787449042</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.6583333412806193</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.4878048698107402</v>
+      </c>
+      <c r="J3" t="n">
+        <v>0.02845203283612698</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.04594582333640614</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.005335784581764257</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.05443310215072308</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.07965820004984106</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.6583333412806193</v>
+      </c>
+      <c r="P3" t="n">
+        <v>0.05443310215072308</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.6533494790395101</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.05271970781422992</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>example</t>
+          <t>masked_freezed</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -541,23 +652,56 @@
         <v>3</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6898147861162821</v>
+        <v>0.7253086566925049</v>
       </c>
       <c r="F4" t="n">
-        <v>0.673490027586619</v>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
+        <v>0.694465498129527</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.1091552252570788</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.6777777671813965</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.5124710996945699</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.02263422443927829</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.04153020843119772</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.005712052724668275</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.05786851861604943</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0.08027937131840475</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0.6777777671813965</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.05786851861604943</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.6594308416048685</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.04799526486346187</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>lung_freezed_e-5</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0001</v>
+        <v>1e-05</v>
       </c>
       <c r="C5" t="n">
         <v>22</v>
@@ -566,21 +710,52 @@
         <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6898147861162821</v>
+        <v>0.5898148417472839</v>
       </c>
       <c r="F5" t="n">
-        <v>0.673490027586619</v>
+        <v>0.6087945501009623</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1165</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
+        <v>0.121993454794089</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0.6027777791023254</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.4270103871822357</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.03175268289771101</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.03308754008741838</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.004789092090307014</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.03215509930389345</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0.04437305274614343</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.6027777791023254</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0.03215509930389345</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0.5865701039632162</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.02966688568351711</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>lower_lr</t>
+          <t>masked_freezed_e-5</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -593,21 +768,52 @@
         <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>0.730246921380361</v>
+        <v>0.6197530925273895</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7210007707277933</v>
+        <v>0.6044983466466268</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1054</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
+        <v>0.1219296182195346</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.5722222328186035</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.4273877044518788</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.1128701534638665</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.09265231432591128</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.00900470649588451</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.05706288663246662</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.03240528570740345</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.5722222328186035</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0.05706288663246662</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.5604207217693329</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.05241903603056015</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>lung_unfreezed</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -620,29 +826,56 @@
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>0.539506177107493</v>
+        <v>0.7583333253860474</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5789739688237509</v>
+        <v>0.6909274657567342</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1457151224215825</v>
+        <v>0.1151315396030744</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5</v>
+        <v>0.6861111124356588</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1333333353201548</v>
+        <v>0.5204678376515707</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.03704476253122629</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.0332223833452473</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.006930309941077968</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.02749861296829705</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.02894589359930188</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.6861111124356588</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0.02749861296829705</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.6457585493723551</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.01718248205627023</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>lower_lr</t>
+          <t>whole_slice_unfreezed</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="C8" t="n">
         <v>22</v>
@@ -651,29 +884,56 @@
         <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6376543243726095</v>
+        <v>0.799999992052714</v>
       </c>
       <c r="F8" t="n">
-        <v>0.6803133686383566</v>
+        <v>0.7500632007916769</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1230962847669919</v>
+        <v>0.1010366926590602</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5333333412806193</v>
+        <v>0.7333333293596903</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1494949559370677</v>
+        <v>0.5988456209500631</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.03871948500772019</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.04240371869329652</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.006485287615350145</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.04461769750363983</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.05854390040075846</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.7333333293596903</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.04461769750363983</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.7456492582956949</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.05651580495753514</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>baseline</t>
+          <t>whole_slice_freezed_e-5</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0001</v>
+        <v>1e-05</v>
       </c>
       <c r="C9" t="n">
         <v>22</v>
@@ -682,25 +942,52 @@
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6898147861162821</v>
+        <v>0.625308632850647</v>
       </c>
       <c r="F9" t="n">
-        <v>0.673490027586619</v>
+        <v>0.6176396409670512</v>
       </c>
       <c r="G9" t="n">
-        <v>0.116528108716011</v>
+        <v>0.1209806948900223</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5888889034589132</v>
+        <v>0.5888888835906982</v>
       </c>
       <c r="I9" t="n">
-        <v>0.352073073387146</v>
+        <v>0.4310664733250936</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.06229372302997798</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.05683710410307316</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.009793734450322491</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.05457466865061458</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.04268537927317011</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.5888888835906982</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.05457466865061458</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.5713350375493368</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.04353825330072314</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>threshold_0.7</t>
+          <t>masked_unfreezed</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -713,29 +1000,56 @@
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7108024557431539</v>
+        <v>0.7756173213322958</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6944655179977417</v>
+        <v>0.7306039730707804</v>
       </c>
       <c r="G10" t="n">
-        <v>0.1092078685760498</v>
+        <v>0.1057684967915217</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6472222010294596</v>
+        <v>0.7138888835906982</v>
       </c>
       <c r="I10" t="n">
-        <v>0.4711474974950154</v>
+        <v>0.5535970429579417</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.0224312857623785</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.02771369582046985</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.003647473201317811</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.04631482175769951</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.05711973121075761</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.7138888835906982</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.04631482175769951</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.6844896872838339</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.01669251672497994</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>threshold_0.6</t>
+          <t>lung_unfreezed_e-5</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0001</v>
+        <v>1e-05</v>
       </c>
       <c r="C11" t="n">
         <v>22</v>
@@ -744,29 +1058,56 @@
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0.7108024557431539</v>
+        <v>0.7469135920206705</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6944655179977417</v>
+        <v>0.6980035305023193</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1092078685760498</v>
+        <v>0.1136565705140432</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6333333253860474</v>
+        <v>0.6527777512868246</v>
       </c>
       <c r="I11" t="n">
-        <v>0.443181832631429</v>
+        <v>0.4817112286885579</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.02830098011018187</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.01953940983251012</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.004275024277005054</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.02187222323547982</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.02785514937305008</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.6527777512868246</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.02187222323547982</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.6258766651153564</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.01498629596755798</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>threshold_0.4</t>
+          <t>whole_slice_unfreezed_e-5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0001</v>
+        <v>1e-05</v>
       </c>
       <c r="C12" t="n">
         <v>22</v>
@@ -775,19 +1116,212 @@
         <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>0.7108024557431539</v>
+        <v>0.7941357890764872</v>
       </c>
       <c r="F12" t="n">
-        <v>0.6944655179977417</v>
+        <v>0.7553702195485433</v>
       </c>
       <c r="G12" t="n">
-        <v>0.1092078685760498</v>
+        <v>0.1094236175219218</v>
       </c>
       <c r="H12" t="n">
-        <v>0.5222222010294596</v>
+        <v>0.6611110965410868</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1739037930965424</v>
+        <v>0.4899878005186717</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.01288185881683751</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.0139841615724536</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.01390135253101567</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.01416394906792663</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.02380734027640757</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.6611110965410868</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0.01416394906792663</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.6740721066792806</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.005932908313592932</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>masked_unfreezed_e-5</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="C13" t="n">
+        <v>22</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.7626543045043945</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.7033105889956156</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.1232371727625529</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0.6055555740992228</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.4108108182748159</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.0240185783748791</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.02235651667108048</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.00678333619978266</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.01416392958552454</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.01528879739522582</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.6055555740992228</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0.01416392958552454</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.6066853602727255</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.02496931730419817</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>whole_slice_unfreezed_e-5</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="C14" t="n">
+        <v>22</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.6370370388031006</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.6285064419110616</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.1376430044571559</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0.5027777949968973</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1797628924250603</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.02800322537623997</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.02109238749112341</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.008168743413863463</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.03356401253736564</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1106548810307757</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.5027777949968973</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0.03356401253736564</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4874837497870128</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.04216014649383777</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Binary_ws</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C15" t="n">
+        <v>22</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6724999944368998</v>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="n">
+        <v>0.6361111203829447</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.461451252301534</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.04972610417041414</v>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>0.03215509072213786</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.03891383121269985</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.6361111203829447</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.03215509072213786</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.6214166482289633</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.03341367063597313</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments_Summary.xlsx
+++ b/Experiments_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R15"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1277,7 +1277,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Binary_ws</t>
+          <t>Binary_lung</t>
         </is>
       </c>
       <c r="B15" t="n">
@@ -1290,38 +1290,1486 @@
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6724999944368998</v>
-      </c>
-      <c r="F15" t="inlineStr"/>
+        <v>0.7180555462837219</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.3065453668435414</v>
+      </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.6361111203829447</v>
+        <v>0.5944444537162781</v>
       </c>
       <c r="I15" t="n">
-        <v>0.461451252301534</v>
+        <v>0.3705882330735524</v>
       </c>
       <c r="J15" t="n">
-        <v>0.04972610417041414</v>
-      </c>
-      <c r="K15" t="inlineStr"/>
+        <v>0.0177473625427014</v>
+      </c>
+      <c r="K15" t="n">
+        <v>0.008404500681152147</v>
+      </c>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="n">
-        <v>0.03215509072213786</v>
+        <v>0.04374447422688386</v>
       </c>
       <c r="N15" t="n">
-        <v>0.03891383121269985</v>
+        <v>0.08668573726387595</v>
       </c>
       <c r="O15" t="n">
+        <v>0.5944444537162781</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0.04374447422688386</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.611289362112681</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.04465261233339038</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Binary_ws</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C16" t="n">
+        <v>22</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6802777449289957</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.3292898635069529</v>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="n">
+        <v>0.6111111044883728</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.4248851239681244</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.0462597515408647</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0445713789914697</v>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>0.04530416812354012</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.0580141072311248</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.6111111044883728</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.04530416812354012</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.6057166258494059</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.046444056459004</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Binary_ws_unfrozen</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C17" t="n">
+        <v>22</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.6694444219271342</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.3532979488372803</v>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="n">
+        <v>0.6194444298744202</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.4214214285214742</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.0302790475087229</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0.020371539477665</v>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>0.03868995764163432</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.06460916600228836</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.6194444298744202</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.03868995764163432</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.6372597614924113</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.0426971189543995</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Binary_lung_unfrozen</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C18" t="n">
+        <v>22</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.761388878027598</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.285064438978831</v>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="n">
+        <v>0.6777777671813965</v>
+      </c>
+      <c r="I18" t="n">
+        <v>0.5158483982086182</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.01979444973510131</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0.01932911187972722</v>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>0.0171234074691646</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.02356130428270595</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.6777777671813965</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0.0171234074691646</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.6824351747830709</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.02547267761211013</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Binary_masked</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C19" t="n">
+        <v>22</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.7374999721844991</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.2901187737782796</v>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="n">
+        <v>0.6388888955116272</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.4489954610665639</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.008686954775978832</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0.00939480916770619</v>
+      </c>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>0.07647722305038354</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.1283333211564751</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.6388888955116272</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.07647722305038354</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.6467669606208801</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.07412415624564839</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Binary_masked_unfrozen</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C20" t="n">
+        <v>22</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.7530555327733358</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.2977002759774526</v>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="n">
+        <v>0.6250000397364298</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.4206773738066356</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.05390462990124372</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0.04140699839998828</v>
+      </c>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>0.05314202337176079</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.08833876738283358</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.6250000397364298</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.05314202337176079</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.6376960674921671</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.02982949637940507</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Binary_ws</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C21" t="n">
+        <v>22</v>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.6750000317891439</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5352539817492167</v>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="n">
+        <v>0.6444444457689921</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.472810963789622</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.04876738852446711</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0.04299898082445552</v>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>0.04101338115208705</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.05243174356704906</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.6444444457689921</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0.04101338115208705</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.6404328147570292</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.04775576276599745</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Binary_ws</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C22" t="n">
+        <v>22</v>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.6777777473131815</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5347485542297363</v>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.50533127784729</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.04998857642828167</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.04312062077190951</v>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>0.06905444741871394</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.09493238731669183</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.06905444741871394</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.6619555552800497</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.07178272167197755</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ws</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C23" t="n">
+        <v>22</v>
+      </c>
+      <c r="D23" t="n">
+        <v>3</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6750000317891439</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.5352539817492167</v>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="n">
+        <v>0.569444457689921</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.2883597960074742</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.04876738852446711</v>
+      </c>
+      <c r="K23" t="n">
+        <v>0.04299898082445552</v>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>0.02389535058159446</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.05511287742699388</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.569444457689921</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.02389535058159446</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.6483565370241801</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.04559983856047613</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ws</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C24" t="n">
+        <v>22</v>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.6750000317891439</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5352539817492167</v>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="n">
         <v>0.6361111203829447</v>
       </c>
-      <c r="P15" t="n">
-        <v>0.03215509072213786</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.6214166482289633</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.03341367063597313</v>
+      <c r="I24" t="n">
+        <v>0.4512180785338084</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.04876738852446711</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.04299898082445552</v>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>0.03491611882203919</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.05617007846464612</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.6361111203829447</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.03491611882203919</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.6701036890347799</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.05639690825394791</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ws</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C25" t="n">
+        <v>22</v>
+      </c>
+      <c r="D25" t="n">
+        <v>3</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.6040123303731283</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.4023249844710032</v>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="n">
+        <v>0.5861111283302307</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.3925263384977977</v>
+      </c>
+      <c r="J25" t="n">
+        <v>0.01680890165551272</v>
+      </c>
+      <c r="K25" t="n">
+        <v>0.0877760461480723</v>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>0.01571348308978993</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.02491096407036001</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.5861111283302307</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.01571348308978993</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.5779856642087301</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.01715543494942115</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ws</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C26" t="n">
+        <v>22</v>
+      </c>
+      <c r="D26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.6308641831080118</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.4101592103640239</v>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="n">
+        <v>0.5555555621782938</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.3464452524979909</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0.01176893225703141</v>
+      </c>
+      <c r="K26" t="n">
+        <v>0.08217685279196114</v>
+      </c>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>0.03747428387082062</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.04184199902328577</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.5555555621782938</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0.03747428387082062</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.554495096206665</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.03799833592158253</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ws</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C27" t="n">
+        <v>22</v>
+      </c>
+      <c r="D27" t="n">
+        <v>3</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.7669753233591715</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.6636340618133545</v>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="n">
+        <v>0.6583333214124044</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.4850857555866241</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0.02187661595596984</v>
+      </c>
+      <c r="K27" t="n">
+        <v>0.03857056303696577</v>
+      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>0.01360828770443337</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.0222654709887029</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.6583333214124044</v>
+      </c>
+      <c r="P27" t="n">
+        <v>0.01360828770443337</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.6706487735112509</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.007504073290785176</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ws</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C28" t="n">
+        <v>22</v>
+      </c>
+      <c r="D28" t="n">
+        <v>3</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.554938276608785</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.547889788945516</v>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="n">
+        <v>0.5388888915379842</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.187600647409757</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0.03448238791338994</v>
+      </c>
+      <c r="K28" t="n">
+        <v>0.005337050282270258</v>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>0.003928395358104403</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0.02465924648509743</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0.5388888915379842</v>
+      </c>
+      <c r="P28" t="n">
+        <v>0.003928395358104403</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.6486254930496216</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.04989722428412248</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ws</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C29" t="n">
+        <v>22</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.4574073950449626</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.4763709902763367</v>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="n">
+        <v>0.497222234805425</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.1413817678888639</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0.03725243515284618</v>
+      </c>
+      <c r="K29" t="n">
+        <v>0.02611922751504557</v>
+      </c>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>0.03215510874383116</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0.06043857519630202</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0.497222234805425</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0.03215510874383116</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.5012608965237936</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.06831620322264773</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>ws</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C30" t="n">
+        <v>22</v>
+      </c>
+      <c r="D30" t="n">
+        <v>3</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.4675925970077515</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.4548900624116262</v>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="n">
+        <v>0.4888888796170552</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0.08024691541989644</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0.06053318116116507</v>
+      </c>
+      <c r="K30" t="n">
+        <v>0.06051284787483691</v>
+      </c>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>0.0321550855730742</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0.06818124292876049</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0.4888888796170552</v>
+      </c>
+      <c r="P30" t="n">
+        <v>0.0321550855730742</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.4798457225163777</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.1115330794236924</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>ws</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C31" t="n">
+        <v>22</v>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.4666666487852733</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.4533737599849701</v>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="n">
+        <v>0.4805555641651154</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0.09611993034680684</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0.03998312804202871</v>
+      </c>
+      <c r="K31" t="n">
+        <v>0.04290529784879946</v>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>0.04101340806499109</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.08885984050050091</v>
+      </c>
+      <c r="O31" t="n">
+        <v>0.4805555641651154</v>
+      </c>
+      <c r="P31" t="n">
+        <v>0.04101340806499109</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.4572823643684387</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.0858000446282922</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>lung_radio_frozen</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C32" t="n">
+        <v>22</v>
+      </c>
+      <c r="D32" t="n">
+        <v>3</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.6061728398005167</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.5936315457026163</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0.1242708389957746</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0.5861111283302307</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0.4216248492399852</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0.0520187809289429</v>
+      </c>
+      <c r="K32" t="n">
+        <v>0.02796602883009606</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.002620993199262494</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.02576005466145912</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.02483285144258953</v>
+      </c>
+      <c r="O32" t="n">
+        <v>0.5861111283302307</v>
+      </c>
+      <c r="P32" t="n">
+        <v>0.02576005466145912</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>0.5647678772608439</v>
+      </c>
+      <c r="R32" t="n">
+        <v>0.01940908164067787</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>lung_radio_unfrozen</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C33" t="n">
+        <v>22</v>
+      </c>
+      <c r="D33" t="n">
+        <v>3</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.5993827184041342</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.5718979040781657</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0.1262166673938433</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0.575000007947286</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0.3978034754594167</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0.02264682721450439</v>
+      </c>
+      <c r="K33" t="n">
+        <v>0.01030885992897227</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.001969844602953353</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0.01800205872188277</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0.03545061676519656</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0.575000007947286</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0.01800205872188277</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0.5580615599950155</v>
+      </c>
+      <c r="R33" t="n">
+        <v>0.01112326027637736</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>masked_radio_frozen</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C34" t="n">
+        <v>22</v>
+      </c>
+      <c r="D34" t="n">
+        <v>3</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.6061728398005167</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.5936315457026163</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0.1242708389957746</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0.5861111283302307</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0.4216248492399852</v>
+      </c>
+      <c r="J34" t="n">
+        <v>0.0520187809289429</v>
+      </c>
+      <c r="K34" t="n">
+        <v>0.02796602883009606</v>
+      </c>
+      <c r="L34" t="n">
+        <v>0.002620993199262494</v>
+      </c>
+      <c r="M34" t="n">
+        <v>0.02576005466145912</v>
+      </c>
+      <c r="N34" t="n">
+        <v>0.02483285144258953</v>
+      </c>
+      <c r="O34" t="n">
+        <v>0.5861111283302307</v>
+      </c>
+      <c r="P34" t="n">
+        <v>0.02576005466145912</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.5647678772608439</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.01940908164067787</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ws_radio_frozen</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C35" t="n">
+        <v>22</v>
+      </c>
+      <c r="D35" t="n">
+        <v>3</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.6061728398005167</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.5936315457026163</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0.1242708389957746</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0.5861111283302307</v>
+      </c>
+      <c r="I35" t="n">
+        <v>0.4216248492399852</v>
+      </c>
+      <c r="J35" t="n">
+        <v>0.0520187809289429</v>
+      </c>
+      <c r="K35" t="n">
+        <v>0.02796602883009606</v>
+      </c>
+      <c r="L35" t="n">
+        <v>0.002620993199262494</v>
+      </c>
+      <c r="M35" t="n">
+        <v>0.02576005466145912</v>
+      </c>
+      <c r="N35" t="n">
+        <v>0.02483285144258953</v>
+      </c>
+      <c r="O35" t="n">
+        <v>0.5861111283302307</v>
+      </c>
+      <c r="P35" t="n">
+        <v>0.02576005466145912</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>0.5647678772608439</v>
+      </c>
+      <c r="R35" t="n">
+        <v>0.01940908164067787</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>masked_radio_unfrozen</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C36" t="n">
+        <v>22</v>
+      </c>
+      <c r="D36" t="n">
+        <v>3</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.5993827184041342</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.5718979040781657</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0.1262166673938433</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0.575000007947286</v>
+      </c>
+      <c r="I36" t="n">
+        <v>0.3978034754594167</v>
+      </c>
+      <c r="J36" t="n">
+        <v>0.02264682721450439</v>
+      </c>
+      <c r="K36" t="n">
+        <v>0.01030885992897227</v>
+      </c>
+      <c r="L36" t="n">
+        <v>0.001969844602953353</v>
+      </c>
+      <c r="M36" t="n">
+        <v>0.01800205872188277</v>
+      </c>
+      <c r="N36" t="n">
+        <v>0.03545061676519656</v>
+      </c>
+      <c r="O36" t="n">
+        <v>0.575000007947286</v>
+      </c>
+      <c r="P36" t="n">
+        <v>0.01800205872188277</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>0.5580615599950155</v>
+      </c>
+      <c r="R36" t="n">
+        <v>0.01112326027637736</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>ws_radio_unfrozen</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C37" t="n">
+        <v>22</v>
+      </c>
+      <c r="D37" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.5993827184041342</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.5718979040781657</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0.1262166673938433</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0.575000007947286</v>
+      </c>
+      <c r="I37" t="n">
+        <v>0.3978034754594167</v>
+      </c>
+      <c r="J37" t="n">
+        <v>0.02264682721450439</v>
+      </c>
+      <c r="K37" t="n">
+        <v>0.01030885992897227</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.001969844602953353</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.01800205872188277</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.03545061676519656</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.575000007947286</v>
+      </c>
+      <c r="P37" t="n">
+        <v>0.01800205872188277</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.5580615599950155</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.01112326027637736</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>lung_unfrozen_med_reg_64</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C38" t="n">
+        <v>22</v>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.7583333253860474</v>
+      </c>
+      <c r="F38" t="n">
+        <v>0.6909274657567342</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0.1151315396030744</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0.6861111124356588</v>
+      </c>
+      <c r="I38" t="n">
+        <v>0.5204678376515707</v>
+      </c>
+      <c r="J38" t="n">
+        <v>0.03704476253122629</v>
+      </c>
+      <c r="K38" t="n">
+        <v>0.0332223833452473</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.006930309941077968</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.02749861296829705</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.02894589359930188</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.6861111124356588</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0.02749861296829705</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.6457585493723551</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.01718248205627023</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>lung_unfrozen_med_reg_24</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C39" t="n">
+        <v>22</v>
+      </c>
+      <c r="D39" t="n">
+        <v>3</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.7583333253860474</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.6909274657567342</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0.1151315396030744</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0.6861111124356588</v>
+      </c>
+      <c r="I39" t="n">
+        <v>0.5204678376515707</v>
+      </c>
+      <c r="J39" t="n">
+        <v>0.03704476253122629</v>
+      </c>
+      <c r="K39" t="n">
+        <v>0.0332223833452473</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.006930309941077968</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.02749861296829705</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.02894589359930188</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.6861111124356588</v>
+      </c>
+      <c r="P39" t="n">
+        <v>0.02749861296829705</v>
+      </c>
+      <c r="Q39" t="n">
+        <v>0.6457585493723551</v>
+      </c>
+      <c r="R39" t="n">
+        <v>0.01718248205627023</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>lung_unfrozen_med_reg_24</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C40" t="n">
+        <v>22</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.7515432039896647</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.7065958976745605</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0.1104106903076172</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.6222222248713175</v>
+      </c>
+      <c r="I40" t="n">
+        <v>0.4110016425450643</v>
+      </c>
+      <c r="J40" t="n">
+        <v>0.02656110095530181</v>
+      </c>
+      <c r="K40" t="n">
+        <v>0.02696144616643013</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.005783183394275743</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.04631481341638571</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.09714666605188385</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.6222222248713175</v>
+      </c>
+      <c r="P40" t="n">
+        <v>0.04631481341638571</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.6404226024945577</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.026548026103587</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>lung_unfrozen_med_reg_64</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C41" t="n">
+        <v>22</v>
+      </c>
+      <c r="D41" t="n">
+        <v>3</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.7182098627090454</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.6866312821706136</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0.1201578105489413</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0.6444444457689921</v>
+      </c>
+      <c r="I41" t="n">
+        <v>0.4303233077128728</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.01371983956692996</v>
+      </c>
+      <c r="K41" t="n">
+        <v>0.009616515688300849</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.003787863766263155</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.06712802507473127</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.1412710913608317</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.6444444457689921</v>
+      </c>
+      <c r="P41" t="n">
+        <v>0.06712802507473127</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.6493601202964783</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.01006019797878372</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments_Summary.xlsx
+++ b/Experiments_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2772,6 +2772,760 @@
         <v>0.01006019797878372</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>masked_unfrozen_med_reg_24</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C42" t="n">
+        <v>22</v>
+      </c>
+      <c r="D42" t="n">
+        <v>3</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.779938280582428</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.7212534745534261</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0.1108078807592392</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="I42" t="n">
+        <v>0.5454332232475281</v>
+      </c>
+      <c r="J42" t="n">
+        <v>0.02417279762807992</v>
+      </c>
+      <c r="K42" t="n">
+        <v>0.04139772608022362</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.006992792258105583</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.04138794527037967</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.04375373816919498</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0.04138794527037967</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.6631452043851217</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.02760079309767969</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>masked_unfrozen_med_reg_24</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C43" t="n">
+        <v>22</v>
+      </c>
+      <c r="D43" t="n">
+        <v>3</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.779938280582428</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.7212534745534261</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0.1108078807592392</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="I43" t="n">
+        <v>0.5454332232475281</v>
+      </c>
+      <c r="J43" t="n">
+        <v>0.02417279762807992</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0.04139772608022362</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.006992792258105583</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.04138794527037967</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.04375373816919498</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0.04138794527037967</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.6631452043851217</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.02760079309767969</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>ws_unfrozen_med_reg_24</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C44" t="n">
+        <v>22</v>
+      </c>
+      <c r="D44" t="n">
+        <v>3</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.750308632850647</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.6972453991572062</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0.1102481509248416</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0.6472222010294596</v>
+      </c>
+      <c r="I44" t="n">
+        <v>0.4727095564206441</v>
+      </c>
+      <c r="J44" t="n">
+        <v>0.01026439158585974</v>
+      </c>
+      <c r="K44" t="n">
+        <v>0.01590710472105708</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.003657719155071491</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.01712335590034907</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.02269092807431733</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.6472222010294596</v>
+      </c>
+      <c r="P44" t="n">
+        <v>0.01712335590034907</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>0.655231237411499</v>
+      </c>
+      <c r="R44" t="n">
+        <v>0.03545959297481422</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>ws_unfrozen_med_reg_24</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C45" t="n">
+        <v>22</v>
+      </c>
+      <c r="D45" t="n">
+        <v>3</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.750308632850647</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.6972453991572062</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0.1102481509248416</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0.6472222010294596</v>
+      </c>
+      <c r="I45" t="n">
+        <v>0.4727095564206441</v>
+      </c>
+      <c r="J45" t="n">
+        <v>0.01026439158585974</v>
+      </c>
+      <c r="K45" t="n">
+        <v>0.01590710472105708</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.003657719155071491</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.01712335590034907</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.02269092807431733</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.6472222010294596</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0.01712335590034907</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.655231237411499</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.03545959297481422</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>lung_radio_frozen</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C46" t="n">
+        <v>22</v>
+      </c>
+      <c r="D46" t="n">
+        <v>3</v>
+      </c>
+      <c r="E46" t="n">
+        <v>0.5646605292956034</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.5592620571454366</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0.1267349819342295</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0.5222222208976746</v>
+      </c>
+      <c r="I46" t="n">
+        <v>0.3726898034413655</v>
+      </c>
+      <c r="J46" t="n">
+        <v>0.06943963216138521</v>
+      </c>
+      <c r="K46" t="n">
+        <v>0.03796475431558221</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.0004855356616961235</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.03747426325259959</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.03862246438014032</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.5222222208976746</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0.03747426325259959</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.5197017788887024</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.03245576114304535</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>lung_radio_unfrozen</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C47" t="n">
+        <v>22</v>
+      </c>
+      <c r="D47" t="n">
+        <v>3</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.582253078619639</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.5772049427032471</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0.1265902022520701</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0.5527777671813965</v>
+      </c>
+      <c r="I47" t="n">
+        <v>0.2964392999807994</v>
+      </c>
+      <c r="J47" t="n">
+        <v>0.01301429476918438</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0.02173070685657801</v>
+      </c>
+      <c r="L47" t="n">
+        <v>0.01228707093973039</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.01964186439892599</v>
+      </c>
+      <c r="N47" t="n">
+        <v>0.02683911843699489</v>
+      </c>
+      <c r="O47" t="n">
+        <v>0.5527777671813965</v>
+      </c>
+      <c r="P47" t="n">
+        <v>0.01964186439892599</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.5816750327746073</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.04533517937991077</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>masked_radio_frozen</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C48" t="n">
+        <v>22</v>
+      </c>
+      <c r="D48" t="n">
+        <v>3</v>
+      </c>
+      <c r="E48" t="n">
+        <v>0.4987654089927673</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.4964619576931</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0.135143925746282</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.4750000238418579</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.3736263811588287</v>
+      </c>
+      <c r="J48" t="n">
+        <v>0.04364854072333719</v>
+      </c>
+      <c r="K48" t="n">
+        <v>0.01793664925001662</v>
+      </c>
+      <c r="L48" t="n">
+        <v>0.002920762179963498</v>
+      </c>
+      <c r="M48" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" t="n">
+        <v>0.4750000238418579</v>
+      </c>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.4530516564846039</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>masked_radio_unfrozen</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C49" t="n">
+        <v>22</v>
+      </c>
+      <c r="D49" t="n">
+        <v>3</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.5231481492519379</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.4823098282019297</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0.1288677702347437</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.4833333492279053</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.2490842541058858</v>
+      </c>
+      <c r="J49" t="n">
+        <v>0.03062562846201696</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0.03731317950051978</v>
+      </c>
+      <c r="L49" t="n">
+        <v>0.004134124493627369</v>
+      </c>
+      <c r="M49" t="n">
+        <v>0.01178510178061619</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0.176129165165065</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0.4833333492279053</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0.01178510178061619</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.4270344376564026</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.03679390372207091</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ws_radio_frozen</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C50" t="n">
+        <v>22</v>
+      </c>
+      <c r="D50" t="n">
+        <v>3</v>
+      </c>
+      <c r="E50" t="n">
+        <v>0.6061728398005167</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.5936315457026163</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0.1242708389957746</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.5861111283302307</v>
+      </c>
+      <c r="I50" t="n">
+        <v>0.4216248492399852</v>
+      </c>
+      <c r="J50" t="n">
+        <v>0.0520187809289429</v>
+      </c>
+      <c r="K50" t="n">
+        <v>0.02796602883009606</v>
+      </c>
+      <c r="L50" t="n">
+        <v>0.002620993199262494</v>
+      </c>
+      <c r="M50" t="n">
+        <v>0.02576005466145912</v>
+      </c>
+      <c r="N50" t="n">
+        <v>0.02483285144258953</v>
+      </c>
+      <c r="O50" t="n">
+        <v>0.5861111283302307</v>
+      </c>
+      <c r="P50" t="n">
+        <v>0.02576005466145912</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.5647678772608439</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.01940908164067787</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>ws_radio_unfrozen</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C51" t="n">
+        <v>22</v>
+      </c>
+      <c r="D51" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.5993827184041342</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.5718979040781657</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0.1262166673938433</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0.575000007947286</v>
+      </c>
+      <c r="I51" t="n">
+        <v>0.3978034754594167</v>
+      </c>
+      <c r="J51" t="n">
+        <v>0.02264682721450439</v>
+      </c>
+      <c r="K51" t="n">
+        <v>0.01030885992897227</v>
+      </c>
+      <c r="L51" t="n">
+        <v>0.001969844602953353</v>
+      </c>
+      <c r="M51" t="n">
+        <v>0.01800205872188277</v>
+      </c>
+      <c r="N51" t="n">
+        <v>0.03545061676519656</v>
+      </c>
+      <c r="O51" t="n">
+        <v>0.575000007947286</v>
+      </c>
+      <c r="P51" t="n">
+        <v>0.01800205872188277</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.5580615599950155</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.01112326027637736</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>lung_unfrozen_med_reg_24</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C52" t="n">
+        <v>22</v>
+      </c>
+      <c r="D52" t="n">
+        <v>3</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.7515432039896647</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.7065958976745605</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0.1104106903076172</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.6222222248713175</v>
+      </c>
+      <c r="I52" t="n">
+        <v>0.4110016425450643</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0.02656110095530181</v>
+      </c>
+      <c r="K52" t="n">
+        <v>0.02696144616643013</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0.005783183394275743</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0.04631481341638571</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0.09714666605188385</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0.6222222248713175</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0.04631481341638571</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.6404226024945577</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.026548026103587</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>masked_unfrozen_med_reg_24</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C53" t="n">
+        <v>22</v>
+      </c>
+      <c r="D53" t="n">
+        <v>3</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.779938280582428</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.7212534745534261</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0.1108078807592392</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="I53" t="n">
+        <v>0.5454332232475281</v>
+      </c>
+      <c r="J53" t="n">
+        <v>0.02417279762807992</v>
+      </c>
+      <c r="K53" t="n">
+        <v>0.04139772608022362</v>
+      </c>
+      <c r="L53" t="n">
+        <v>0.006992792258105583</v>
+      </c>
+      <c r="M53" t="n">
+        <v>0.04138794527037967</v>
+      </c>
+      <c r="N53" t="n">
+        <v>0.04375373816919498</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0.7083333333333334</v>
+      </c>
+      <c r="P53" t="n">
+        <v>0.04138794527037967</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.6631452043851217</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.02760079309767969</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>ws_unfrozen_med_reg_24</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C54" t="n">
+        <v>22</v>
+      </c>
+      <c r="D54" t="n">
+        <v>3</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.750308632850647</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.6972453991572062</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0.1102481509248416</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.6472222010294596</v>
+      </c>
+      <c r="I54" t="n">
+        <v>0.4727095564206441</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.01026439158585974</v>
+      </c>
+      <c r="K54" t="n">
+        <v>0.01590710472105708</v>
+      </c>
+      <c r="L54" t="n">
+        <v>0.003657719155071491</v>
+      </c>
+      <c r="M54" t="n">
+        <v>0.01712335590034907</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.02269092807431733</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.6472222010294596</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.01712335590034907</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.655231237411499</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.03545959297481422</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Experiments_Summary.xlsx
+++ b/Experiments_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R54"/>
+  <dimension ref="A1:R82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1709,7 +1709,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ws</t>
+          <t>lung_radio_frozen</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -1722,48 +1722,52 @@
         <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6750000317891439</v>
+        <v>0.6061728398005167</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5352539817492167</v>
-      </c>
-      <c r="G23" t="inlineStr"/>
+        <v>0.5936315457026163</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.1242708389957746</v>
+      </c>
       <c r="H23" t="n">
-        <v>0.569444457689921</v>
+        <v>0.5861111283302307</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2883597960074742</v>
+        <v>0.4216248492399852</v>
       </c>
       <c r="J23" t="n">
-        <v>0.04876738852446711</v>
+        <v>0.0520187809289429</v>
       </c>
       <c r="K23" t="n">
-        <v>0.04299898082445552</v>
-      </c>
-      <c r="L23" t="inlineStr"/>
+        <v>0.02796602883009606</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.002620993199262494</v>
+      </c>
       <c r="M23" t="n">
-        <v>0.02389535058159446</v>
+        <v>0.02576005466145912</v>
       </c>
       <c r="N23" t="n">
-        <v>0.05511287742699388</v>
+        <v>0.02483285144258953</v>
       </c>
       <c r="O23" t="n">
-        <v>0.569444457689921</v>
+        <v>0.5861111283302307</v>
       </c>
       <c r="P23" t="n">
-        <v>0.02389535058159446</v>
+        <v>0.02576005466145912</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.6483565370241801</v>
+        <v>0.5647678772608439</v>
       </c>
       <c r="R23" t="n">
-        <v>0.04559983856047613</v>
+        <v>0.01940908164067787</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ws</t>
+          <t>lung_radio_unfrozen</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -1776,48 +1780,52 @@
         <v>3</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6750000317891439</v>
+        <v>0.5993827184041342</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5352539817492167</v>
-      </c>
-      <c r="G24" t="inlineStr"/>
+        <v>0.5718979040781657</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.1262166673938433</v>
+      </c>
       <c r="H24" t="n">
-        <v>0.6361111203829447</v>
+        <v>0.575000007947286</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4512180785338084</v>
+        <v>0.3978034754594167</v>
       </c>
       <c r="J24" t="n">
-        <v>0.04876738852446711</v>
+        <v>0.02264682721450439</v>
       </c>
       <c r="K24" t="n">
-        <v>0.04299898082445552</v>
-      </c>
-      <c r="L24" t="inlineStr"/>
+        <v>0.01030885992897227</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.001969844602953353</v>
+      </c>
       <c r="M24" t="n">
-        <v>0.03491611882203919</v>
+        <v>0.01800205872188277</v>
       </c>
       <c r="N24" t="n">
-        <v>0.05617007846464612</v>
+        <v>0.03545061676519656</v>
       </c>
       <c r="O24" t="n">
-        <v>0.6361111203829447</v>
+        <v>0.575000007947286</v>
       </c>
       <c r="P24" t="n">
-        <v>0.03491611882203919</v>
+        <v>0.01800205872188277</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.6701036890347799</v>
+        <v>0.5580615599950155</v>
       </c>
       <c r="R24" t="n">
-        <v>0.05639690825394791</v>
+        <v>0.01112326027637736</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ws</t>
+          <t>masked_radio_frozen</t>
         </is>
       </c>
       <c r="B25" t="n">
@@ -1830,48 +1838,52 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6040123303731283</v>
+        <v>0.6061728398005167</v>
       </c>
       <c r="F25" t="n">
-        <v>0.4023249844710032</v>
-      </c>
-      <c r="G25" t="inlineStr"/>
+        <v>0.5936315457026163</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.1242708389957746</v>
+      </c>
       <c r="H25" t="n">
         <v>0.5861111283302307</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3925263384977977</v>
+        <v>0.4216248492399852</v>
       </c>
       <c r="J25" t="n">
-        <v>0.01680890165551272</v>
+        <v>0.0520187809289429</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0877760461480723</v>
-      </c>
-      <c r="L25" t="inlineStr"/>
+        <v>0.02796602883009606</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.002620993199262494</v>
+      </c>
       <c r="M25" t="n">
-        <v>0.01571348308978993</v>
+        <v>0.02576005466145912</v>
       </c>
       <c r="N25" t="n">
-        <v>0.02491096407036001</v>
+        <v>0.02483285144258953</v>
       </c>
       <c r="O25" t="n">
         <v>0.5861111283302307</v>
       </c>
       <c r="P25" t="n">
-        <v>0.01571348308978993</v>
+        <v>0.02576005466145912</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.5779856642087301</v>
+        <v>0.5647678772608439</v>
       </c>
       <c r="R25" t="n">
-        <v>0.01715543494942115</v>
+        <v>0.01940908164067787</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ws</t>
+          <t>ws_radio_frozen</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -1884,48 +1896,52 @@
         <v>3</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6308641831080118</v>
+        <v>0.6061728398005167</v>
       </c>
       <c r="F26" t="n">
-        <v>0.4101592103640239</v>
-      </c>
-      <c r="G26" t="inlineStr"/>
+        <v>0.5936315457026163</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0.1242708389957746</v>
+      </c>
       <c r="H26" t="n">
-        <v>0.5555555621782938</v>
+        <v>0.5861111283302307</v>
       </c>
       <c r="I26" t="n">
-        <v>0.3464452524979909</v>
+        <v>0.4216248492399852</v>
       </c>
       <c r="J26" t="n">
-        <v>0.01176893225703141</v>
+        <v>0.0520187809289429</v>
       </c>
       <c r="K26" t="n">
-        <v>0.08217685279196114</v>
-      </c>
-      <c r="L26" t="inlineStr"/>
+        <v>0.02796602883009606</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.002620993199262494</v>
+      </c>
       <c r="M26" t="n">
-        <v>0.03747428387082062</v>
+        <v>0.02576005466145912</v>
       </c>
       <c r="N26" t="n">
-        <v>0.04184199902328577</v>
+        <v>0.02483285144258953</v>
       </c>
       <c r="O26" t="n">
-        <v>0.5555555621782938</v>
+        <v>0.5861111283302307</v>
       </c>
       <c r="P26" t="n">
-        <v>0.03747428387082062</v>
+        <v>0.02576005466145912</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.554495096206665</v>
+        <v>0.5647678772608439</v>
       </c>
       <c r="R26" t="n">
-        <v>0.03799833592158253</v>
+        <v>0.01940908164067787</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ws</t>
+          <t>masked_radio_unfrozen</t>
         </is>
       </c>
       <c r="B27" t="n">
@@ -1938,48 +1954,52 @@
         <v>3</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7669753233591715</v>
+        <v>0.5993827184041342</v>
       </c>
       <c r="F27" t="n">
-        <v>0.6636340618133545</v>
-      </c>
-      <c r="G27" t="inlineStr"/>
+        <v>0.5718979040781657</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.1262166673938433</v>
+      </c>
       <c r="H27" t="n">
-        <v>0.6583333214124044</v>
+        <v>0.575000007947286</v>
       </c>
       <c r="I27" t="n">
-        <v>0.4850857555866241</v>
+        <v>0.3978034754594167</v>
       </c>
       <c r="J27" t="n">
-        <v>0.02187661595596984</v>
+        <v>0.02264682721450439</v>
       </c>
       <c r="K27" t="n">
-        <v>0.03857056303696577</v>
-      </c>
-      <c r="L27" t="inlineStr"/>
+        <v>0.01030885992897227</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.001969844602953353</v>
+      </c>
       <c r="M27" t="n">
-        <v>0.01360828770443337</v>
+        <v>0.01800205872188277</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0222654709887029</v>
+        <v>0.03545061676519656</v>
       </c>
       <c r="O27" t="n">
-        <v>0.6583333214124044</v>
+        <v>0.575000007947286</v>
       </c>
       <c r="P27" t="n">
-        <v>0.01360828770443337</v>
+        <v>0.01800205872188277</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.6706487735112509</v>
+        <v>0.5580615599950155</v>
       </c>
       <c r="R27" t="n">
-        <v>0.007504073290785176</v>
+        <v>0.01112326027637736</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ws</t>
+          <t>ws_radio_unfrozen</t>
         </is>
       </c>
       <c r="B28" t="n">
@@ -1992,48 +2012,52 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>0.554938276608785</v>
+        <v>0.5993827184041342</v>
       </c>
       <c r="F28" t="n">
-        <v>0.547889788945516</v>
-      </c>
-      <c r="G28" t="inlineStr"/>
+        <v>0.5718979040781657</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0.1262166673938433</v>
+      </c>
       <c r="H28" t="n">
-        <v>0.5388888915379842</v>
+        <v>0.575000007947286</v>
       </c>
       <c r="I28" t="n">
-        <v>0.187600647409757</v>
+        <v>0.3978034754594167</v>
       </c>
       <c r="J28" t="n">
-        <v>0.03448238791338994</v>
+        <v>0.02264682721450439</v>
       </c>
       <c r="K28" t="n">
-        <v>0.005337050282270258</v>
-      </c>
-      <c r="L28" t="inlineStr"/>
+        <v>0.01030885992897227</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0.001969844602953353</v>
+      </c>
       <c r="M28" t="n">
-        <v>0.003928395358104403</v>
+        <v>0.01800205872188277</v>
       </c>
       <c r="N28" t="n">
-        <v>0.02465924648509743</v>
+        <v>0.03545061676519656</v>
       </c>
       <c r="O28" t="n">
-        <v>0.5388888915379842</v>
+        <v>0.575000007947286</v>
       </c>
       <c r="P28" t="n">
-        <v>0.003928395358104403</v>
+        <v>0.01800205872188277</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.6486254930496216</v>
+        <v>0.5580615599950155</v>
       </c>
       <c r="R28" t="n">
-        <v>0.04989722428412248</v>
+        <v>0.01112326027637736</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ws</t>
+          <t>lung_unfrozen_med_reg_64</t>
         </is>
       </c>
       <c r="B29" t="n">
@@ -2046,48 +2070,52 @@
         <v>3</v>
       </c>
       <c r="E29" t="n">
-        <v>0.4574073950449626</v>
+        <v>0.7583333253860474</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4763709902763367</v>
-      </c>
-      <c r="G29" t="inlineStr"/>
+        <v>0.6909274657567342</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.1151315396030744</v>
+      </c>
       <c r="H29" t="n">
-        <v>0.497222234805425</v>
+        <v>0.6861111124356588</v>
       </c>
       <c r="I29" t="n">
-        <v>0.1413817678888639</v>
+        <v>0.5204678376515707</v>
       </c>
       <c r="J29" t="n">
-        <v>0.03725243515284618</v>
+        <v>0.03704476253122629</v>
       </c>
       <c r="K29" t="n">
-        <v>0.02611922751504557</v>
-      </c>
-      <c r="L29" t="inlineStr"/>
+        <v>0.0332223833452473</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0.006930309941077968</v>
+      </c>
       <c r="M29" t="n">
-        <v>0.03215510874383116</v>
+        <v>0.02749861296829705</v>
       </c>
       <c r="N29" t="n">
-        <v>0.06043857519630202</v>
+        <v>0.02894589359930188</v>
       </c>
       <c r="O29" t="n">
-        <v>0.497222234805425</v>
+        <v>0.6861111124356588</v>
       </c>
       <c r="P29" t="n">
-        <v>0.03215510874383116</v>
+        <v>0.02749861296829705</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.5012608965237936</v>
+        <v>0.6457585493723551</v>
       </c>
       <c r="R29" t="n">
-        <v>0.06831620322264773</v>
+        <v>0.01718248205627023</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ws</t>
+          <t>lung_unfrozen_med_reg_24</t>
         </is>
       </c>
       <c r="B30" t="n">
@@ -2100,48 +2128,52 @@
         <v>3</v>
       </c>
       <c r="E30" t="n">
-        <v>0.4675925970077515</v>
+        <v>0.7583333253860474</v>
       </c>
       <c r="F30" t="n">
-        <v>0.4548900624116262</v>
-      </c>
-      <c r="G30" t="inlineStr"/>
+        <v>0.6909274657567342</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0.1151315396030744</v>
+      </c>
       <c r="H30" t="n">
-        <v>0.4888888796170552</v>
+        <v>0.6861111124356588</v>
       </c>
       <c r="I30" t="n">
-        <v>0.08024691541989644</v>
+        <v>0.5204678376515707</v>
       </c>
       <c r="J30" t="n">
-        <v>0.06053318116116507</v>
+        <v>0.03704476253122629</v>
       </c>
       <c r="K30" t="n">
-        <v>0.06051284787483691</v>
-      </c>
-      <c r="L30" t="inlineStr"/>
+        <v>0.0332223833452473</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.006930309941077968</v>
+      </c>
       <c r="M30" t="n">
-        <v>0.0321550855730742</v>
+        <v>0.02749861296829705</v>
       </c>
       <c r="N30" t="n">
-        <v>0.06818124292876049</v>
+        <v>0.02894589359930188</v>
       </c>
       <c r="O30" t="n">
-        <v>0.4888888796170552</v>
+        <v>0.6861111124356588</v>
       </c>
       <c r="P30" t="n">
-        <v>0.0321550855730742</v>
+        <v>0.02749861296829705</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.4798457225163777</v>
+        <v>0.6457585493723551</v>
       </c>
       <c r="R30" t="n">
-        <v>0.1115330794236924</v>
+        <v>0.01718248205627023</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ws</t>
+          <t>lung_unfrozen_med_reg_24</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -2154,48 +2186,52 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>0.4666666487852733</v>
+        <v>0.7515432039896647</v>
       </c>
       <c r="F31" t="n">
-        <v>0.4533737599849701</v>
-      </c>
-      <c r="G31" t="inlineStr"/>
+        <v>0.7065958976745605</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0.1104106903076172</v>
+      </c>
       <c r="H31" t="n">
-        <v>0.4805555641651154</v>
+        <v>0.6222222248713175</v>
       </c>
       <c r="I31" t="n">
-        <v>0.09611993034680684</v>
+        <v>0.4110016425450643</v>
       </c>
       <c r="J31" t="n">
-        <v>0.03998312804202871</v>
+        <v>0.02656110095530181</v>
       </c>
       <c r="K31" t="n">
-        <v>0.04290529784879946</v>
-      </c>
-      <c r="L31" t="inlineStr"/>
+        <v>0.02696144616643013</v>
+      </c>
+      <c r="L31" t="n">
+        <v>0.005783183394275743</v>
+      </c>
       <c r="M31" t="n">
-        <v>0.04101340806499109</v>
+        <v>0.04631481341638571</v>
       </c>
       <c r="N31" t="n">
-        <v>0.08885984050050091</v>
+        <v>0.09714666605188385</v>
       </c>
       <c r="O31" t="n">
-        <v>0.4805555641651154</v>
+        <v>0.6222222248713175</v>
       </c>
       <c r="P31" t="n">
-        <v>0.04101340806499109</v>
+        <v>0.04631481341638571</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.4572823643684387</v>
+        <v>0.6404226024945577</v>
       </c>
       <c r="R31" t="n">
-        <v>0.0858000446282922</v>
+        <v>0.026548026103587</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>lung_radio_frozen</t>
+          <t>lung_unfrozen_med_reg_64</t>
         </is>
       </c>
       <c r="B32" t="n">
@@ -2208,52 +2244,52 @@
         <v>3</v>
       </c>
       <c r="E32" t="n">
-        <v>0.6061728398005167</v>
+        <v>0.7182098627090454</v>
       </c>
       <c r="F32" t="n">
-        <v>0.5936315457026163</v>
+        <v>0.6866312821706136</v>
       </c>
       <c r="G32" t="n">
-        <v>0.1242708389957746</v>
+        <v>0.1201578105489413</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5861111283302307</v>
+        <v>0.6444444457689921</v>
       </c>
       <c r="I32" t="n">
-        <v>0.4216248492399852</v>
+        <v>0.4303233077128728</v>
       </c>
       <c r="J32" t="n">
-        <v>0.0520187809289429</v>
+        <v>0.01371983956692996</v>
       </c>
       <c r="K32" t="n">
-        <v>0.02796602883009606</v>
+        <v>0.009616515688300849</v>
       </c>
       <c r="L32" t="n">
-        <v>0.002620993199262494</v>
+        <v>0.003787863766263155</v>
       </c>
       <c r="M32" t="n">
-        <v>0.02576005466145912</v>
+        <v>0.06712802507473127</v>
       </c>
       <c r="N32" t="n">
-        <v>0.02483285144258953</v>
+        <v>0.1412710913608317</v>
       </c>
       <c r="O32" t="n">
-        <v>0.5861111283302307</v>
+        <v>0.6444444457689921</v>
       </c>
       <c r="P32" t="n">
-        <v>0.02576005466145912</v>
+        <v>0.06712802507473127</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.5647678772608439</v>
+        <v>0.6493601202964783</v>
       </c>
       <c r="R32" t="n">
-        <v>0.01940908164067787</v>
+        <v>0.01006019797878372</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>lung_radio_unfrozen</t>
+          <t>masked_unfrozen_med_reg_24</t>
         </is>
       </c>
       <c r="B33" t="n">
@@ -2266,52 +2302,52 @@
         <v>3</v>
       </c>
       <c r="E33" t="n">
-        <v>0.5993827184041342</v>
+        <v>0.779938280582428</v>
       </c>
       <c r="F33" t="n">
-        <v>0.5718979040781657</v>
+        <v>0.7212534745534261</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1262166673938433</v>
+        <v>0.1108078807592392</v>
       </c>
       <c r="H33" t="n">
-        <v>0.575000007947286</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="I33" t="n">
-        <v>0.3978034754594167</v>
+        <v>0.5454332232475281</v>
       </c>
       <c r="J33" t="n">
-        <v>0.02264682721450439</v>
+        <v>0.02417279762807992</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01030885992897227</v>
+        <v>0.04139772608022362</v>
       </c>
       <c r="L33" t="n">
-        <v>0.001969844602953353</v>
+        <v>0.006992792258105583</v>
       </c>
       <c r="M33" t="n">
-        <v>0.01800205872188277</v>
+        <v>0.04138794527037967</v>
       </c>
       <c r="N33" t="n">
-        <v>0.03545061676519656</v>
+        <v>0.04375373816919498</v>
       </c>
       <c r="O33" t="n">
-        <v>0.575000007947286</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="P33" t="n">
-        <v>0.01800205872188277</v>
+        <v>0.04138794527037967</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.5580615599950155</v>
+        <v>0.6631452043851217</v>
       </c>
       <c r="R33" t="n">
-        <v>0.01112326027637736</v>
+        <v>0.02760079309767969</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>masked_radio_frozen</t>
+          <t>masked_unfrozen_med_reg_24</t>
         </is>
       </c>
       <c r="B34" t="n">
@@ -2324,52 +2360,52 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6061728398005167</v>
+        <v>0.779938280582428</v>
       </c>
       <c r="F34" t="n">
-        <v>0.5936315457026163</v>
+        <v>0.7212534745534261</v>
       </c>
       <c r="G34" t="n">
-        <v>0.1242708389957746</v>
+        <v>0.1108078807592392</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5861111283302307</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4216248492399852</v>
+        <v>0.5454332232475281</v>
       </c>
       <c r="J34" t="n">
-        <v>0.0520187809289429</v>
+        <v>0.02417279762807992</v>
       </c>
       <c r="K34" t="n">
-        <v>0.02796602883009606</v>
+        <v>0.04139772608022362</v>
       </c>
       <c r="L34" t="n">
-        <v>0.002620993199262494</v>
+        <v>0.006992792258105583</v>
       </c>
       <c r="M34" t="n">
-        <v>0.02576005466145912</v>
+        <v>0.04138794527037967</v>
       </c>
       <c r="N34" t="n">
-        <v>0.02483285144258953</v>
+        <v>0.04375373816919498</v>
       </c>
       <c r="O34" t="n">
-        <v>0.5861111283302307</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="P34" t="n">
-        <v>0.02576005466145912</v>
+        <v>0.04138794527037967</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.5647678772608439</v>
+        <v>0.6631452043851217</v>
       </c>
       <c r="R34" t="n">
-        <v>0.01940908164067787</v>
+        <v>0.02760079309767969</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ws_radio_frozen</t>
+          <t>ws_unfrozen_med_reg_24</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -2382,52 +2418,52 @@
         <v>3</v>
       </c>
       <c r="E35" t="n">
-        <v>0.6061728398005167</v>
+        <v>0.750308632850647</v>
       </c>
       <c r="F35" t="n">
-        <v>0.5936315457026163</v>
+        <v>0.6972453991572062</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1242708389957746</v>
+        <v>0.1102481509248416</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5861111283302307</v>
+        <v>0.6472222010294596</v>
       </c>
       <c r="I35" t="n">
-        <v>0.4216248492399852</v>
+        <v>0.4727095564206441</v>
       </c>
       <c r="J35" t="n">
-        <v>0.0520187809289429</v>
+        <v>0.01026439158585974</v>
       </c>
       <c r="K35" t="n">
-        <v>0.02796602883009606</v>
+        <v>0.01590710472105708</v>
       </c>
       <c r="L35" t="n">
-        <v>0.002620993199262494</v>
+        <v>0.003657719155071491</v>
       </c>
       <c r="M35" t="n">
-        <v>0.02576005466145912</v>
+        <v>0.01712335590034907</v>
       </c>
       <c r="N35" t="n">
-        <v>0.02483285144258953</v>
+        <v>0.02269092807431733</v>
       </c>
       <c r="O35" t="n">
-        <v>0.5861111283302307</v>
+        <v>0.6472222010294596</v>
       </c>
       <c r="P35" t="n">
-        <v>0.02576005466145912</v>
+        <v>0.01712335590034907</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.5647678772608439</v>
+        <v>0.655231237411499</v>
       </c>
       <c r="R35" t="n">
-        <v>0.01940908164067787</v>
+        <v>0.03545959297481422</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>masked_radio_unfrozen</t>
+          <t>ws_unfrozen_med_reg_24</t>
         </is>
       </c>
       <c r="B36" t="n">
@@ -2440,52 +2476,52 @@
         <v>3</v>
       </c>
       <c r="E36" t="n">
-        <v>0.5993827184041342</v>
+        <v>0.750308632850647</v>
       </c>
       <c r="F36" t="n">
-        <v>0.5718979040781657</v>
+        <v>0.6972453991572062</v>
       </c>
       <c r="G36" t="n">
-        <v>0.1262166673938433</v>
+        <v>0.1102481509248416</v>
       </c>
       <c r="H36" t="n">
-        <v>0.575000007947286</v>
+        <v>0.6472222010294596</v>
       </c>
       <c r="I36" t="n">
-        <v>0.3978034754594167</v>
+        <v>0.4727095564206441</v>
       </c>
       <c r="J36" t="n">
-        <v>0.02264682721450439</v>
+        <v>0.01026439158585974</v>
       </c>
       <c r="K36" t="n">
-        <v>0.01030885992897227</v>
+        <v>0.01590710472105708</v>
       </c>
       <c r="L36" t="n">
-        <v>0.001969844602953353</v>
+        <v>0.003657719155071491</v>
       </c>
       <c r="M36" t="n">
-        <v>0.01800205872188277</v>
+        <v>0.01712335590034907</v>
       </c>
       <c r="N36" t="n">
-        <v>0.03545061676519656</v>
+        <v>0.02269092807431733</v>
       </c>
       <c r="O36" t="n">
-        <v>0.575000007947286</v>
+        <v>0.6472222010294596</v>
       </c>
       <c r="P36" t="n">
-        <v>0.01800205872188277</v>
+        <v>0.01712335590034907</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.5580615599950155</v>
+        <v>0.655231237411499</v>
       </c>
       <c r="R36" t="n">
-        <v>0.01112326027637736</v>
+        <v>0.03545959297481422</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ws_radio_unfrozen</t>
+          <t>lung_radio_frozen</t>
         </is>
       </c>
       <c r="B37" t="n">
@@ -2498,52 +2534,52 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>0.5993827184041342</v>
+        <v>0.5646605292956034</v>
       </c>
       <c r="F37" t="n">
-        <v>0.5718979040781657</v>
+        <v>0.5592620571454366</v>
       </c>
       <c r="G37" t="n">
-        <v>0.1262166673938433</v>
+        <v>0.1267349819342295</v>
       </c>
       <c r="H37" t="n">
-        <v>0.575000007947286</v>
+        <v>0.5222222208976746</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3978034754594167</v>
+        <v>0.3726898034413655</v>
       </c>
       <c r="J37" t="n">
-        <v>0.02264682721450439</v>
+        <v>0.06943963216138521</v>
       </c>
       <c r="K37" t="n">
-        <v>0.01030885992897227</v>
+        <v>0.03796475431558221</v>
       </c>
       <c r="L37" t="n">
-        <v>0.001969844602953353</v>
+        <v>0.0004855356616961235</v>
       </c>
       <c r="M37" t="n">
-        <v>0.01800205872188277</v>
+        <v>0.03747426325259959</v>
       </c>
       <c r="N37" t="n">
-        <v>0.03545061676519656</v>
+        <v>0.03862246438014032</v>
       </c>
       <c r="O37" t="n">
-        <v>0.575000007947286</v>
+        <v>0.5222222208976746</v>
       </c>
       <c r="P37" t="n">
-        <v>0.01800205872188277</v>
+        <v>0.03747426325259959</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.5580615599950155</v>
+        <v>0.5197017788887024</v>
       </c>
       <c r="R37" t="n">
-        <v>0.01112326027637736</v>
+        <v>0.03245576114304535</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>lung_unfrozen_med_reg_64</t>
+          <t>lung_radio_unfrozen</t>
         </is>
       </c>
       <c r="B38" t="n">
@@ -2556,52 +2592,52 @@
         <v>3</v>
       </c>
       <c r="E38" t="n">
-        <v>0.7583333253860474</v>
+        <v>0.582253078619639</v>
       </c>
       <c r="F38" t="n">
-        <v>0.6909274657567342</v>
+        <v>0.5772049427032471</v>
       </c>
       <c r="G38" t="n">
-        <v>0.1151315396030744</v>
+        <v>0.1265902022520701</v>
       </c>
       <c r="H38" t="n">
-        <v>0.6861111124356588</v>
+        <v>0.5527777671813965</v>
       </c>
       <c r="I38" t="n">
-        <v>0.5204678376515707</v>
+        <v>0.2964392999807994</v>
       </c>
       <c r="J38" t="n">
-        <v>0.03704476253122629</v>
+        <v>0.01301429476918438</v>
       </c>
       <c r="K38" t="n">
-        <v>0.0332223833452473</v>
+        <v>0.02173070685657801</v>
       </c>
       <c r="L38" t="n">
-        <v>0.006930309941077968</v>
+        <v>0.01228707093973039</v>
       </c>
       <c r="M38" t="n">
-        <v>0.02749861296829705</v>
+        <v>0.01964186439892599</v>
       </c>
       <c r="N38" t="n">
-        <v>0.02894589359930188</v>
+        <v>0.02683911843699489</v>
       </c>
       <c r="O38" t="n">
-        <v>0.6861111124356588</v>
+        <v>0.5527777671813965</v>
       </c>
       <c r="P38" t="n">
-        <v>0.02749861296829705</v>
+        <v>0.01964186439892599</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.6457585493723551</v>
+        <v>0.5816750327746073</v>
       </c>
       <c r="R38" t="n">
-        <v>0.01718248205627023</v>
+        <v>0.04533517937991077</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>lung_unfrozen_med_reg_24</t>
+          <t>masked_radio_frozen</t>
         </is>
       </c>
       <c r="B39" t="n">
@@ -2614,52 +2650,52 @@
         <v>3</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7583333253860474</v>
+        <v>0.4987654089927673</v>
       </c>
       <c r="F39" t="n">
-        <v>0.6909274657567342</v>
+        <v>0.4964619576931</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1151315396030744</v>
+        <v>0.135143925746282</v>
       </c>
       <c r="H39" t="n">
-        <v>0.6861111124356588</v>
+        <v>0.4750000238418579</v>
       </c>
       <c r="I39" t="n">
-        <v>0.5204678376515707</v>
+        <v>0.3736263811588287</v>
       </c>
       <c r="J39" t="n">
-        <v>0.03704476253122629</v>
+        <v>0.04364854072333719</v>
       </c>
       <c r="K39" t="n">
-        <v>0.0332223833452473</v>
+        <v>0.01793664925001662</v>
       </c>
       <c r="L39" t="n">
-        <v>0.006930309941077968</v>
+        <v>0.002920762179963498</v>
       </c>
       <c r="M39" t="n">
-        <v>0.02749861296829705</v>
+        <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0.02894589359930188</v>
+        <v>0</v>
       </c>
       <c r="O39" t="n">
-        <v>0.6861111124356588</v>
+        <v>0.4750000238418579</v>
       </c>
       <c r="P39" t="n">
-        <v>0.02749861296829705</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.6457585493723551</v>
+        <v>0.4530516564846039</v>
       </c>
       <c r="R39" t="n">
-        <v>0.01718248205627023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>lung_unfrozen_med_reg_24</t>
+          <t>masked_radio_unfrozen</t>
         </is>
       </c>
       <c r="B40" t="n">
@@ -2672,52 +2708,52 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>0.7515432039896647</v>
+        <v>0.5231481492519379</v>
       </c>
       <c r="F40" t="n">
-        <v>0.7065958976745605</v>
+        <v>0.4823098282019297</v>
       </c>
       <c r="G40" t="n">
-        <v>0.1104106903076172</v>
+        <v>0.1288677702347437</v>
       </c>
       <c r="H40" t="n">
-        <v>0.6222222248713175</v>
+        <v>0.4833333492279053</v>
       </c>
       <c r="I40" t="n">
-        <v>0.4110016425450643</v>
+        <v>0.2490842541058858</v>
       </c>
       <c r="J40" t="n">
-        <v>0.02656110095530181</v>
+        <v>0.03062562846201696</v>
       </c>
       <c r="K40" t="n">
-        <v>0.02696144616643013</v>
+        <v>0.03731317950051978</v>
       </c>
       <c r="L40" t="n">
-        <v>0.005783183394275743</v>
+        <v>0.004134124493627369</v>
       </c>
       <c r="M40" t="n">
-        <v>0.04631481341638571</v>
+        <v>0.01178510178061619</v>
       </c>
       <c r="N40" t="n">
-        <v>0.09714666605188385</v>
+        <v>0.176129165165065</v>
       </c>
       <c r="O40" t="n">
-        <v>0.6222222248713175</v>
+        <v>0.4833333492279053</v>
       </c>
       <c r="P40" t="n">
-        <v>0.04631481341638571</v>
+        <v>0.01178510178061619</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.6404226024945577</v>
+        <v>0.4270344376564026</v>
       </c>
       <c r="R40" t="n">
-        <v>0.026548026103587</v>
+        <v>0.03679390372207091</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>lung_unfrozen_med_reg_64</t>
+          <t>ws_radio_frozen</t>
         </is>
       </c>
       <c r="B41" t="n">
@@ -2730,52 +2766,52 @@
         <v>3</v>
       </c>
       <c r="E41" t="n">
-        <v>0.7182098627090454</v>
+        <v>0.6061728398005167</v>
       </c>
       <c r="F41" t="n">
-        <v>0.6866312821706136</v>
+        <v>0.5936315457026163</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1201578105489413</v>
+        <v>0.1242708389957746</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6444444457689921</v>
+        <v>0.5861111283302307</v>
       </c>
       <c r="I41" t="n">
-        <v>0.4303233077128728</v>
+        <v>0.4216248492399852</v>
       </c>
       <c r="J41" t="n">
-        <v>0.01371983956692996</v>
+        <v>0.0520187809289429</v>
       </c>
       <c r="K41" t="n">
-        <v>0.009616515688300849</v>
+        <v>0.02796602883009606</v>
       </c>
       <c r="L41" t="n">
-        <v>0.003787863766263155</v>
+        <v>0.002620993199262494</v>
       </c>
       <c r="M41" t="n">
-        <v>0.06712802507473127</v>
+        <v>0.02576005466145912</v>
       </c>
       <c r="N41" t="n">
-        <v>0.1412710913608317</v>
+        <v>0.02483285144258953</v>
       </c>
       <c r="O41" t="n">
-        <v>0.6444444457689921</v>
+        <v>0.5861111283302307</v>
       </c>
       <c r="P41" t="n">
-        <v>0.06712802507473127</v>
+        <v>0.02576005466145912</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.6493601202964783</v>
+        <v>0.5647678772608439</v>
       </c>
       <c r="R41" t="n">
-        <v>0.01006019797878372</v>
+        <v>0.01940908164067787</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>masked_unfrozen_med_reg_24</t>
+          <t>ws_radio_unfrozen</t>
         </is>
       </c>
       <c r="B42" t="n">
@@ -2788,52 +2824,52 @@
         <v>3</v>
       </c>
       <c r="E42" t="n">
-        <v>0.779938280582428</v>
+        <v>0.5993827184041342</v>
       </c>
       <c r="F42" t="n">
-        <v>0.7212534745534261</v>
+        <v>0.5718979040781657</v>
       </c>
       <c r="G42" t="n">
-        <v>0.1108078807592392</v>
+        <v>0.1262166673938433</v>
       </c>
       <c r="H42" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.575000007947286</v>
       </c>
       <c r="I42" t="n">
-        <v>0.5454332232475281</v>
+        <v>0.3978034754594167</v>
       </c>
       <c r="J42" t="n">
-        <v>0.02417279762807992</v>
+        <v>0.02264682721450439</v>
       </c>
       <c r="K42" t="n">
-        <v>0.04139772608022362</v>
+        <v>0.01030885992897227</v>
       </c>
       <c r="L42" t="n">
-        <v>0.006992792258105583</v>
+        <v>0.001969844602953353</v>
       </c>
       <c r="M42" t="n">
-        <v>0.04138794527037967</v>
+        <v>0.01800205872188277</v>
       </c>
       <c r="N42" t="n">
-        <v>0.04375373816919498</v>
+        <v>0.03545061676519656</v>
       </c>
       <c r="O42" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.575000007947286</v>
       </c>
       <c r="P42" t="n">
-        <v>0.04138794527037967</v>
+        <v>0.01800205872188277</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.6631452043851217</v>
+        <v>0.5580615599950155</v>
       </c>
       <c r="R42" t="n">
-        <v>0.02760079309767969</v>
+        <v>0.01112326027637736</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>masked_unfrozen_med_reg_24</t>
+          <t>lung_unfrozen_med_reg_24</t>
         </is>
       </c>
       <c r="B43" t="n">
@@ -2846,52 +2882,52 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>0.779938280582428</v>
+        <v>0.7515432039896647</v>
       </c>
       <c r="F43" t="n">
-        <v>0.7212534745534261</v>
+        <v>0.7065958976745605</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1108078807592392</v>
+        <v>0.1104106903076172</v>
       </c>
       <c r="H43" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6222222248713175</v>
       </c>
       <c r="I43" t="n">
-        <v>0.5454332232475281</v>
+        <v>0.4110016425450643</v>
       </c>
       <c r="J43" t="n">
-        <v>0.02417279762807992</v>
+        <v>0.02656110095530181</v>
       </c>
       <c r="K43" t="n">
-        <v>0.04139772608022362</v>
+        <v>0.02696144616643013</v>
       </c>
       <c r="L43" t="n">
-        <v>0.006992792258105583</v>
+        <v>0.005783183394275743</v>
       </c>
       <c r="M43" t="n">
-        <v>0.04138794527037967</v>
+        <v>0.04631481341638571</v>
       </c>
       <c r="N43" t="n">
-        <v>0.04375373816919498</v>
+        <v>0.09714666605188385</v>
       </c>
       <c r="O43" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6222222248713175</v>
       </c>
       <c r="P43" t="n">
-        <v>0.04138794527037967</v>
+        <v>0.04631481341638571</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.6631452043851217</v>
+        <v>0.6404226024945577</v>
       </c>
       <c r="R43" t="n">
-        <v>0.02760079309767969</v>
+        <v>0.026548026103587</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ws_unfrozen_med_reg_24</t>
+          <t>masked_unfrozen_med_reg_24</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -2904,46 +2940,46 @@
         <v>3</v>
       </c>
       <c r="E44" t="n">
-        <v>0.750308632850647</v>
+        <v>0.779938280582428</v>
       </c>
       <c r="F44" t="n">
-        <v>0.6972453991572062</v>
+        <v>0.7212534745534261</v>
       </c>
       <c r="G44" t="n">
-        <v>0.1102481509248416</v>
+        <v>0.1108078807592392</v>
       </c>
       <c r="H44" t="n">
-        <v>0.6472222010294596</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="I44" t="n">
-        <v>0.4727095564206441</v>
+        <v>0.5454332232475281</v>
       </c>
       <c r="J44" t="n">
-        <v>0.01026439158585974</v>
+        <v>0.02417279762807992</v>
       </c>
       <c r="K44" t="n">
-        <v>0.01590710472105708</v>
+        <v>0.04139772608022362</v>
       </c>
       <c r="L44" t="n">
-        <v>0.003657719155071491</v>
+        <v>0.006992792258105583</v>
       </c>
       <c r="M44" t="n">
-        <v>0.01712335590034907</v>
+        <v>0.04138794527037967</v>
       </c>
       <c r="N44" t="n">
-        <v>0.02269092807431733</v>
+        <v>0.04375373816919498</v>
       </c>
       <c r="O44" t="n">
-        <v>0.6472222010294596</v>
+        <v>0.7083333333333334</v>
       </c>
       <c r="P44" t="n">
-        <v>0.01712335590034907</v>
+        <v>0.04138794527037967</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.655231237411499</v>
+        <v>0.6631452043851217</v>
       </c>
       <c r="R44" t="n">
-        <v>0.03545959297481422</v>
+        <v>0.02760079309767969</v>
       </c>
     </row>
     <row r="45">
@@ -3007,7 +3043,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>lung_radio_frozen</t>
+          <t>compare</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -3020,52 +3056,52 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>0.5646605292956034</v>
+        <v>0.799999992052714</v>
       </c>
       <c r="F46" t="n">
-        <v>0.5592620571454366</v>
+        <v>0.7500632007916769</v>
       </c>
       <c r="G46" t="n">
-        <v>0.1267349819342295</v>
+        <v>0.1010366926590602</v>
       </c>
       <c r="H46" t="n">
-        <v>0.5222222208976746</v>
+        <v>0.7333333293596903</v>
       </c>
       <c r="I46" t="n">
-        <v>0.3726898034413655</v>
+        <v>0.5988456209500631</v>
       </c>
       <c r="J46" t="n">
-        <v>0.06943963216138521</v>
+        <v>0.03871948500772019</v>
       </c>
       <c r="K46" t="n">
-        <v>0.03796475431558221</v>
+        <v>0.04240371869329652</v>
       </c>
       <c r="L46" t="n">
-        <v>0.0004855356616961235</v>
+        <v>0.006485287615350145</v>
       </c>
       <c r="M46" t="n">
-        <v>0.03747426325259959</v>
+        <v>0.04461769750363983</v>
       </c>
       <c r="N46" t="n">
-        <v>0.03862246438014032</v>
+        <v>0.05854390040075846</v>
       </c>
       <c r="O46" t="n">
-        <v>0.5222222208976746</v>
+        <v>0.7333333293596903</v>
       </c>
       <c r="P46" t="n">
-        <v>0.03747426325259959</v>
+        <v>0.04461769750363983</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.5197017788887024</v>
+        <v>0.7456492582956949</v>
       </c>
       <c r="R46" t="n">
-        <v>0.03245576114304535</v>
+        <v>0.05651580495753514</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>lung_radio_unfrozen</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -3078,52 +3114,52 @@
         <v>3</v>
       </c>
       <c r="E47" t="n">
-        <v>0.582253078619639</v>
+        <v>0.5657407442728678</v>
       </c>
       <c r="F47" t="n">
-        <v>0.5772049427032471</v>
+        <v>0.5534495910008749</v>
       </c>
       <c r="G47" t="n">
-        <v>0.1265902022520701</v>
+        <v>0.1335071126619975</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5527777671813965</v>
+        <v>0.4694444437821706</v>
       </c>
       <c r="I47" t="n">
-        <v>0.2964392999807994</v>
+        <v>0.1411483238140742</v>
       </c>
       <c r="J47" t="n">
-        <v>0.01301429476918438</v>
+        <v>0.02960068956921679</v>
       </c>
       <c r="K47" t="n">
-        <v>0.02173070685657801</v>
+        <v>0.0186942060388321</v>
       </c>
       <c r="L47" t="n">
-        <v>0.01228707093973039</v>
+        <v>0.004079234160386625</v>
       </c>
       <c r="M47" t="n">
-        <v>0.01964186439892599</v>
+        <v>0.04827260907539483</v>
       </c>
       <c r="N47" t="n">
-        <v>0.02683911843699489</v>
+        <v>0.1323523713448295</v>
       </c>
       <c r="O47" t="n">
-        <v>0.5527777671813965</v>
+        <v>0.4694444437821706</v>
       </c>
       <c r="P47" t="n">
-        <v>0.01964186439892599</v>
+        <v>0.04827260907539483</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.5816750327746073</v>
+        <v>0.4356076121330261</v>
       </c>
       <c r="R47" t="n">
-        <v>0.04533517937991077</v>
+        <v>0.06892894485763129</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>masked_radio_frozen</t>
+          <t>multimodal</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -3136,52 +3172,52 @@
         <v>3</v>
       </c>
       <c r="E48" t="n">
-        <v>0.4987654089927673</v>
+        <v>0.7169753114382426</v>
       </c>
       <c r="F48" t="n">
-        <v>0.4964619576931</v>
+        <v>0.6848622759183248</v>
       </c>
       <c r="G48" t="n">
-        <v>0.135143925746282</v>
+        <v>0.118777222931385</v>
       </c>
       <c r="H48" t="n">
-        <v>0.4750000238418579</v>
+        <v>0.6166666348775228</v>
       </c>
       <c r="I48" t="n">
-        <v>0.3736263811588287</v>
+        <v>0.42036172747612</v>
       </c>
       <c r="J48" t="n">
-        <v>0.04364854072333719</v>
+        <v>0.07258270275081022</v>
       </c>
       <c r="K48" t="n">
-        <v>0.01793664925001662</v>
+        <v>0.05610422420679469</v>
       </c>
       <c r="L48" t="n">
-        <v>0.002920762179963498</v>
+        <v>0.01044314629910432</v>
       </c>
       <c r="M48" t="n">
-        <v>0</v>
+        <v>0.04138794527037967</v>
       </c>
       <c r="N48" t="n">
-        <v>0</v>
+        <v>0.06653859894337134</v>
       </c>
       <c r="O48" t="n">
-        <v>0.4750000238418579</v>
+        <v>0.6166666348775228</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>0.04138794527037967</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.4530516564846039</v>
+        <v>0.6358993649482727</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>0.0564584969409441</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>masked_radio_unfrozen</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -3194,52 +3230,52 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>0.5231481492519379</v>
+        <v>0.7018518249193827</v>
       </c>
       <c r="F49" t="n">
-        <v>0.4823098282019297</v>
+        <v>0.7043214639027914</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1288677702347437</v>
+        <v>0.1156958813468615</v>
       </c>
       <c r="H49" t="n">
-        <v>0.4833333492279053</v>
+        <v>0.6611110766728719</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2490842541058858</v>
+        <v>0.4991121292114258</v>
       </c>
       <c r="J49" t="n">
-        <v>0.03062562846201696</v>
+        <v>0.03725245786916991</v>
       </c>
       <c r="K49" t="n">
-        <v>0.03731317950051978</v>
+        <v>0.01236504407035012</v>
       </c>
       <c r="L49" t="n">
-        <v>0.004134124493627369</v>
+        <v>0.007024357886870683</v>
       </c>
       <c r="M49" t="n">
-        <v>0.01178510178061619</v>
+        <v>0.02576002680967757</v>
       </c>
       <c r="N49" t="n">
-        <v>0.176129165165065</v>
+        <v>0.02271484949679217</v>
       </c>
       <c r="O49" t="n">
-        <v>0.4833333492279053</v>
+        <v>0.6611110766728719</v>
       </c>
       <c r="P49" t="n">
-        <v>0.01178510178061619</v>
+        <v>0.02576002680967757</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.4270344376564026</v>
+        <v>0.6331106623013815</v>
       </c>
       <c r="R49" t="n">
-        <v>0.03679390372207091</v>
+        <v>0.01365818713970217</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ws_radio_frozen</t>
+          <t>multimodal</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -3252,52 +3288,52 @@
         <v>3</v>
       </c>
       <c r="E50" t="n">
-        <v>0.6061728398005167</v>
+        <v>0.7175925970077515</v>
       </c>
       <c r="F50" t="n">
-        <v>0.5936315457026163</v>
+        <v>0.6954763730367025</v>
       </c>
       <c r="G50" t="n">
-        <v>0.1242708389957746</v>
+        <v>0.1066700667142868</v>
       </c>
       <c r="H50" t="n">
-        <v>0.5861111283302307</v>
+        <v>0.6694444417953491</v>
       </c>
       <c r="I50" t="n">
-        <v>0.4216248492399852</v>
+        <v>0.5017684698104858</v>
       </c>
       <c r="J50" t="n">
-        <v>0.0520187809289429</v>
+        <v>0.04267972909240782</v>
       </c>
       <c r="K50" t="n">
-        <v>0.02796602883009606</v>
+        <v>0.05076148698912605</v>
       </c>
       <c r="L50" t="n">
-        <v>0.002620993199262494</v>
+        <v>0.008602235476116436</v>
       </c>
       <c r="M50" t="n">
-        <v>0.02576005466145912</v>
+        <v>0.05152010932291824</v>
       </c>
       <c r="N50" t="n">
-        <v>0.02483285144258953</v>
+        <v>0.06698495284174283</v>
       </c>
       <c r="O50" t="n">
-        <v>0.5861111283302307</v>
+        <v>0.6694444417953491</v>
       </c>
       <c r="P50" t="n">
-        <v>0.02576005466145912</v>
+        <v>0.05152010932291824</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.5647678772608439</v>
+        <v>0.6471394697825114</v>
       </c>
       <c r="R50" t="n">
-        <v>0.01940908164067787</v>
+        <v>0.04014487764849362</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ws_radio_unfrozen</t>
+          <t>preclinical</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -3310,52 +3346,52 @@
         <v>3</v>
       </c>
       <c r="E51" t="n">
-        <v>0.5993827184041342</v>
+        <v>0.7018518249193827</v>
       </c>
       <c r="F51" t="n">
-        <v>0.5718979040781657</v>
+        <v>0.7043214639027914</v>
       </c>
       <c r="G51" t="n">
-        <v>0.1262166673938433</v>
+        <v>0.1156958813468615</v>
       </c>
       <c r="H51" t="n">
-        <v>0.575000007947286</v>
+        <v>0.6611110766728719</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3978034754594167</v>
+        <v>0.4991121292114258</v>
       </c>
       <c r="J51" t="n">
-        <v>0.02264682721450439</v>
+        <v>0.03725245786916991</v>
       </c>
       <c r="K51" t="n">
-        <v>0.01030885992897227</v>
+        <v>0.01236504407035012</v>
       </c>
       <c r="L51" t="n">
-        <v>0.001969844602953353</v>
+        <v>0.007024357886870683</v>
       </c>
       <c r="M51" t="n">
-        <v>0.01800205872188277</v>
+        <v>0.02576002680967757</v>
       </c>
       <c r="N51" t="n">
-        <v>0.03545061676519656</v>
+        <v>0.02271484949679217</v>
       </c>
       <c r="O51" t="n">
-        <v>0.575000007947286</v>
+        <v>0.6611110766728719</v>
       </c>
       <c r="P51" t="n">
-        <v>0.01800205872188277</v>
+        <v>0.02576002680967757</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.5580615599950155</v>
+        <v>0.6331106623013815</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01112326027637736</v>
+        <v>0.01365818713970217</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>lung_unfrozen_med_reg_24</t>
+          <t>afterdiagnosis</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -3368,52 +3404,52 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>0.7515432039896647</v>
+        <v>0.7018518249193827</v>
       </c>
       <c r="F52" t="n">
-        <v>0.7065958976745605</v>
+        <v>0.7043214639027914</v>
       </c>
       <c r="G52" t="n">
-        <v>0.1104106903076172</v>
+        <v>0.1156958813468615</v>
       </c>
       <c r="H52" t="n">
-        <v>0.6222222248713175</v>
+        <v>0.6611110766728719</v>
       </c>
       <c r="I52" t="n">
-        <v>0.4110016425450643</v>
+        <v>0.4991121292114258</v>
       </c>
       <c r="J52" t="n">
-        <v>0.02656110095530181</v>
+        <v>0.03725245786916991</v>
       </c>
       <c r="K52" t="n">
-        <v>0.02696144616643013</v>
+        <v>0.01236504407035012</v>
       </c>
       <c r="L52" t="n">
-        <v>0.005783183394275743</v>
+        <v>0.007024357886870683</v>
       </c>
       <c r="M52" t="n">
-        <v>0.04631481341638571</v>
+        <v>0.02576002680967757</v>
       </c>
       <c r="N52" t="n">
-        <v>0.09714666605188385</v>
+        <v>0.02271484949679217</v>
       </c>
       <c r="O52" t="n">
-        <v>0.6222222248713175</v>
+        <v>0.6611110766728719</v>
       </c>
       <c r="P52" t="n">
-        <v>0.04631481341638571</v>
+        <v>0.02576002680967757</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.6404226024945577</v>
+        <v>0.6331106623013815</v>
       </c>
       <c r="R52" t="n">
-        <v>0.026548026103587</v>
+        <v>0.01365818713970217</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>masked_unfrozen_med_reg_24</t>
+          <t>full_information</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -3426,52 +3462,52 @@
         <v>3</v>
       </c>
       <c r="E53" t="n">
-        <v>0.779938280582428</v>
+        <v>0.7018518249193827</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7212534745534261</v>
+        <v>0.7043214639027914</v>
       </c>
       <c r="G53" t="n">
-        <v>0.1108078807592392</v>
+        <v>0.1156958813468615</v>
       </c>
       <c r="H53" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6611110766728719</v>
       </c>
       <c r="I53" t="n">
-        <v>0.5454332232475281</v>
+        <v>0.4991121292114258</v>
       </c>
       <c r="J53" t="n">
-        <v>0.02417279762807992</v>
+        <v>0.03725245786916991</v>
       </c>
       <c r="K53" t="n">
-        <v>0.04139772608022362</v>
+        <v>0.01236504407035012</v>
       </c>
       <c r="L53" t="n">
-        <v>0.006992792258105583</v>
+        <v>0.007024357886870683</v>
       </c>
       <c r="M53" t="n">
-        <v>0.04138794527037967</v>
+        <v>0.02576002680967757</v>
       </c>
       <c r="N53" t="n">
-        <v>0.04375373816919498</v>
+        <v>0.02271484949679217</v>
       </c>
       <c r="O53" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6611110766728719</v>
       </c>
       <c r="P53" t="n">
-        <v>0.04138794527037967</v>
+        <v>0.02576002680967757</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.6631452043851217</v>
+        <v>0.6331106623013815</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02760079309767969</v>
+        <v>0.01365818713970217</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ws_unfrozen_med_reg_24</t>
+          <t>preclinical</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -3484,46 +3520,1670 @@
         <v>3</v>
       </c>
       <c r="E54" t="n">
-        <v>0.750308632850647</v>
+        <v>0.7018518249193827</v>
       </c>
       <c r="F54" t="n">
-        <v>0.6972453991572062</v>
+        <v>0.7043214639027914</v>
       </c>
       <c r="G54" t="n">
-        <v>0.1102481509248416</v>
+        <v>0.1156958813468615</v>
       </c>
       <c r="H54" t="n">
-        <v>0.6472222010294596</v>
+        <v>0.6611110766728719</v>
       </c>
       <c r="I54" t="n">
-        <v>0.4727095564206441</v>
+        <v>0.4991121292114258</v>
       </c>
       <c r="J54" t="n">
-        <v>0.01026439158585974</v>
+        <v>0.03725245786916991</v>
       </c>
       <c r="K54" t="n">
-        <v>0.01590710472105708</v>
+        <v>0.01236504407035012</v>
       </c>
       <c r="L54" t="n">
-        <v>0.003657719155071491</v>
+        <v>0.007024357886870683</v>
       </c>
       <c r="M54" t="n">
+        <v>0.02576002680967757</v>
+      </c>
+      <c r="N54" t="n">
+        <v>0.02271484949679217</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0.6611110766728719</v>
+      </c>
+      <c r="P54" t="n">
+        <v>0.02576002680967757</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>0.6331106623013815</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0.01365818713970217</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>afterdiagnosis</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C55" t="n">
+        <v>22</v>
+      </c>
+      <c r="D55" t="n">
+        <v>3</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.8317901293436686</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.8132423758506775</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0.09302877138058345</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.7472222248713175</v>
+      </c>
+      <c r="I55" t="n">
+        <v>0.60503222544988</v>
+      </c>
+      <c r="J55" t="n">
+        <v>0.02730388211210475</v>
+      </c>
+      <c r="K55" t="n">
+        <v>0.01392924918327228</v>
+      </c>
+      <c r="L55" t="n">
+        <v>0.0008837493809184164</v>
+      </c>
+      <c r="M55" t="n">
+        <v>0.0501540819562726</v>
+      </c>
+      <c r="N55" t="n">
+        <v>0.06575198976962711</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0.7472222248713175</v>
+      </c>
+      <c r="P55" t="n">
+        <v>0.0501540819562726</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.7106180191040039</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.04436113289559018</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>full_information</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C56" t="n">
+        <v>22</v>
+      </c>
+      <c r="D56" t="n">
+        <v>3</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.935802499453227</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.89259539047877</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.06989602496226628</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0.8805555502573649</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0.7692080537478129</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0.005572658655639164</v>
+      </c>
+      <c r="K56" t="n">
+        <v>0.01363735088178001</v>
+      </c>
+      <c r="L56" t="n">
+        <v>0.004191057105724293</v>
+      </c>
+      <c r="M56" t="n">
+        <v>0.01416392958552454</v>
+      </c>
+      <c r="N56" t="n">
+        <v>0.01716494275681022</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0.8805555502573649</v>
+      </c>
+      <c r="P56" t="n">
+        <v>0.01416392958552454</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0.8154445091883341</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0.01123694784910104</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>top_10_preclinical</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C57" t="n">
+        <v>22</v>
+      </c>
+      <c r="D57" t="n">
+        <v>3</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.6796296437581381</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.6628759106000265</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0.1185119772950808</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0.6277777751286825</v>
+      </c>
+      <c r="I57" t="n">
+        <v>0.4563494424025218</v>
+      </c>
+      <c r="J57" t="n">
+        <v>0.02499428306195467</v>
+      </c>
+      <c r="K57" t="n">
+        <v>0.02647620840746739</v>
+      </c>
+      <c r="L57" t="n">
+        <v>0.002521963044963608</v>
+      </c>
+      <c r="M57" t="n">
+        <v>0.01039348282903164</v>
+      </c>
+      <c r="N57" t="n">
+        <v>0.01591946477559731</v>
+      </c>
+      <c r="O57" t="n">
+        <v>0.6277777751286825</v>
+      </c>
+      <c r="P57" t="n">
+        <v>0.01039348282903164</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.6009632349014282</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.005258692579715008</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>concat_preclinical</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C58" t="n">
+        <v>22</v>
+      </c>
+      <c r="D58" t="n">
+        <v>3</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.6521604458491007</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.649734656016032</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0.1176550736029943</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.6027777989705404</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0.4020467797915141</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0.03660498429824183</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0.030652777280975</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0.001461029907767851</v>
+      </c>
+      <c r="M58" t="n">
         <v>0.01712335590034907</v>
       </c>
-      <c r="N54" t="n">
-        <v>0.02269092807431733</v>
-      </c>
-      <c r="O54" t="n">
-        <v>0.6472222010294596</v>
-      </c>
-      <c r="P54" t="n">
+      <c r="N58" t="n">
+        <v>0.05119046248759551</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0.6027777989705404</v>
+      </c>
+      <c r="P58" t="n">
         <v>0.01712335590034907</v>
       </c>
-      <c r="Q54" t="n">
-        <v>0.655231237411499</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0.03545959297481422</v>
+      <c r="Q58" t="n">
+        <v>0.6065183480580648</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.02614780329723496</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>concat_afterdiagnosis</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C59" t="n">
+        <v>22</v>
+      </c>
+      <c r="D59" t="n">
+        <v>3</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.851234515508016</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.832448800404867</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0.08991438895463943</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.694444457689921</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0.5437266627947489</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0.01374066916882353</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0.01205117114823</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0.00280024692922228</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0.02389535058159446</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0.03894682538007912</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0.694444457689921</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0.02389535058159446</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.7276108264923096</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.02981974036652465</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>concat_full_information</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C60" t="n">
+        <v>22</v>
+      </c>
+      <c r="D60" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.9481481313705444</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.896638870239258</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0.06433018048604329</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.8666666348775228</v>
+      </c>
+      <c r="I60" t="n">
+        <v>0.7855569918950399</v>
+      </c>
+      <c r="J60" t="n">
+        <v>0.0170899635792661</v>
+      </c>
+      <c r="K60" t="n">
+        <v>0.01161945756969</v>
+      </c>
+      <c r="L60" t="n">
+        <v>0.01056657627582428</v>
+      </c>
+      <c r="M60" t="n">
+        <v>0.05569427166238675</v>
+      </c>
+      <c r="N60" t="n">
+        <v>0.06029642210423249</v>
+      </c>
+      <c r="O60" t="n">
+        <v>0.8666666348775228</v>
+      </c>
+      <c r="P60" t="n">
+        <v>0.05569427166238675</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.8527359962463379</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.01882708618980631</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>top10_preclinical</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C61" t="n">
+        <v>22</v>
+      </c>
+      <c r="D61" t="n">
+        <v>3</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.6796296437581381</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.662875910600027</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0.1185119772950808</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0.6277777751286825</v>
+      </c>
+      <c r="I61" t="n">
+        <v>0.4563494424025218</v>
+      </c>
+      <c r="J61" t="n">
+        <v>0.02499428306195467</v>
+      </c>
+      <c r="K61" t="n">
+        <v>0.02647620840746739</v>
+      </c>
+      <c r="L61" t="n">
+        <v>0.002521963044963608</v>
+      </c>
+      <c r="M61" t="n">
+        <v>0.01039348282903164</v>
+      </c>
+      <c r="N61" t="n">
+        <v>0.01591946477559731</v>
+      </c>
+      <c r="O61" t="n">
+        <v>0.6277777751286825</v>
+      </c>
+      <c r="P61" t="n">
+        <v>0.01039348282903164</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.6009632349014282</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.005258692579715008</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>top10_afterdiagnosis</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C62" t="n">
+        <v>22</v>
+      </c>
+      <c r="D62" t="n">
+        <v>3</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.845370352268219</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.821329275767008</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0.08659801880518596</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.6349206566810608</v>
+      </c>
+      <c r="J62" t="n">
+        <v>0.0374132089371915</v>
+      </c>
+      <c r="K62" t="n">
+        <v>0.040857350676302</v>
+      </c>
+      <c r="L62" t="n">
+        <v>0.007232978746397981</v>
+      </c>
+      <c r="M62" t="n">
+        <v>0.04138794527037967</v>
+      </c>
+      <c r="N62" t="n">
+        <v>0.04489566597077454</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0.7916666666666666</v>
+      </c>
+      <c r="P62" t="n">
+        <v>0.04138794527037967</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.7216211160024008</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.03172842995302576</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>top10_full_information</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C63" t="n">
+        <v>22</v>
+      </c>
+      <c r="D63" t="n">
+        <v>3</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.911419689655304</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.874652524789174</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0.07187414169311523</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.8888888756434122</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.7715966900189718</v>
+      </c>
+      <c r="J63" t="n">
+        <v>0.02096952557558691</v>
+      </c>
+      <c r="K63" t="n">
+        <v>0.020775090238849</v>
+      </c>
+      <c r="L63" t="n">
+        <v>0.006144555501610594</v>
+      </c>
+      <c r="M63" t="n">
+        <v>0.01712335590034907</v>
+      </c>
+      <c r="N63" t="n">
+        <v>0.03185822401351295</v>
+      </c>
+      <c r="O63" t="n">
+        <v>0.8888888756434122</v>
+      </c>
+      <c r="P63" t="n">
+        <v>0.01712335590034907</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.8155528505643209</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.02289970628700663</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>multi_preclinical</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C64" t="n">
+        <v>22</v>
+      </c>
+      <c r="D64" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.6941358248392741</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.685367703437805</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0.1095799406369527</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.6361110806465149</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.4634725749492645</v>
+      </c>
+      <c r="J64" t="n">
+        <v>0.00387957648555436</v>
+      </c>
+      <c r="K64" t="n">
+        <v>0.003765414222334</v>
+      </c>
+      <c r="L64" t="n">
+        <v>0.0008418924959250069</v>
+      </c>
+      <c r="M64" t="n">
+        <v>0.04530416812354012</v>
+      </c>
+      <c r="N64" t="n">
+        <v>0.05322897496608538</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0.6361110806465149</v>
+      </c>
+      <c r="P64" t="n">
+        <v>0.04530416812354012</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.611373762289683</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.03762011370266357</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>multi_afterdiagnosis</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C65" t="n">
+        <v>22</v>
+      </c>
+      <c r="D65" t="n">
+        <v>3</v>
+      </c>
+      <c r="E65" t="n">
+        <v>0.8540123303731283</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.831943392753601</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0.08642075955867767</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.7611111203829447</v>
+      </c>
+      <c r="I65" t="n">
+        <v>0.6211080153783163</v>
+      </c>
+      <c r="J65" t="n">
+        <v>0.01443044373058052</v>
+      </c>
+      <c r="K65" t="n">
+        <v>0.016451828856431</v>
+      </c>
+      <c r="L65" t="n">
+        <v>0.006254339057347812</v>
+      </c>
+      <c r="M65" t="n">
+        <v>0.0554164955414844</v>
+      </c>
+      <c r="N65" t="n">
+        <v>0.06582409189912801</v>
+      </c>
+      <c r="O65" t="n">
+        <v>0.7611111203829447</v>
+      </c>
+      <c r="P65" t="n">
+        <v>0.0554164955414844</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0.7444340189297994</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.01000636959259894</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>multi_full_information</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C66" t="n">
+        <v>22</v>
+      </c>
+      <c r="D66" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.9197530746459961</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.87945411602656</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0.07385217646757762</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.8083333373069763</v>
+      </c>
+      <c r="I66" t="n">
+        <v>0.7179382642110189</v>
+      </c>
+      <c r="J66" t="n">
+        <v>0.02207170143291048</v>
+      </c>
+      <c r="K66" t="n">
+        <v>0.012426881672972</v>
+      </c>
+      <c r="L66" t="n">
+        <v>0.008636260472083221</v>
+      </c>
+      <c r="M66" t="n">
+        <v>0.03402070709431814</v>
+      </c>
+      <c r="N66" t="n">
+        <v>0.05214313467528363</v>
+      </c>
+      <c r="O66" t="n">
+        <v>0.8083333373069763</v>
+      </c>
+      <c r="P66" t="n">
+        <v>0.03402070709431814</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>0.8236904541651408</v>
+      </c>
+      <c r="R66" t="n">
+        <v>0.03922935157531927</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>multi_preclinical</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C67" t="n">
+        <v>22</v>
+      </c>
+      <c r="D67" t="n">
+        <v>3</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.7512345512708029</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.7220116257667542</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0.1063749492168427</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.6527777711550394</v>
+      </c>
+      <c r="I67" t="n">
+        <v>0.4741267263889313</v>
+      </c>
+      <c r="J67" t="n">
+        <v>0.04988742657071263</v>
+      </c>
+      <c r="K67" t="n">
+        <v>0.04559137051153241</v>
+      </c>
+      <c r="L67" t="n">
+        <v>0.00621956463948731</v>
+      </c>
+      <c r="M67" t="n">
+        <v>0.0554164955414844</v>
+      </c>
+      <c r="N67" t="n">
+        <v>0.08183041921616445</v>
+      </c>
+      <c r="O67" t="n">
+        <v>0.6527777711550394</v>
+      </c>
+      <c r="P67" t="n">
+        <v>0.0554164955414844</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>0.6330611705780029</v>
+      </c>
+      <c r="R67" t="n">
+        <v>0.03932005167897431</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>multi_afterdiagnosis</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C68" t="n">
+        <v>22</v>
+      </c>
+      <c r="D68" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.7287036776542664</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.7098812262217203</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0.1106418371200562</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.6416666905085245</v>
+      </c>
+      <c r="I68" t="n">
+        <v>0.464814821879069</v>
+      </c>
+      <c r="J68" t="n">
+        <v>0.04209311955544119</v>
+      </c>
+      <c r="K68" t="n">
+        <v>0.02949539316871806</v>
+      </c>
+      <c r="L68" t="n">
+        <v>0.006274919888555584</v>
+      </c>
+      <c r="M68" t="n">
+        <v>0.04461772719022646</v>
+      </c>
+      <c r="N68" t="n">
+        <v>0.06290847612988194</v>
+      </c>
+      <c r="O68" t="n">
+        <v>0.6416666905085245</v>
+      </c>
+      <c r="P68" t="n">
+        <v>0.04461772719022646</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>0.6454166968663534</v>
+      </c>
+      <c r="R68" t="n">
+        <v>0.04958508262701199</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>multi_full_information</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C69" t="n">
+        <v>22</v>
+      </c>
+      <c r="D69" t="n">
+        <v>3</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.7370370427767435</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.7058377663294474</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0.1135951429605484</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.6222222447395325</v>
+      </c>
+      <c r="I69" t="n">
+        <v>0.4192192256450653</v>
+      </c>
+      <c r="J69" t="n">
+        <v>0.06416338476750581</v>
+      </c>
+      <c r="K69" t="n">
+        <v>0.07193508069192826</v>
+      </c>
+      <c r="L69" t="n">
+        <v>0.00992522211996668</v>
+      </c>
+      <c r="M69" t="n">
+        <v>0.05457469595477504</v>
+      </c>
+      <c r="N69" t="n">
+        <v>0.08640304658090184</v>
+      </c>
+      <c r="O69" t="n">
+        <v>0.6222222447395325</v>
+      </c>
+      <c r="P69" t="n">
+        <v>0.05457469595477504</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0.6442107558250427</v>
+      </c>
+      <c r="R69" t="n">
+        <v>0.05733476336399203</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>multi_preclinical_e-5</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>1e-05</v>
+      </c>
+      <c r="C70" t="n">
+        <v>22</v>
+      </c>
+      <c r="D70" t="n">
+        <v>3</v>
+      </c>
+      <c r="E70" t="n">
+        <v>0.6925925811131796</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.6712155739466349</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0.1210001508394877</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0.569444457689921</v>
+      </c>
+      <c r="I70" t="n">
+        <v>0.3425925970077515</v>
+      </c>
+      <c r="J70" t="n">
+        <v>0.02905496045134185</v>
+      </c>
+      <c r="K70" t="n">
+        <v>0.0142421094062406</v>
+      </c>
+      <c r="L70" t="n">
+        <v>0.004062613795302412</v>
+      </c>
+      <c r="M70" t="n">
+        <v>0.03986860103736582</v>
+      </c>
+      <c r="N70" t="n">
+        <v>0.07965116090652802</v>
+      </c>
+      <c r="O70" t="n">
+        <v>0.569444457689921</v>
+      </c>
+      <c r="P70" t="n">
+        <v>0.03986860103736582</v>
+      </c>
+      <c r="Q70" t="n">
+        <v>0.5683775146802267</v>
+      </c>
+      <c r="R70" t="n">
+        <v>0.02880027709289949</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>multi_tab_clinical</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C71" t="n">
+        <v>22</v>
+      </c>
+      <c r="D71" t="n">
+        <v>3</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.6675925652186075</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.6456911762555441</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0.1369505127271017</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0.5805555582046509</v>
+      </c>
+      <c r="I71" t="n">
+        <v>0.3587132692337036</v>
+      </c>
+      <c r="J71" t="n">
+        <v>0.07066619656240486</v>
+      </c>
+      <c r="K71" t="n">
+        <v>0.04665481710120005</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.008687240933261875</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.03868995764163432</v>
+      </c>
+      <c r="N71" t="n">
+        <v>0.06830460330554404</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0.5805555582046509</v>
+      </c>
+      <c r="P71" t="n">
+        <v>0.03868995764163432</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0.6023876070976257</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0.04774613509449457</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>multi_tab_afterdiagnosis</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C72" t="n">
+        <v>22</v>
+      </c>
+      <c r="D72" t="n">
+        <v>3</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.7472222248713175</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.709375778834025</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0.1095965653657913</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.6666666467984518</v>
+      </c>
+      <c r="I72" t="n">
+        <v>0.5006929934024811</v>
+      </c>
+      <c r="J72" t="n">
+        <v>0.03369999990208236</v>
+      </c>
+      <c r="K72" t="n">
+        <v>0.03365784197993441</v>
+      </c>
+      <c r="L72" t="n">
+        <v>0.004939846145852769</v>
+      </c>
+      <c r="M72" t="n">
+        <v>0.02041241938989685</v>
+      </c>
+      <c r="N72" t="n">
+        <v>0.0322561751865104</v>
+      </c>
+      <c r="O72" t="n">
+        <v>0.6666666467984518</v>
+      </c>
+      <c r="P72" t="n">
+        <v>0.02041241938989685</v>
+      </c>
+      <c r="Q72" t="n">
+        <v>0.6855810681978861</v>
+      </c>
+      <c r="R72" t="n">
+        <v>0.0286304818249801</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>multi_tab_clinical</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C73" t="n">
+        <v>22</v>
+      </c>
+      <c r="D73" t="n">
+        <v>3</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.7358024517695109</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.6967399517695109</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0.1200171783566475</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0.6166666547457377</v>
+      </c>
+      <c r="I73" t="n">
+        <v>0.4128881891568502</v>
+      </c>
+      <c r="J73" t="n">
+        <v>0.05488450300690534</v>
+      </c>
+      <c r="K73" t="n">
+        <v>0.04473727374454729</v>
+      </c>
+      <c r="L73" t="n">
+        <v>0.004475676647804342</v>
+      </c>
+      <c r="M73" t="n">
+        <v>0.02965855032792139</v>
+      </c>
+      <c r="N73" t="n">
+        <v>0.06392086866593683</v>
+      </c>
+      <c r="O73" t="n">
+        <v>0.6166666547457377</v>
+      </c>
+      <c r="P73" t="n">
+        <v>0.02965855032792139</v>
+      </c>
+      <c r="Q73" t="n">
+        <v>0.6281009515126547</v>
+      </c>
+      <c r="R73" t="n">
+        <v>0.01313746755009773</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>multi_tab_afterdiagnosis</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C74" t="n">
+        <v>22</v>
+      </c>
+      <c r="D74" t="n">
+        <v>3</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.6919753154118856</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0.1199673563241959</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.6222222248713175</v>
+      </c>
+      <c r="I74" t="n">
+        <v>0.4278532067934672</v>
+      </c>
+      <c r="J74" t="n">
+        <v>0.03009219043157539</v>
+      </c>
+      <c r="K74" t="n">
+        <v>0.02410500102707477</v>
+      </c>
+      <c r="L74" t="n">
+        <v>0.004882721894399043</v>
+      </c>
+      <c r="M74" t="n">
+        <v>0.04101340671934498</v>
+      </c>
+      <c r="N74" t="n">
+        <v>0.06382941390756608</v>
+      </c>
+      <c r="O74" t="n">
+        <v>0.6222222248713175</v>
+      </c>
+      <c r="P74" t="n">
+        <v>0.04101340671934498</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0.6367863416671753</v>
+      </c>
+      <c r="R74" t="n">
+        <v>0.04353320095644261</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>multi_tab_full_information</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C75" t="n">
+        <v>22</v>
+      </c>
+      <c r="D75" t="n">
+        <v>3</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.7743826905886332</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.7265605330467224</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0.1162096038460732</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.6555555462837219</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.4683186809221904</v>
+      </c>
+      <c r="J75" t="n">
+        <v>0.02789415783760969</v>
+      </c>
+      <c r="K75" t="n">
+        <v>0.02633838880105135</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.01008813926077326</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.07147045070655243</v>
+      </c>
+      <c r="N75" t="n">
+        <v>0.1200634785197399</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0.6555555462837219</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0.07147045070655243</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0.6575312813123068</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0.05036916693012583</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>tab_preclinical</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C76" t="n">
+        <v>22</v>
+      </c>
+      <c r="D76" t="n">
+        <v>3</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.709876557191213</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.6714682976404825</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0.1209295044342677</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.502777765194575</v>
+      </c>
+      <c r="I76" t="n">
+        <v>0.08231883992751439</v>
+      </c>
+      <c r="J76" t="n">
+        <v>0.01699495024256513</v>
+      </c>
+      <c r="K76" t="n">
+        <v>0.02912937425761127</v>
+      </c>
+      <c r="L76" t="n">
+        <v>0.0004737936446113057</v>
+      </c>
+      <c r="M76" t="n">
+        <v>0.02078697893307328</v>
+      </c>
+      <c r="N76" t="n">
+        <v>0.06540199178722554</v>
+      </c>
+      <c r="O76" t="n">
+        <v>0.502777765194575</v>
+      </c>
+      <c r="P76" t="n">
+        <v>0.02078697893307328</v>
+      </c>
+      <c r="Q76" t="n">
+        <v>0.4978066285451253</v>
+      </c>
+      <c r="R76" t="n">
+        <v>0.09151655161265683</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>tab_afterdiagnosis</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C77" t="n">
+        <v>22</v>
+      </c>
+      <c r="D77" t="n">
+        <v>3</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.8287036816279093</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.7872125307718912</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0.1054519166549047</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0.5916666587193807</v>
+      </c>
+      <c r="I77" t="n">
+        <v>0.3312440663576126</v>
+      </c>
+      <c r="J77" t="n">
+        <v>0.007920102504937885</v>
+      </c>
+      <c r="K77" t="n">
+        <v>0.006390777757801492</v>
+      </c>
+      <c r="L77" t="n">
+        <v>0.0006695753189390991</v>
+      </c>
+      <c r="M77" t="n">
+        <v>0.04249181603191683</v>
+      </c>
+      <c r="N77" t="n">
+        <v>0.09942471196290645</v>
+      </c>
+      <c r="O77" t="n">
+        <v>0.5916666587193807</v>
+      </c>
+      <c r="P77" t="n">
+        <v>0.04249181603191683</v>
+      </c>
+      <c r="Q77" t="n">
+        <v>0.6894677678743998</v>
+      </c>
+      <c r="R77" t="n">
+        <v>0.05069506281368039</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>tab_full_information</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C78" t="n">
+        <v>22</v>
+      </c>
+      <c r="D78" t="n">
+        <v>3</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.8728394707043966</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.7952994704246521</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0.09486502160628636</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0.7083333134651184</v>
+      </c>
+      <c r="I78" t="n">
+        <v>0.5489165584246317</v>
+      </c>
+      <c r="J78" t="n">
+        <v>0.005146075021080628</v>
+      </c>
+      <c r="K78" t="n">
+        <v>0.006521840242339773</v>
+      </c>
+      <c r="L78" t="n">
+        <v>0.009201009630659925</v>
+      </c>
+      <c r="M78" t="n">
+        <v>0.07200824408467908</v>
+      </c>
+      <c r="N78" t="n">
+        <v>0.09673676536974546</v>
+      </c>
+      <c r="O78" t="n">
+        <v>0.7083333134651184</v>
+      </c>
+      <c r="P78" t="n">
+        <v>0.07200824408467908</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0.7326412995656332</v>
+      </c>
+      <c r="R78" t="n">
+        <v>0.0186604029259421</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>multi_tab_preclinical</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C79" t="n">
+        <v>22</v>
+      </c>
+      <c r="D79" t="n">
+        <v>3</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.6444444457689921</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.6333080530166626</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0.130621112883091</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.5805555582046509</v>
+      </c>
+      <c r="I79" t="n">
+        <v>0.2814814845720927</v>
+      </c>
+      <c r="J79" t="n">
+        <v>0.0151203223753127</v>
+      </c>
+      <c r="K79" t="n">
+        <v>0.006790524989921566</v>
+      </c>
+      <c r="L79" t="n">
+        <v>0.006539771672149623</v>
+      </c>
+      <c r="M79" t="n">
+        <v>0.05786851861604943</v>
+      </c>
+      <c r="N79" t="n">
+        <v>0.1998627807927345</v>
+      </c>
+      <c r="O79" t="n">
+        <v>0.5805555582046509</v>
+      </c>
+      <c r="P79" t="n">
+        <v>0.05786851861604943</v>
+      </c>
+      <c r="Q79" t="n">
+        <v>0.5548611084620158</v>
+      </c>
+      <c r="R79" t="n">
+        <v>0.1275246570843699</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>multi_tab_afterdiagnosis</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C80" t="n">
+        <v>22</v>
+      </c>
+      <c r="D80" t="n">
+        <v>3</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.755864143371582</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.7169572909673055</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0.117992527782917</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0.5888888835906982</v>
+      </c>
+      <c r="I80" t="n">
+        <v>0.299182911713918</v>
+      </c>
+      <c r="J80" t="n">
+        <v>0.02544005055806658</v>
+      </c>
+      <c r="K80" t="n">
+        <v>0.02375266715158017</v>
+      </c>
+      <c r="L80" t="n">
+        <v>0.009440909177274814</v>
+      </c>
+      <c r="M80" t="n">
+        <v>0.06322114378112367</v>
+      </c>
+      <c r="N80" t="n">
+        <v>0.2119746360582592</v>
+      </c>
+      <c r="O80" t="n">
+        <v>0.5888888835906982</v>
+      </c>
+      <c r="P80" t="n">
+        <v>0.06322114378112367</v>
+      </c>
+      <c r="Q80" t="n">
+        <v>0.5482426683108012</v>
+      </c>
+      <c r="R80" t="n">
+        <v>0.1225743953061023</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>multi_tab_full_information</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C81" t="n">
+        <v>22</v>
+      </c>
+      <c r="D81" t="n">
+        <v>3</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.766357958316803</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.7407126426696777</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0.1120431149999301</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0.6194444497426351</v>
+      </c>
+      <c r="I81" t="n">
+        <v>0.3694617028037707</v>
+      </c>
+      <c r="J81" t="n">
+        <v>0.02154753841843343</v>
+      </c>
+      <c r="K81" t="n">
+        <v>0.007903202944492456</v>
+      </c>
+      <c r="L81" t="n">
+        <v>0.007803693681788834</v>
+      </c>
+      <c r="M81" t="n">
+        <v>0.08561687619324791</v>
+      </c>
+      <c r="N81" t="n">
+        <v>0.2058204866292003</v>
+      </c>
+      <c r="O81" t="n">
+        <v>0.6194444497426351</v>
+      </c>
+      <c r="P81" t="n">
+        <v>0.08561687619324791</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0.6267950336138407</v>
+      </c>
+      <c r="R81" t="n">
+        <v>0.06567524429238983</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Image_ws</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C82" t="n">
+        <v>22</v>
+      </c>
+      <c r="D82" t="n">
+        <v>3</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.799999992052714</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.7500632007916769</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0.1010366926590602</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.7333333293596903</v>
+      </c>
+      <c r="I82" t="n">
+        <v>0.5988456209500631</v>
+      </c>
+      <c r="J82" t="n">
+        <v>0.03871948500772019</v>
+      </c>
+      <c r="K82" t="n">
+        <v>0.04240371869329652</v>
+      </c>
+      <c r="L82" t="n">
+        <v>0.006485287615350145</v>
+      </c>
+      <c r="M82" t="n">
+        <v>0.04461769750363983</v>
+      </c>
+      <c r="N82" t="n">
+        <v>0.05854390040075846</v>
+      </c>
+      <c r="O82" t="n">
+        <v>0.7333333293596903</v>
+      </c>
+      <c r="P82" t="n">
+        <v>0.04461769750363983</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>0.7456492582956949</v>
+      </c>
+      <c r="R82" t="n">
+        <v>0.05651580495753514</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments_Summary.xlsx
+++ b/Experiments_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R82"/>
+  <dimension ref="A1:R91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5186,6 +5186,528 @@
         <v>0.05651580495753514</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>tab_pre_resn</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C83" t="n">
+        <v>22</v>
+      </c>
+      <c r="D83" t="n">
+        <v>3</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.6033950448036194</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.5870609283447266</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0.1176031132539113</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I83" t="n">
+        <v>0</v>
+      </c>
+      <c r="J83" t="n">
+        <v>0.0008729876735452817</v>
+      </c>
+      <c r="K83" t="n">
+        <v>0.008934879003218469</v>
+      </c>
+      <c r="L83" t="n">
+        <v>0.001255213362286689</v>
+      </c>
+      <c r="M83" t="n">
+        <v>0</v>
+      </c>
+      <c r="N83" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P83" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="R83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>tab_pre_resn</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C84" t="n">
+        <v>22</v>
+      </c>
+      <c r="D84" t="n">
+        <v>3</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.709876557191213</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.6717210213343302</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0.1209424510598183</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0.502777765194575</v>
+      </c>
+      <c r="I84" t="n">
+        <v>0.08231883992751439</v>
+      </c>
+      <c r="J84" t="n">
+        <v>0.01699495024256513</v>
+      </c>
+      <c r="K84" t="n">
+        <v>0.02889602969154902</v>
+      </c>
+      <c r="L84" t="n">
+        <v>0.000471021447613563</v>
+      </c>
+      <c r="M84" t="n">
+        <v>0.02078697893307328</v>
+      </c>
+      <c r="N84" t="n">
+        <v>0.06540199178722554</v>
+      </c>
+      <c r="O84" t="n">
+        <v>0.502777765194575</v>
+      </c>
+      <c r="P84" t="n">
+        <v>0.02078697893307328</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>0.4978066285451253</v>
+      </c>
+      <c r="R84" t="n">
+        <v>0.09151655161265683</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>tab_pre_resn</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C85" t="n">
+        <v>22</v>
+      </c>
+      <c r="D85" t="n">
+        <v>3</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.6992284059524536</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.6877684990564982</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0.1216342250506083</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0.4944444398085276</v>
+      </c>
+      <c r="I85" t="n">
+        <v>0.05676328639189402</v>
+      </c>
+      <c r="J85" t="n">
+        <v>0.01840373757560653</v>
+      </c>
+      <c r="K85" t="n">
+        <v>0.01829098897489592</v>
+      </c>
+      <c r="L85" t="n">
+        <v>0.003392353664551395</v>
+      </c>
+      <c r="M85" t="n">
+        <v>0.01416394322319628</v>
+      </c>
+      <c r="N85" t="n">
+        <v>0.0401649505871076</v>
+      </c>
+      <c r="O85" t="n">
+        <v>0.4944444398085276</v>
+      </c>
+      <c r="P85" t="n">
+        <v>0.01416394322319628</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0.4711399674415588</v>
+      </c>
+      <c r="R85" t="n">
+        <v>0.07357891121034246</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>tab_pre_128_64</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C86" t="n">
+        <v>22</v>
+      </c>
+      <c r="D86" t="n">
+        <v>3</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.6916666626930237</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.673490027586619</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0.1223395243287086</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.4944444398085276</v>
+      </c>
+      <c r="I86" t="n">
+        <v>0.05676328639189402</v>
+      </c>
+      <c r="J86" t="n">
+        <v>0.04124963054908527</v>
+      </c>
+      <c r="K86" t="n">
+        <v>0.0349864460899716</v>
+      </c>
+      <c r="L86" t="n">
+        <v>0.0009858471260710778</v>
+      </c>
+      <c r="M86" t="n">
+        <v>0.01416394322319628</v>
+      </c>
+      <c r="N86" t="n">
+        <v>0.0401649505871076</v>
+      </c>
+      <c r="O86" t="n">
+        <v>0.4944444398085276</v>
+      </c>
+      <c r="P86" t="n">
+        <v>0.01416394322319628</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0.4711399674415588</v>
+      </c>
+      <c r="R86" t="n">
+        <v>0.07357891121034246</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>tab_afterdiagnosis</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C87" t="n">
+        <v>22</v>
+      </c>
+      <c r="D87" t="n">
+        <v>3</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.8013888597488403</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.7791256109873453</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0.1069254254301389</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0.5916666587193807</v>
+      </c>
+      <c r="I87" t="n">
+        <v>0.3312440663576126</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.01264491137200896</v>
+      </c>
+      <c r="K87" t="n">
+        <v>0.01119536412657434</v>
+      </c>
+      <c r="L87" t="n">
+        <v>0.003018286538069441</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0.04249181603191683</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0.09942471196290645</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0.5916666587193807</v>
+      </c>
+      <c r="P87" t="n">
+        <v>0.04249181603191683</v>
+      </c>
+      <c r="Q87" t="n">
+        <v>0.6894677678743998</v>
+      </c>
+      <c r="R87" t="n">
+        <v>0.05069506281368039</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>tab_full_information</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C88" t="n">
+        <v>22</v>
+      </c>
+      <c r="D88" t="n">
+        <v>3</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.8563271562258402</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.8209502100944519</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0.09375821302334468</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0.7333333293596903</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0.5939394036928812</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0.02841936840030329</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0.02445417238144693</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0.007556646869239699</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0.05443312648421197</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0.07435057336681122</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0.7333333293596903</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0.05443312648421197</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0.732167661190033</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0.02962769103852985</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>pre_CoOp</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C89" t="n">
+        <v>22</v>
+      </c>
+      <c r="D89" t="n">
+        <v>3</v>
+      </c>
+      <c r="E89" t="n">
+        <v>0.7614197333653768</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0.7359110514322916</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0.1084280560413996</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.6361111203829447</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0.453561266263326</v>
+      </c>
+      <c r="J89" t="n">
+        <v>0.06307331560651415</v>
+      </c>
+      <c r="K89" t="n">
+        <v>0.02471718409125153</v>
+      </c>
+      <c r="L89" t="n">
+        <v>0.00325371845366385</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0.06983225186975574</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0.1076184230971922</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0.6361111203829447</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0.06983225186975574</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>0.6323418815930685</v>
+      </c>
+      <c r="R89" t="n">
+        <v>0.07056928534311084</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>ad_CoOp</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C90" t="n">
+        <v>22</v>
+      </c>
+      <c r="D90" t="n">
+        <v>3</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.8030864199002584</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0.788223405679067</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0.09749501943588257</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.6916666626930237</v>
+      </c>
+      <c r="I90" t="n">
+        <v>0.5209097564220428</v>
+      </c>
+      <c r="J90" t="n">
+        <v>0.02908776323609105</v>
+      </c>
+      <c r="K90" t="n">
+        <v>0.02235648612694575</v>
+      </c>
+      <c r="L90" t="n">
+        <v>0.006887580660721673</v>
+      </c>
+      <c r="M90" t="n">
+        <v>0.04906533859619368</v>
+      </c>
+      <c r="N90" t="n">
+        <v>0.07770960592794864</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0.6916666626930237</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0.04906533859619368</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>0.7040334343910217</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.02453009805722536</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>FI_CoOp</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C91" t="n">
+        <v>22</v>
+      </c>
+      <c r="D91" t="n">
+        <v>3</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.9429012338320414</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0.8888046542803446</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0.07449456428488095</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.7944444219271342</v>
+      </c>
+      <c r="I91" t="n">
+        <v>0.7100529273351034</v>
+      </c>
+      <c r="J91" t="n">
+        <v>0.01259016958928738</v>
+      </c>
+      <c r="K91" t="n">
+        <v>0.01804049610859226</v>
+      </c>
+      <c r="L91" t="n">
+        <v>0.01003749337308951</v>
+      </c>
+      <c r="M91" t="n">
+        <v>0.02749859891933678</v>
+      </c>
+      <c r="N91" t="n">
+        <v>0.04851594794990716</v>
+      </c>
+      <c r="O91" t="n">
+        <v>0.7944444219271342</v>
+      </c>
+      <c r="P91" t="n">
+        <v>0.02749859891933678</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0.8379382491111755</v>
+      </c>
+      <c r="R91" t="n">
+        <v>0.04323375905162748</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Experiments_Summary.xlsx
+++ b/Experiments_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R91"/>
+  <dimension ref="A1:R117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -887,7 +887,7 @@
         <v>0.799999992052714</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7500632007916769</v>
+        <v>0.750063200791677</v>
       </c>
       <c r="G8" t="n">
         <v>0.1010366926590602</v>
@@ -3752,7 +3752,7 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>0.6521604458491007</v>
+        <v>0.652160445849101</v>
       </c>
       <c r="F58" t="n">
         <v>0.649734656016032</v>
@@ -3868,7 +3868,7 @@
         <v>3</v>
       </c>
       <c r="E60" t="n">
-        <v>0.9481481313705444</v>
+        <v>0.948148131370544</v>
       </c>
       <c r="F60" t="n">
         <v>0.896638870239258</v>
@@ -4158,7 +4158,7 @@
         <v>3</v>
       </c>
       <c r="E65" t="n">
-        <v>0.8540123303731283</v>
+        <v>0.854012330373128</v>
       </c>
       <c r="F65" t="n">
         <v>0.831943392753601</v>
@@ -4216,7 +4216,7 @@
         <v>3</v>
       </c>
       <c r="E66" t="n">
-        <v>0.9197530746459961</v>
+        <v>0.919753074645996</v>
       </c>
       <c r="F66" t="n">
         <v>0.87945411602656</v>
@@ -5706,6 +5706,1514 @@
       </c>
       <c r="R91" t="n">
         <v>0.04323375905162748</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>pre_CoOp</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C92" t="n">
+        <v>22</v>
+      </c>
+      <c r="D92" t="n">
+        <v>3</v>
+      </c>
+      <c r="E92" t="n">
+        <v>0.7271604935328165</v>
+      </c>
+      <c r="F92" t="n">
+        <v>0.7141774098078409</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0.1039891963203748</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.6083333293596903</v>
+      </c>
+      <c r="I92" t="n">
+        <v>0.4259574413299561</v>
+      </c>
+      <c r="J92" t="n">
+        <v>0.04379890738578462</v>
+      </c>
+      <c r="K92" t="n">
+        <v>0.01427793922164154</v>
+      </c>
+      <c r="L92" t="n">
+        <v>0.002862160304320834</v>
+      </c>
+      <c r="M92" t="n">
+        <v>0.07103729257576374</v>
+      </c>
+      <c r="N92" t="n">
+        <v>0.09093714315943806</v>
+      </c>
+      <c r="O92" t="n">
+        <v>0.6083333293596903</v>
+      </c>
+      <c r="P92" t="n">
+        <v>0.07103729257576374</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0.5919325550397238</v>
+      </c>
+      <c r="R92" t="n">
+        <v>0.06120548340203817</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>ad_CoOp</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C93" t="n">
+        <v>22</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3</v>
+      </c>
+      <c r="E93" t="n">
+        <v>0.8083333373069763</v>
+      </c>
+      <c r="F93" t="n">
+        <v>0.7841799457867941</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0.09675302108128865</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.7333333293596903</v>
+      </c>
+      <c r="I93" t="n">
+        <v>0.5835600892702738</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.008418635274313489</v>
+      </c>
+      <c r="K93" t="n">
+        <v>0.001288615771151459</v>
+      </c>
+      <c r="L93" t="n">
+        <v>0.004742441070154052</v>
+      </c>
+      <c r="M93" t="n">
+        <v>0.04762899479874634</v>
+      </c>
+      <c r="N93" t="n">
+        <v>0.05665507444919343</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0.7333333293596903</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0.04762899479874634</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0.7147795756657919</v>
+      </c>
+      <c r="R93" t="n">
+        <v>0.01810625476685216</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>see_Image_baseline</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C94" t="n">
+        <v>22</v>
+      </c>
+      <c r="D94" t="n">
+        <v>3</v>
+      </c>
+      <c r="E94" t="n">
+        <v>0.7543209592501322</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0.7247914870580038</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0.1118485157688459</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0.6861111124356588</v>
+      </c>
+      <c r="I94" t="n">
+        <v>0.5313005248705546</v>
+      </c>
+      <c r="J94" t="n">
+        <v>0.02393518175128641</v>
+      </c>
+      <c r="K94" t="n">
+        <v>0.01146454045086145</v>
+      </c>
+      <c r="L94" t="n">
+        <v>0.005149910841333673</v>
+      </c>
+      <c r="M94" t="n">
+        <v>0.007856734520410793</v>
+      </c>
+      <c r="N94" t="n">
+        <v>0.01306732130391361</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0.6861111124356588</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0.007856734520410793</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>0.7035652796427408</v>
+      </c>
+      <c r="R94" t="n">
+        <v>0.01582119638561543</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>see_Image_baseline</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C95" t="n">
+        <v>22</v>
+      </c>
+      <c r="D95" t="n">
+        <v>3</v>
+      </c>
+      <c r="E95" t="n">
+        <v>0.6712963183720907</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0.665655791759491</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0.1282205482323965</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0.5166666706403097</v>
+      </c>
+      <c r="I95" t="n">
+        <v>0.124761904279391</v>
+      </c>
+      <c r="J95" t="n">
+        <v>0.04134651670082449</v>
+      </c>
+      <c r="K95" t="n">
+        <v>0.04256908324660434</v>
+      </c>
+      <c r="L95" t="n">
+        <v>0.009349192353431148</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0.01800205872188277</v>
+      </c>
+      <c r="N95" t="n">
+        <v>0.09096110677387681</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0.5166666706403097</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0.01800205872188277</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0.5076207121213278</v>
+      </c>
+      <c r="R95" t="n">
+        <v>0.09499362880770693</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>match_baseline</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C96" t="n">
+        <v>22</v>
+      </c>
+      <c r="D96" t="n">
+        <v>3</v>
+      </c>
+      <c r="E96" t="n">
+        <v>0.796913584073385</v>
+      </c>
+      <c r="F96" t="n">
+        <v>0.7591609756151835</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0.1081615785757701</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0.5972222487131754</v>
+      </c>
+      <c r="I96" t="n">
+        <v>0.2968254089355469</v>
+      </c>
+      <c r="J96" t="n">
+        <v>0.04290902192186398</v>
+      </c>
+      <c r="K96" t="n">
+        <v>0.03067984098640803</v>
+      </c>
+      <c r="L96" t="n">
+        <v>0.007566640229399261</v>
+      </c>
+      <c r="M96" t="n">
+        <v>0.07827226045491056</v>
+      </c>
+      <c r="N96" t="n">
+        <v>0.2218704805626614</v>
+      </c>
+      <c r="O96" t="n">
+        <v>0.5972222487131754</v>
+      </c>
+      <c r="P96" t="n">
+        <v>0.07827226045491056</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0.583535373210907</v>
+      </c>
+      <c r="R96" t="n">
+        <v>0.1484065254011023</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>match_baseline_return</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C97" t="n">
+        <v>22</v>
+      </c>
+      <c r="D97" t="n">
+        <v>3</v>
+      </c>
+      <c r="E97" t="n">
+        <v>0.7493826945622762</v>
+      </c>
+      <c r="F97" t="n">
+        <v>0.7081122001012167</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0.1135660782456398</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="I97" t="n">
+        <v>0.5022982259591421</v>
+      </c>
+      <c r="J97" t="n">
+        <v>0.02999704888011242</v>
+      </c>
+      <c r="K97" t="n">
+        <v>0.02831329605691882</v>
+      </c>
+      <c r="L97" t="n">
+        <v>0.009637442777040638</v>
+      </c>
+      <c r="M97" t="n">
+        <v>0.03788385436344015</v>
+      </c>
+      <c r="N97" t="n">
+        <v>0.05122465674329838</v>
+      </c>
+      <c r="O97" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="P97" t="n">
+        <v>0.03788385436344015</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0.6608619689941406</v>
+      </c>
+      <c r="R97" t="n">
+        <v>0.04338741584450634</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>match_baseline_returnP=0.5</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C98" t="n">
+        <v>22</v>
+      </c>
+      <c r="D98" t="n">
+        <v>3</v>
+      </c>
+      <c r="E98" t="n">
+        <v>0.794444461663564</v>
+      </c>
+      <c r="F98" t="n">
+        <v>0.745261569817861</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0.102765813469887</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.722222248713175</v>
+      </c>
+      <c r="I98" t="n">
+        <v>0.5860305825869242</v>
+      </c>
+      <c r="J98" t="n">
+        <v>0.0207181076124321</v>
+      </c>
+      <c r="K98" t="n">
+        <v>0.01746491577653433</v>
+      </c>
+      <c r="L98" t="n">
+        <v>0.00506271653945393</v>
+      </c>
+      <c r="M98" t="n">
+        <v>0.007856734520410793</v>
+      </c>
+      <c r="N98" t="n">
+        <v>0.005126155402093149</v>
+      </c>
+      <c r="O98" t="n">
+        <v>0.7222222487131754</v>
+      </c>
+      <c r="P98" t="n">
+        <v>0.007856734520410793</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0.7408978541692098</v>
+      </c>
+      <c r="R98" t="n">
+        <v>0.03034497385943204</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C99" t="n">
+        <v>22</v>
+      </c>
+      <c r="D99" t="n">
+        <v>3</v>
+      </c>
+      <c r="E99" t="n">
+        <v>0.6537037293116251</v>
+      </c>
+      <c r="F99" t="n">
+        <v>0.6378569602966309</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0.1194086323181788</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.5361111164093018</v>
+      </c>
+      <c r="I99" t="n">
+        <v>0.2468694150447845</v>
+      </c>
+      <c r="J99" t="n">
+        <v>0.06444782232783053</v>
+      </c>
+      <c r="K99" t="n">
+        <v>0.04365055837106078</v>
+      </c>
+      <c r="L99" t="n">
+        <v>0.006634336032179559</v>
+      </c>
+      <c r="M99" t="n">
+        <v>0.01964186439892599</v>
+      </c>
+      <c r="N99" t="n">
+        <v>0.02276909733816156</v>
+      </c>
+      <c r="O99" t="n">
+        <v>0.5361111164093018</v>
+      </c>
+      <c r="P99" t="n">
+        <v>0.01964186439892599</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0.5926326910654703</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0.06010758751431648</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C100" t="n">
+        <v>22</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3</v>
+      </c>
+      <c r="E100" t="n">
+        <v>0.8620369831720988</v>
+      </c>
+      <c r="F100" t="n">
+        <v>0.8309325178464254</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0.08912100394566853</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.7305555740992228</v>
+      </c>
+      <c r="I100" t="n">
+        <v>0.595167895158132</v>
+      </c>
+      <c r="J100" t="n">
+        <v>0.0007560173355705599</v>
+      </c>
+      <c r="K100" t="n">
+        <v>0.007298219986008177</v>
+      </c>
+      <c r="L100" t="n">
+        <v>0.003799691040853169</v>
+      </c>
+      <c r="M100" t="n">
+        <v>0.003928367260205397</v>
+      </c>
+      <c r="N100" t="n">
+        <v>0.003733442640877693</v>
+      </c>
+      <c r="O100" t="n">
+        <v>0.7305555740992228</v>
+      </c>
+      <c r="P100" t="n">
+        <v>0.003928367260205397</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0.731255849202474</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.01792827326992585</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>preclinical</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C101" t="n">
+        <v>22</v>
+      </c>
+      <c r="D101" t="n">
+        <v>3</v>
+      </c>
+      <c r="E101" t="n">
+        <v>0.6537037293116251</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0.6378569602966309</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0.1194086323181788</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.5361111164093018</v>
+      </c>
+      <c r="I101" t="n">
+        <v>0.2468694150447845</v>
+      </c>
+      <c r="J101" t="n">
+        <v>0.06444782232783053</v>
+      </c>
+      <c r="K101" t="n">
+        <v>0.04365055837106078</v>
+      </c>
+      <c r="L101" t="n">
+        <v>0.006634336032179559</v>
+      </c>
+      <c r="M101" t="n">
+        <v>0.01964186439892599</v>
+      </c>
+      <c r="N101" t="n">
+        <v>0.02276909733816156</v>
+      </c>
+      <c r="O101" t="n">
+        <v>0.5361111164093018</v>
+      </c>
+      <c r="P101" t="n">
+        <v>0.01964186439892599</v>
+      </c>
+      <c r="Q101" t="n">
+        <v>0.5926326910654703</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.06010758751431648</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>afterdiagnosis</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C102" t="n">
+        <v>22</v>
+      </c>
+      <c r="D102" t="n">
+        <v>3</v>
+      </c>
+      <c r="E102" t="n">
+        <v>0.8620369831720988</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0.8309325178464254</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0.08912100394566853</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0.7305555740992228</v>
+      </c>
+      <c r="I102" t="n">
+        <v>0.595167895158132</v>
+      </c>
+      <c r="J102" t="n">
+        <v>0.0007560173355705599</v>
+      </c>
+      <c r="K102" t="n">
+        <v>0.007298219986008177</v>
+      </c>
+      <c r="L102" t="n">
+        <v>0.003799691040853169</v>
+      </c>
+      <c r="M102" t="n">
+        <v>0.003928367260205397</v>
+      </c>
+      <c r="N102" t="n">
+        <v>0.003733442640877693</v>
+      </c>
+      <c r="O102" t="n">
+        <v>0.7305555740992228</v>
+      </c>
+      <c r="P102" t="n">
+        <v>0.003928367260205397</v>
+      </c>
+      <c r="Q102" t="n">
+        <v>0.731255849202474</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.01792827326992585</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>fullinformation</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C103" t="n">
+        <v>22</v>
+      </c>
+      <c r="D103" t="n">
+        <v>3</v>
+      </c>
+      <c r="E103" t="n">
+        <v>0.9527777632077535</v>
+      </c>
+      <c r="F103" t="n">
+        <v>0.9082638422648112</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0.06045951694250107</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.8861111005147299</v>
+      </c>
+      <c r="I103" t="n">
+        <v>0.7965039610862732</v>
+      </c>
+      <c r="J103" t="n">
+        <v>0.004721311160787947</v>
+      </c>
+      <c r="K103" t="n">
+        <v>0.006282441169508703</v>
+      </c>
+      <c r="L103" t="n">
+        <v>0.0003903475149894043</v>
+      </c>
+      <c r="M103" t="n">
+        <v>0.02187222323547982</v>
+      </c>
+      <c r="N103" t="n">
+        <v>0.02216752297962848</v>
+      </c>
+      <c r="O103" t="n">
+        <v>0.8861111005147299</v>
+      </c>
+      <c r="P103" t="n">
+        <v>0.02187222323547982</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0.8422519167264303</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.01175603153386143</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>preclinical</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C104" t="n">
+        <v>22</v>
+      </c>
+      <c r="D104" t="n">
+        <v>3</v>
+      </c>
+      <c r="E104" t="n">
+        <v>0.633024712403615</v>
+      </c>
+      <c r="F104" t="n">
+        <v>0.6345716516176859</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0.1220587939023972</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0.5388888915379842</v>
+      </c>
+      <c r="I104" t="n">
+        <v>0.2571598043044408</v>
+      </c>
+      <c r="J104" t="n">
+        <v>0.02383946176410684</v>
+      </c>
+      <c r="K104" t="n">
+        <v>0.02431599940818758</v>
+      </c>
+      <c r="L104" t="n">
+        <v>0.006479194973625087</v>
+      </c>
+      <c r="M104" t="n">
+        <v>0.0554164955414844</v>
+      </c>
+      <c r="N104" t="n">
+        <v>0.1312662042046276</v>
+      </c>
+      <c r="O104" t="n">
+        <v>0.5388888915379842</v>
+      </c>
+      <c r="P104" t="n">
+        <v>0.0554164955414844</v>
+      </c>
+      <c r="Q104" t="n">
+        <v>0.5302863816420237</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.04610789895390428</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>afterdiagnosis</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C105" t="n">
+        <v>22</v>
+      </c>
+      <c r="D105" t="n">
+        <v>3</v>
+      </c>
+      <c r="E105" t="n">
+        <v>0.8617284099260966</v>
+      </c>
+      <c r="F105" t="n">
+        <v>0.8291635115941366</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0.08465183029572169</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.7861110965410868</v>
+      </c>
+      <c r="I105" t="n">
+        <v>0.6565656661987305</v>
+      </c>
+      <c r="J105" t="n">
+        <v>0.006859900117492283</v>
+      </c>
+      <c r="K105" t="n">
+        <v>0.009872142969452361</v>
+      </c>
+      <c r="L105" t="n">
+        <v>0.002351730716503672</v>
+      </c>
+      <c r="M105" t="n">
+        <v>0.0171233816847532</v>
+      </c>
+      <c r="N105" t="n">
+        <v>0.01428499995319136</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0.7861110965410868</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0.0171233816847532</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>0.7493780652681986</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0.01228302606188206</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>fullinformation</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C106" t="n">
+        <v>22</v>
+      </c>
+      <c r="D106" t="n">
+        <v>3</v>
+      </c>
+      <c r="E106" t="n">
+        <v>0.9608024756113688</v>
+      </c>
+      <c r="F106" t="n">
+        <v>0.9214051167170206</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0.05509461214145025</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0.9166666269302368</v>
+      </c>
+      <c r="I106" t="n">
+        <v>0.8260869383811951</v>
+      </c>
+      <c r="J106" t="n">
+        <v>0.006429816009790161</v>
+      </c>
+      <c r="K106" t="n">
+        <v>0.007690220105856583</v>
+      </c>
+      <c r="L106" t="n">
+        <v>0.00263128649748886</v>
+      </c>
+      <c r="M106" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="n">
+        <v>0.9166666269302368</v>
+      </c>
+      <c r="P106" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q106" t="n">
+        <v>0.8561253547668457</v>
+      </c>
+      <c r="R106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Image</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C107" t="n">
+        <v>22</v>
+      </c>
+      <c r="D107" t="n">
+        <v>3</v>
+      </c>
+      <c r="E107" t="n">
+        <v>0.794444461663564</v>
+      </c>
+      <c r="F107" t="n">
+        <v>0.745261569817861</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0.1027658134698868</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.7222222487131754</v>
+      </c>
+      <c r="I107" t="n">
+        <v>0.5860305825869242</v>
+      </c>
+      <c r="J107" t="n">
+        <v>0.0207181076124321</v>
+      </c>
+      <c r="K107" t="n">
+        <v>0.01746491577653433</v>
+      </c>
+      <c r="L107" t="n">
+        <v>0.00506271653945393</v>
+      </c>
+      <c r="M107" t="n">
+        <v>0.007856734520410793</v>
+      </c>
+      <c r="N107" t="n">
+        <v>0.005126155402093149</v>
+      </c>
+      <c r="O107" t="n">
+        <v>0.7222222487131754</v>
+      </c>
+      <c r="P107" t="n">
+        <v>0.007856734520410793</v>
+      </c>
+      <c r="Q107" t="n">
+        <v>0.7408978541692098</v>
+      </c>
+      <c r="R107" t="n">
+        <v>0.03034497385943204</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>preclinical</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C108" t="n">
+        <v>22</v>
+      </c>
+      <c r="D108" t="n">
+        <v>3</v>
+      </c>
+      <c r="E108" t="n">
+        <v>0.6388888756434122</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0.6317917704582214</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0.1347640827298164</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0.5194444259007772</v>
+      </c>
+      <c r="I108" t="n">
+        <v>0.2130232652028402</v>
+      </c>
+      <c r="J108" t="n">
+        <v>0.01834799120400695</v>
+      </c>
+      <c r="K108" t="n">
+        <v>0.02157141652651975</v>
+      </c>
+      <c r="L108" t="n">
+        <v>0.02075320389901747</v>
+      </c>
+      <c r="M108" t="n">
+        <v>0.02187222323547982</v>
+      </c>
+      <c r="N108" t="n">
+        <v>0.1542111307951697</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0.5194444259007772</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0.02187222323547982</v>
+      </c>
+      <c r="Q108" t="n">
+        <v>0.4742092291514079</v>
+      </c>
+      <c r="R108" t="n">
+        <v>0.07138554373540211</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>preclinical</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C109" t="n">
+        <v>22</v>
+      </c>
+      <c r="D109" t="n">
+        <v>3</v>
+      </c>
+      <c r="E109" t="n">
+        <v>0.6388888557751974</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0.6214303771654764</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0.1188214023907979</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="I109" t="n">
+        <v>0.2629445840915044</v>
+      </c>
+      <c r="J109" t="n">
+        <v>0.01387860026965727</v>
+      </c>
+      <c r="K109" t="n">
+        <v>0.02215852659379937</v>
+      </c>
+      <c r="L109" t="n">
+        <v>0.003471834382339399</v>
+      </c>
+      <c r="M109" t="n">
+        <v>0.006804156018974732</v>
+      </c>
+      <c r="N109" t="n">
+        <v>0.02847322226031639</v>
+      </c>
+      <c r="O109" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="P109" t="n">
+        <v>0.006804156018974732</v>
+      </c>
+      <c r="Q109" t="n">
+        <v>0.5781148672103882</v>
+      </c>
+      <c r="R109" t="n">
+        <v>0.04245189735119193</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>afterdiagnosis</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C110" t="n">
+        <v>22</v>
+      </c>
+      <c r="D110" t="n">
+        <v>3</v>
+      </c>
+      <c r="E110" t="n">
+        <v>0.8648147781689962</v>
+      </c>
+      <c r="F110" t="n">
+        <v>0.8327015240987142</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0.08130829532941182</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0.819444457689921</v>
+      </c>
+      <c r="I110" t="n">
+        <v>0.6871223847071329</v>
+      </c>
+      <c r="J110" t="n">
+        <v>0.03032556968182725</v>
+      </c>
+      <c r="K110" t="n">
+        <v>0.02699932529883946</v>
+      </c>
+      <c r="L110" t="n">
+        <v>0.006424428648573273</v>
+      </c>
+      <c r="M110" t="n">
+        <v>0.0257600825132412</v>
+      </c>
+      <c r="N110" t="n">
+        <v>0.04111647933410563</v>
+      </c>
+      <c r="O110" t="n">
+        <v>0.819444457689921</v>
+      </c>
+      <c r="P110" t="n">
+        <v>0.0257600825132412</v>
+      </c>
+      <c r="Q110" t="n">
+        <v>0.7595431804656982</v>
+      </c>
+      <c r="R110" t="n">
+        <v>0.03019185147198399</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>preclinical_CTCLIP</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C111" t="n">
+        <v>22</v>
+      </c>
+      <c r="D111" t="n">
+        <v>3</v>
+      </c>
+      <c r="E111" t="n">
+        <v>0.6388888557751971</v>
+      </c>
+      <c r="F111" t="n">
+        <v>0.621430377165476</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0.1188214023907979</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="I111" t="n">
+        <v>0.2629445840915044</v>
+      </c>
+      <c r="J111" t="n">
+        <v>0.01387860026965727</v>
+      </c>
+      <c r="K111" t="n">
+        <v>0.02215852659379937</v>
+      </c>
+      <c r="L111" t="n">
+        <v>0.003471834382339399</v>
+      </c>
+      <c r="M111" t="n">
+        <v>0.006804156018974732</v>
+      </c>
+      <c r="N111" t="n">
+        <v>0.02847322226031639</v>
+      </c>
+      <c r="O111" t="n">
+        <v>0.5416666666666666</v>
+      </c>
+      <c r="P111" t="n">
+        <v>0.006804156018974732</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>0.5781148672103882</v>
+      </c>
+      <c r="R111" t="n">
+        <v>0.04245189735119193</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>afterdiagnosis_CTCLIP</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C112" t="n">
+        <v>22</v>
+      </c>
+      <c r="D112" t="n">
+        <v>3</v>
+      </c>
+      <c r="E112" t="n">
+        <v>0.864814778168996</v>
+      </c>
+      <c r="F112" t="n">
+        <v>0.832701524098714</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0.08130829532941182</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.819444457689921</v>
+      </c>
+      <c r="I112" t="n">
+        <v>0.6871223847071329</v>
+      </c>
+      <c r="J112" t="n">
+        <v>0.03032556968182725</v>
+      </c>
+      <c r="K112" t="n">
+        <v>0.02699932529883946</v>
+      </c>
+      <c r="L112" t="n">
+        <v>0.006424428648573273</v>
+      </c>
+      <c r="M112" t="n">
+        <v>0.0257600825132412</v>
+      </c>
+      <c r="N112" t="n">
+        <v>0.04111647933410563</v>
+      </c>
+      <c r="O112" t="n">
+        <v>0.819444457689921</v>
+      </c>
+      <c r="P112" t="n">
+        <v>0.0257600825132412</v>
+      </c>
+      <c r="Q112" t="n">
+        <v>0.7595431804656982</v>
+      </c>
+      <c r="R112" t="n">
+        <v>0.03019185147198399</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>fullinformation_CTCLIP</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C113" t="n">
+        <v>22</v>
+      </c>
+      <c r="D113" t="n">
+        <v>3</v>
+      </c>
+      <c r="E113" t="n">
+        <v>0.964506149291992</v>
+      </c>
+      <c r="F113" t="n">
+        <v>0.912560025850932</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0.05982691049575806</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0.8500000039736429</v>
+      </c>
+      <c r="I113" t="n">
+        <v>0.7794277866681417</v>
+      </c>
+      <c r="J113" t="n">
+        <v>0.008762400404379126</v>
+      </c>
+      <c r="K113" t="n">
+        <v>0.01094001433428774</v>
+      </c>
+      <c r="L113" t="n">
+        <v>0.003324855261258421</v>
+      </c>
+      <c r="M113" t="n">
+        <v>0.03118047503711526</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0.04347542945344824</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0.8500000039736429</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0.03118047503711526</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>0.8604120413462321</v>
+      </c>
+      <c r="R113" t="n">
+        <v>0.03357979512793006</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Multi_prec_CTCLIP</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C114" t="n">
+        <v>22</v>
+      </c>
+      <c r="D114" t="n">
+        <v>3</v>
+      </c>
+      <c r="E114" t="n">
+        <v>0.719135800997416</v>
+      </c>
+      <c r="F114" t="n">
+        <v>0.689916590849559</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0.11240121225516</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0.624999980131785</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0.4398204882939656</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0.04121730568205791</v>
+      </c>
+      <c r="K114" t="n">
+        <v>0.03095135311960703</v>
+      </c>
+      <c r="L114" t="n">
+        <v>0.005571248426331015</v>
+      </c>
+      <c r="M114" t="n">
+        <v>0.03535533343974757</v>
+      </c>
+      <c r="N114" t="n">
+        <v>0.04789055078121116</v>
+      </c>
+      <c r="O114" t="n">
+        <v>0.624999980131785</v>
+      </c>
+      <c r="P114" t="n">
+        <v>0.03535533343974757</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0.6304101546605428</v>
+      </c>
+      <c r="R114" t="n">
+        <v>0.04367110333624002</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>multi_ad_CTCLIP</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C115" t="n">
+        <v>22</v>
+      </c>
+      <c r="D115" t="n">
+        <v>3</v>
+      </c>
+      <c r="E115" t="n">
+        <v>0.816357990105947</v>
+      </c>
+      <c r="F115" t="n">
+        <v>0.77862016359965</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0.09700256586074829</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0.7305555740992228</v>
+      </c>
+      <c r="I115" t="n">
+        <v>0.5848134358723959</v>
+      </c>
+      <c r="J115" t="n">
+        <v>0.05091935927117046</v>
+      </c>
+      <c r="K115" t="n">
+        <v>0.03158857436526307</v>
+      </c>
+      <c r="L115" t="n">
+        <v>0.008512600664356437</v>
+      </c>
+      <c r="M115" t="n">
+        <v>0.02187222323547982</v>
+      </c>
+      <c r="N115" t="n">
+        <v>0.02517820070439423</v>
+      </c>
+      <c r="O115" t="n">
+        <v>0.7305555740992228</v>
+      </c>
+      <c r="P115" t="n">
+        <v>0.02187222323547982</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0.7054436008135477</v>
+      </c>
+      <c r="R115" t="n">
+        <v>0.005920755329285242</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>multi_fi_CTCLIP</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C116" t="n">
+        <v>22</v>
+      </c>
+      <c r="D116" t="n">
+        <v>3</v>
+      </c>
+      <c r="E116" t="n">
+        <v>0.935185134410858</v>
+      </c>
+      <c r="F116" t="n">
+        <v>0.87237807114919</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.07027052839597066</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0.8305555582046509</v>
+      </c>
+      <c r="I116" t="n">
+        <v>0.7286324898401896</v>
+      </c>
+      <c r="J116" t="n">
+        <v>0.02475302680396097</v>
+      </c>
+      <c r="K116" t="n">
+        <v>0.02540526931575507</v>
+      </c>
+      <c r="L116" t="n">
+        <v>0.007202527369445301</v>
+      </c>
+      <c r="M116" t="n">
+        <v>0.03491614569275737</v>
+      </c>
+      <c r="N116" t="n">
+        <v>0.0445142399539349</v>
+      </c>
+      <c r="O116" t="n">
+        <v>0.8305555582046509</v>
+      </c>
+      <c r="P116" t="n">
+        <v>0.03491614569275737</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>0.8074695666631063</v>
+      </c>
+      <c r="R116" t="n">
+        <v>0.03583267613861628</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Image_only</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C117" t="n">
+        <v>22</v>
+      </c>
+      <c r="D117" t="n">
+        <v>3</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.7944444616635641</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.745261569817861</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.1027658134698868</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.7222222487131754</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.5860305825869242</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.0207181076124321</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.01746491577653433</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.00506271653945393</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.007856734520410793</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.005126155402093149</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.7222222487131754</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.007856734520410793</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.7408978541692098</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.03034497385943204</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments_Summary.xlsx
+++ b/Experiments_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R117"/>
+  <dimension ref="A1:T129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,6 +519,16 @@
           <t>Std_Test_precision</t>
         </is>
       </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Avg_Test_td_auc</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>std_Test_td_auc</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -577,6 +587,8 @@
       <c r="R2" t="n">
         <v>0.0485919095517561</v>
       </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -635,6 +647,8 @@
       <c r="R3" t="n">
         <v>0.05271970781422992</v>
       </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -693,6 +707,8 @@
       <c r="R4" t="n">
         <v>0.04799526486346187</v>
       </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -751,6 +767,8 @@
       <c r="R5" t="n">
         <v>0.02966688568351711</v>
       </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -809,6 +827,8 @@
       <c r="R6" t="n">
         <v>0.05241903603056015</v>
       </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -867,6 +887,8 @@
       <c r="R7" t="n">
         <v>0.01718248205627023</v>
       </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -925,6 +947,8 @@
       <c r="R8" t="n">
         <v>0.05651580495753514</v>
       </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -983,6 +1007,8 @@
       <c r="R9" t="n">
         <v>0.04353825330072314</v>
       </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1041,6 +1067,8 @@
       <c r="R10" t="n">
         <v>0.01669251672497994</v>
       </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1099,6 +1127,8 @@
       <c r="R11" t="n">
         <v>0.01498629596755798</v>
       </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1157,6 +1187,8 @@
       <c r="R12" t="n">
         <v>0.005932908313592932</v>
       </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1215,6 +1247,8 @@
       <c r="R13" t="n">
         <v>0.02496931730419817</v>
       </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1273,6 +1307,8 @@
       <c r="R14" t="n">
         <v>0.04216014649383777</v>
       </c>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1327,6 +1363,8 @@
       <c r="R15" t="n">
         <v>0.04465261233339038</v>
       </c>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1381,6 +1419,8 @@
       <c r="R16" t="n">
         <v>0.046444056459004</v>
       </c>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1435,6 +1475,8 @@
       <c r="R17" t="n">
         <v>0.0426971189543995</v>
       </c>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1489,6 +1531,8 @@
       <c r="R18" t="n">
         <v>0.02547267761211013</v>
       </c>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1543,6 +1587,8 @@
       <c r="R19" t="n">
         <v>0.07412415624564839</v>
       </c>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1597,6 +1643,8 @@
       <c r="R20" t="n">
         <v>0.02982949637940507</v>
       </c>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1651,6 +1699,8 @@
       <c r="R21" t="n">
         <v>0.04775576276599745</v>
       </c>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1705,6 +1755,8 @@
       <c r="R22" t="n">
         <v>0.07178272167197755</v>
       </c>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1763,6 +1815,8 @@
       <c r="R23" t="n">
         <v>0.01940908164067787</v>
       </c>
+      <c r="S23" t="inlineStr"/>
+      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1821,6 +1875,8 @@
       <c r="R24" t="n">
         <v>0.01112326027637736</v>
       </c>
+      <c r="S24" t="inlineStr"/>
+      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1879,6 +1935,8 @@
       <c r="R25" t="n">
         <v>0.01940908164067787</v>
       </c>
+      <c r="S25" t="inlineStr"/>
+      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1937,6 +1995,8 @@
       <c r="R26" t="n">
         <v>0.01940908164067787</v>
       </c>
+      <c r="S26" t="inlineStr"/>
+      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1995,6 +2055,8 @@
       <c r="R27" t="n">
         <v>0.01112326027637736</v>
       </c>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2053,6 +2115,8 @@
       <c r="R28" t="n">
         <v>0.01112326027637736</v>
       </c>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2111,6 +2175,8 @@
       <c r="R29" t="n">
         <v>0.01718248205627023</v>
       </c>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2169,6 +2235,8 @@
       <c r="R30" t="n">
         <v>0.01718248205627023</v>
       </c>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2227,6 +2295,8 @@
       <c r="R31" t="n">
         <v>0.026548026103587</v>
       </c>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2285,6 +2355,8 @@
       <c r="R32" t="n">
         <v>0.01006019797878372</v>
       </c>
+      <c r="S32" t="inlineStr"/>
+      <c r="T32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2343,6 +2415,8 @@
       <c r="R33" t="n">
         <v>0.02760079309767969</v>
       </c>
+      <c r="S33" t="inlineStr"/>
+      <c r="T33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2401,6 +2475,8 @@
       <c r="R34" t="n">
         <v>0.02760079309767969</v>
       </c>
+      <c r="S34" t="inlineStr"/>
+      <c r="T34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2459,6 +2535,8 @@
       <c r="R35" t="n">
         <v>0.03545959297481422</v>
       </c>
+      <c r="S35" t="inlineStr"/>
+      <c r="T35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2517,6 +2595,8 @@
       <c r="R36" t="n">
         <v>0.03545959297481422</v>
       </c>
+      <c r="S36" t="inlineStr"/>
+      <c r="T36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2575,6 +2655,8 @@
       <c r="R37" t="n">
         <v>0.03245576114304535</v>
       </c>
+      <c r="S37" t="inlineStr"/>
+      <c r="T37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2633,6 +2715,8 @@
       <c r="R38" t="n">
         <v>0.04533517937991077</v>
       </c>
+      <c r="S38" t="inlineStr"/>
+      <c r="T38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2691,6 +2775,8 @@
       <c r="R39" t="n">
         <v>0</v>
       </c>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2749,6 +2835,8 @@
       <c r="R40" t="n">
         <v>0.03679390372207091</v>
       </c>
+      <c r="S40" t="inlineStr"/>
+      <c r="T40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2807,6 +2895,8 @@
       <c r="R41" t="n">
         <v>0.01940908164067787</v>
       </c>
+      <c r="S41" t="inlineStr"/>
+      <c r="T41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2865,6 +2955,8 @@
       <c r="R42" t="n">
         <v>0.01112326027637736</v>
       </c>
+      <c r="S42" t="inlineStr"/>
+      <c r="T42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2923,6 +3015,8 @@
       <c r="R43" t="n">
         <v>0.026548026103587</v>
       </c>
+      <c r="S43" t="inlineStr"/>
+      <c r="T43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2981,6 +3075,8 @@
       <c r="R44" t="n">
         <v>0.02760079309767969</v>
       </c>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3039,6 +3135,8 @@
       <c r="R45" t="n">
         <v>0.03545959297481422</v>
       </c>
+      <c r="S45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3097,6 +3195,8 @@
       <c r="R46" t="n">
         <v>0.05651580495753514</v>
       </c>
+      <c r="S46" t="inlineStr"/>
+      <c r="T46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3155,6 +3255,8 @@
       <c r="R47" t="n">
         <v>0.06892894485763129</v>
       </c>
+      <c r="S47" t="inlineStr"/>
+      <c r="T47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3213,6 +3315,8 @@
       <c r="R48" t="n">
         <v>0.0564584969409441</v>
       </c>
+      <c r="S48" t="inlineStr"/>
+      <c r="T48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3271,6 +3375,8 @@
       <c r="R49" t="n">
         <v>0.01365818713970217</v>
       </c>
+      <c r="S49" t="inlineStr"/>
+      <c r="T49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3329,6 +3435,8 @@
       <c r="R50" t="n">
         <v>0.04014487764849362</v>
       </c>
+      <c r="S50" t="inlineStr"/>
+      <c r="T50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3387,6 +3495,8 @@
       <c r="R51" t="n">
         <v>0.01365818713970217</v>
       </c>
+      <c r="S51" t="inlineStr"/>
+      <c r="T51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3445,6 +3555,8 @@
       <c r="R52" t="n">
         <v>0.01365818713970217</v>
       </c>
+      <c r="S52" t="inlineStr"/>
+      <c r="T52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3503,6 +3615,8 @@
       <c r="R53" t="n">
         <v>0.01365818713970217</v>
       </c>
+      <c r="S53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3561,6 +3675,8 @@
       <c r="R54" t="n">
         <v>0.01365818713970217</v>
       </c>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3619,6 +3735,8 @@
       <c r="R55" t="n">
         <v>0.04436113289559018</v>
       </c>
+      <c r="S55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3677,6 +3795,8 @@
       <c r="R56" t="n">
         <v>0.01123694784910104</v>
       </c>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3735,6 +3855,8 @@
       <c r="R57" t="n">
         <v>0.005258692579715008</v>
       </c>
+      <c r="S57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3793,6 +3915,8 @@
       <c r="R58" t="n">
         <v>0.02614780329723496</v>
       </c>
+      <c r="S58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3851,6 +3975,8 @@
       <c r="R59" t="n">
         <v>0.02981974036652465</v>
       </c>
+      <c r="S59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3909,6 +4035,8 @@
       <c r="R60" t="n">
         <v>0.01882708618980631</v>
       </c>
+      <c r="S60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3967,6 +4095,8 @@
       <c r="R61" t="n">
         <v>0.005258692579715008</v>
       </c>
+      <c r="S61" t="inlineStr"/>
+      <c r="T61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4025,6 +4155,8 @@
       <c r="R62" t="n">
         <v>0.03172842995302576</v>
       </c>
+      <c r="S62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4083,6 +4215,8 @@
       <c r="R63" t="n">
         <v>0.02289970628700663</v>
       </c>
+      <c r="S63" t="inlineStr"/>
+      <c r="T63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4141,6 +4275,8 @@
       <c r="R64" t="n">
         <v>0.03762011370266357</v>
       </c>
+      <c r="S64" t="inlineStr"/>
+      <c r="T64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4199,6 +4335,8 @@
       <c r="R65" t="n">
         <v>0.01000636959259894</v>
       </c>
+      <c r="S65" t="inlineStr"/>
+      <c r="T65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4257,6 +4395,8 @@
       <c r="R66" t="n">
         <v>0.03922935157531927</v>
       </c>
+      <c r="S66" t="inlineStr"/>
+      <c r="T66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4315,6 +4455,8 @@
       <c r="R67" t="n">
         <v>0.03932005167897431</v>
       </c>
+      <c r="S67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4373,6 +4515,8 @@
       <c r="R68" t="n">
         <v>0.04958508262701199</v>
       </c>
+      <c r="S68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4431,6 +4575,8 @@
       <c r="R69" t="n">
         <v>0.05733476336399203</v>
       </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4489,6 +4635,8 @@
       <c r="R70" t="n">
         <v>0.02880027709289949</v>
       </c>
+      <c r="S70" t="inlineStr"/>
+      <c r="T70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4547,6 +4695,8 @@
       <c r="R71" t="n">
         <v>0.04774613509449457</v>
       </c>
+      <c r="S71" t="inlineStr"/>
+      <c r="T71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4605,6 +4755,8 @@
       <c r="R72" t="n">
         <v>0.0286304818249801</v>
       </c>
+      <c r="S72" t="inlineStr"/>
+      <c r="T72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4663,6 +4815,8 @@
       <c r="R73" t="n">
         <v>0.01313746755009773</v>
       </c>
+      <c r="S73" t="inlineStr"/>
+      <c r="T73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4721,6 +4875,8 @@
       <c r="R74" t="n">
         <v>0.04353320095644261</v>
       </c>
+      <c r="S74" t="inlineStr"/>
+      <c r="T74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4779,6 +4935,8 @@
       <c r="R75" t="n">
         <v>0.05036916693012583</v>
       </c>
+      <c r="S75" t="inlineStr"/>
+      <c r="T75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4837,6 +4995,8 @@
       <c r="R76" t="n">
         <v>0.09151655161265683</v>
       </c>
+      <c r="S76" t="inlineStr"/>
+      <c r="T76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -4895,6 +5055,8 @@
       <c r="R77" t="n">
         <v>0.05069506281368039</v>
       </c>
+      <c r="S77" t="inlineStr"/>
+      <c r="T77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -4953,6 +5115,8 @@
       <c r="R78" t="n">
         <v>0.0186604029259421</v>
       </c>
+      <c r="S78" t="inlineStr"/>
+      <c r="T78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5011,6 +5175,8 @@
       <c r="R79" t="n">
         <v>0.1275246570843699</v>
       </c>
+      <c r="S79" t="inlineStr"/>
+      <c r="T79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5069,6 +5235,8 @@
       <c r="R80" t="n">
         <v>0.1225743953061023</v>
       </c>
+      <c r="S80" t="inlineStr"/>
+      <c r="T80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5127,6 +5295,8 @@
       <c r="R81" t="n">
         <v>0.06567524429238983</v>
       </c>
+      <c r="S81" t="inlineStr"/>
+      <c r="T81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5185,6 +5355,8 @@
       <c r="R82" t="n">
         <v>0.05651580495753514</v>
       </c>
+      <c r="S82" t="inlineStr"/>
+      <c r="T82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5243,6 +5415,8 @@
       <c r="R83" t="n">
         <v>0</v>
       </c>
+      <c r="S83" t="inlineStr"/>
+      <c r="T83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5301,6 +5475,8 @@
       <c r="R84" t="n">
         <v>0.09151655161265683</v>
       </c>
+      <c r="S84" t="inlineStr"/>
+      <c r="T84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5359,6 +5535,8 @@
       <c r="R85" t="n">
         <v>0.07357891121034246</v>
       </c>
+      <c r="S85" t="inlineStr"/>
+      <c r="T85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5417,6 +5595,8 @@
       <c r="R86" t="n">
         <v>0.07357891121034246</v>
       </c>
+      <c r="S86" t="inlineStr"/>
+      <c r="T86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5475,6 +5655,8 @@
       <c r="R87" t="n">
         <v>0.05069506281368039</v>
       </c>
+      <c r="S87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5533,6 +5715,8 @@
       <c r="R88" t="n">
         <v>0.02962769103852985</v>
       </c>
+      <c r="S88" t="inlineStr"/>
+      <c r="T88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5591,6 +5775,8 @@
       <c r="R89" t="n">
         <v>0.07056928534311084</v>
       </c>
+      <c r="S89" t="inlineStr"/>
+      <c r="T89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5649,6 +5835,8 @@
       <c r="R90" t="n">
         <v>0.02453009805722536</v>
       </c>
+      <c r="S90" t="inlineStr"/>
+      <c r="T90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5707,6 +5895,8 @@
       <c r="R91" t="n">
         <v>0.04323375905162748</v>
       </c>
+      <c r="S91" t="inlineStr"/>
+      <c r="T91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5765,6 +5955,8 @@
       <c r="R92" t="n">
         <v>0.06120548340203817</v>
       </c>
+      <c r="S92" t="inlineStr"/>
+      <c r="T92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -5823,6 +6015,8 @@
       <c r="R93" t="n">
         <v>0.01810625476685216</v>
       </c>
+      <c r="S93" t="inlineStr"/>
+      <c r="T93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -5881,6 +6075,8 @@
       <c r="R94" t="n">
         <v>0.01582119638561543</v>
       </c>
+      <c r="S94" t="inlineStr"/>
+      <c r="T94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -5939,6 +6135,8 @@
       <c r="R95" t="n">
         <v>0.09499362880770693</v>
       </c>
+      <c r="S95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -5997,6 +6195,8 @@
       <c r="R96" t="n">
         <v>0.1484065254011023</v>
       </c>
+      <c r="S96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6055,6 +6255,8 @@
       <c r="R97" t="n">
         <v>0.04338741584450634</v>
       </c>
+      <c r="S97" t="inlineStr"/>
+      <c r="T97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6113,6 +6315,8 @@
       <c r="R98" t="n">
         <v>0.03034497385943204</v>
       </c>
+      <c r="S98" t="inlineStr"/>
+      <c r="T98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6171,6 +6375,8 @@
       <c r="R99" t="n">
         <v>0.06010758751431648</v>
       </c>
+      <c r="S99" t="inlineStr"/>
+      <c r="T99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6229,6 +6435,8 @@
       <c r="R100" t="n">
         <v>0.01792827326992585</v>
       </c>
+      <c r="S100" t="inlineStr"/>
+      <c r="T100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6287,6 +6495,8 @@
       <c r="R101" t="n">
         <v>0.06010758751431648</v>
       </c>
+      <c r="S101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6345,6 +6555,8 @@
       <c r="R102" t="n">
         <v>0.01792827326992585</v>
       </c>
+      <c r="S102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6403,6 +6615,8 @@
       <c r="R103" t="n">
         <v>0.01175603153386143</v>
       </c>
+      <c r="S103" t="inlineStr"/>
+      <c r="T103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6461,6 +6675,8 @@
       <c r="R104" t="n">
         <v>0.04610789895390428</v>
       </c>
+      <c r="S104" t="inlineStr"/>
+      <c r="T104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6519,6 +6735,8 @@
       <c r="R105" t="n">
         <v>0.01228302606188206</v>
       </c>
+      <c r="S105" t="inlineStr"/>
+      <c r="T105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6577,6 +6795,8 @@
       <c r="R106" t="n">
         <v>0</v>
       </c>
+      <c r="S106" t="inlineStr"/>
+      <c r="T106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6635,6 +6855,8 @@
       <c r="R107" t="n">
         <v>0.03034497385943204</v>
       </c>
+      <c r="S107" t="inlineStr"/>
+      <c r="T107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6693,6 +6915,8 @@
       <c r="R108" t="n">
         <v>0.07138554373540211</v>
       </c>
+      <c r="S108" t="inlineStr"/>
+      <c r="T108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6751,6 +6975,8 @@
       <c r="R109" t="n">
         <v>0.04245189735119193</v>
       </c>
+      <c r="S109" t="inlineStr"/>
+      <c r="T109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6809,6 +7035,8 @@
       <c r="R110" t="n">
         <v>0.03019185147198399</v>
       </c>
+      <c r="S110" t="inlineStr"/>
+      <c r="T110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -6867,6 +7095,8 @@
       <c r="R111" t="n">
         <v>0.04245189735119193</v>
       </c>
+      <c r="S111" t="inlineStr"/>
+      <c r="T111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -6925,6 +7155,8 @@
       <c r="R112" t="n">
         <v>0.03019185147198399</v>
       </c>
+      <c r="S112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -6983,6 +7215,8 @@
       <c r="R113" t="n">
         <v>0.03357979512793006</v>
       </c>
+      <c r="S113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7041,6 +7275,8 @@
       <c r="R114" t="n">
         <v>0.04367110333624002</v>
       </c>
+      <c r="S114" t="inlineStr"/>
+      <c r="T114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7099,6 +7335,8 @@
       <c r="R115" t="n">
         <v>0.005920755329285242</v>
       </c>
+      <c r="S115" t="inlineStr"/>
+      <c r="T115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7157,6 +7395,8 @@
       <c r="R116" t="n">
         <v>0.03583267613861628</v>
       </c>
+      <c r="S116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7214,6 +7454,732 @@
       </c>
       <c r="R117" t="n">
         <v>0.03034497385943204</v>
+      </c>
+      <c r="S117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Image_only</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C118" t="n">
+        <v>22</v>
+      </c>
+      <c r="D118" t="n">
+        <v>3</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7944444616635641</v>
+      </c>
+      <c r="F118" t="n">
+        <v>0.745261569817861</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.1027658134698868</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.7222222487131754</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5860305825869242</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.0207181076124321</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.01746491577653433</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.00506271653945393</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.007856734520410793</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.005126155402093149</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.7222222487131754</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.007856734520410793</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.7408978541692098</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.03034497385943204</v>
+      </c>
+      <c r="S118" t="inlineStr"/>
+      <c r="T118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Image_binary</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C119" t="n">
+        <v>22</v>
+      </c>
+      <c r="D119" t="n">
+        <v>3</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.5444444616635641</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.4536264847106394</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3696845471858978</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.1429522376603718</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.1275516061403077</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.09736101612758238</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.07879416312299103</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.6166666646798452</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.2494438215369265</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.2764622817436854</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.0447275802481077</v>
+      </c>
+      <c r="S119" t="inlineStr"/>
+      <c r="T119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Image_binary</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C120" t="n">
+        <v>22</v>
+      </c>
+      <c r="D120" t="n">
+        <v>3</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.6030555566151937</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.4111700783421784</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.6583333214124044</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.3275231768687566</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.04247183566551653</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.02492560627937922</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.1234627534221223</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.1088146377908272</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.1312334592680055</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.378510390718778</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.1426953046710271</v>
+      </c>
+      <c r="S120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Image_binary</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C121" t="n">
+        <v>22</v>
+      </c>
+      <c r="D121" t="n">
+        <v>3</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.6030555566151937</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.4111700783421784</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.6583333214124044</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.3275231768687566</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.04247183566551653</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.02492560627937922</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.1234627534221223</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.1088146377908272</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.1312334592680055</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.378510390718778</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.1426953046710271</v>
+      </c>
+      <c r="S121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Image_binary</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C122" t="n">
+        <v>22</v>
+      </c>
+      <c r="D122" t="n">
+        <v>3</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.6030555566151937</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4111700783421784</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.6583333214124044</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.3275231768687566</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.04247183566551653</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.02492560627937922</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.1234627534221223</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.1088146377908272</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.1312334592680055</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.378510390718778</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.1426953046710271</v>
+      </c>
+      <c r="S122" t="inlineStr"/>
+      <c r="T122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Image_binary</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C123" t="n">
+        <v>22</v>
+      </c>
+      <c r="D123" t="n">
+        <v>3</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.6030555566151937</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.4111700783421784</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.6583333214124044</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3275231768687566</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.04247183566551653</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.02492560627937922</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.1234627534221223</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.1088146377908272</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.1312334592680055</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.378510390718778</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.1426953046710271</v>
+      </c>
+      <c r="S123" t="inlineStr"/>
+      <c r="T123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Image_only</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C124" t="n">
+        <v>22</v>
+      </c>
+      <c r="D124" t="n">
+        <v>3</v>
+      </c>
+      <c r="E124" t="n">
+        <v>0</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.7033106088638306</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.01581045943116539</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0</v>
+      </c>
+      <c r="S124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Image_only</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C125" t="n">
+        <v>22</v>
+      </c>
+      <c r="D125" t="n">
+        <v>3</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.7033106088638306</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.01581045943116539</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0</v>
+      </c>
+      <c r="S125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Image_only</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C126" t="n">
+        <v>22</v>
+      </c>
+      <c r="D126" t="n">
+        <v>3</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.6166287561257681</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.1433352927366892</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.1754909601564643</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.006886877055669918</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0</v>
+      </c>
+      <c r="S126" t="inlineStr"/>
+      <c r="T126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Image_only</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C127" t="n">
+        <v>22</v>
+      </c>
+      <c r="D127" t="n">
+        <v>3</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.7033106088638306</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.1027658134698868</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.01581045943116539</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.00506271653945393</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="inlineStr"/>
+      <c r="T127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Image_only</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C128" t="n">
+        <v>22</v>
+      </c>
+      <c r="D128" t="n">
+        <v>3</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.7033106088638306</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.1027658134698868</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.01581045943116539</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.00506271653945393</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0</v>
+      </c>
+      <c r="S128" t="inlineStr"/>
+      <c r="T128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Image_only</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C129" t="n">
+        <v>22</v>
+      </c>
+      <c r="D129" t="n">
+        <v>3</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.7033106088638306</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.1027658134698868</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.01581045943116539</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.00506271653945393</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.6871217290560404</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.02029802562326791</v>
       </c>
     </row>
   </sheetData>

--- a/Experiments_Summary.xlsx
+++ b/Experiments_Summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T129"/>
+  <dimension ref="A1:Z134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,36 @@
           <t>std_Test_td_auc</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Avg_Test_Loss</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Std_Test_Loss</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Avg_Test_AUC_5Y</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Std_Test_AUC_5Y</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Avg_Test_Brier_Score</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Std_Test_Brier_Score</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -589,6 +619,12 @@
       </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -649,6 +685,12 @@
       </c>
       <c r="S3" t="inlineStr"/>
       <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -709,6 +751,12 @@
       </c>
       <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -769,6 +817,12 @@
       </c>
       <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -829,6 +883,12 @@
       </c>
       <c r="S6" t="inlineStr"/>
       <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -889,6 +949,12 @@
       </c>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -949,6 +1015,12 @@
       </c>
       <c r="S8" t="inlineStr"/>
       <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1009,6 +1081,12 @@
       </c>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1069,6 +1147,12 @@
       </c>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1129,6 +1213,12 @@
       </c>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1189,6 +1279,12 @@
       </c>
       <c r="S12" t="inlineStr"/>
       <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1249,6 +1345,12 @@
       </c>
       <c r="S13" t="inlineStr"/>
       <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1309,6 +1411,12 @@
       </c>
       <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1365,6 +1473,12 @@
       </c>
       <c r="S15" t="inlineStr"/>
       <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1421,6 +1535,12 @@
       </c>
       <c r="S16" t="inlineStr"/>
       <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1477,6 +1597,12 @@
       </c>
       <c r="S17" t="inlineStr"/>
       <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1533,6 +1659,12 @@
       </c>
       <c r="S18" t="inlineStr"/>
       <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1589,6 +1721,12 @@
       </c>
       <c r="S19" t="inlineStr"/>
       <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1645,6 +1783,12 @@
       </c>
       <c r="S20" t="inlineStr"/>
       <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1701,6 +1845,12 @@
       </c>
       <c r="S21" t="inlineStr"/>
       <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1757,6 +1907,12 @@
       </c>
       <c r="S22" t="inlineStr"/>
       <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1817,6 +1973,12 @@
       </c>
       <c r="S23" t="inlineStr"/>
       <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr"/>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="inlineStr"/>
+      <c r="Z23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1877,6 +2039,12 @@
       </c>
       <c r="S24" t="inlineStr"/>
       <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr"/>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="inlineStr"/>
+      <c r="Z24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1937,6 +2105,12 @@
       </c>
       <c r="S25" t="inlineStr"/>
       <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr"/>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="inlineStr"/>
+      <c r="Z25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1997,6 +2171,12 @@
       </c>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr"/>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="inlineStr"/>
+      <c r="Z26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2057,6 +2237,12 @@
       </c>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2117,6 +2303,12 @@
       </c>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2177,6 +2369,12 @@
       </c>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2237,6 +2435,12 @@
       </c>
       <c r="S30" t="inlineStr"/>
       <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2297,6 +2501,12 @@
       </c>
       <c r="S31" t="inlineStr"/>
       <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2357,6 +2567,12 @@
       </c>
       <c r="S32" t="inlineStr"/>
       <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr"/>
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr"/>
+      <c r="X32" t="inlineStr"/>
+      <c r="Y32" t="inlineStr"/>
+      <c r="Z32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2417,6 +2633,12 @@
       </c>
       <c r="S33" t="inlineStr"/>
       <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr"/>
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr"/>
+      <c r="X33" t="inlineStr"/>
+      <c r="Y33" t="inlineStr"/>
+      <c r="Z33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2477,6 +2699,12 @@
       </c>
       <c r="S34" t="inlineStr"/>
       <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr"/>
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
+      <c r="Y34" t="inlineStr"/>
+      <c r="Z34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2537,6 +2765,12 @@
       </c>
       <c r="S35" t="inlineStr"/>
       <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr"/>
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr"/>
+      <c r="X35" t="inlineStr"/>
+      <c r="Y35" t="inlineStr"/>
+      <c r="Z35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2597,6 +2831,12 @@
       </c>
       <c r="S36" t="inlineStr"/>
       <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr"/>
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr"/>
+      <c r="X36" t="inlineStr"/>
+      <c r="Y36" t="inlineStr"/>
+      <c r="Z36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2657,6 +2897,12 @@
       </c>
       <c r="S37" t="inlineStr"/>
       <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr"/>
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr"/>
+      <c r="X37" t="inlineStr"/>
+      <c r="Y37" t="inlineStr"/>
+      <c r="Z37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2717,6 +2963,12 @@
       </c>
       <c r="S38" t="inlineStr"/>
       <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr"/>
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr"/>
+      <c r="X38" t="inlineStr"/>
+      <c r="Y38" t="inlineStr"/>
+      <c r="Z38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2777,6 +3029,12 @@
       </c>
       <c r="S39" t="inlineStr"/>
       <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="inlineStr"/>
+      <c r="Z39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2837,6 +3095,12 @@
       </c>
       <c r="S40" t="inlineStr"/>
       <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr"/>
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr"/>
+      <c r="X40" t="inlineStr"/>
+      <c r="Y40" t="inlineStr"/>
+      <c r="Z40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2897,6 +3161,12 @@
       </c>
       <c r="S41" t="inlineStr"/>
       <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr"/>
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr"/>
+      <c r="X41" t="inlineStr"/>
+      <c r="Y41" t="inlineStr"/>
+      <c r="Z41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2957,6 +3227,12 @@
       </c>
       <c r="S42" t="inlineStr"/>
       <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr"/>
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr"/>
+      <c r="X42" t="inlineStr"/>
+      <c r="Y42" t="inlineStr"/>
+      <c r="Z42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -3017,6 +3293,12 @@
       </c>
       <c r="S43" t="inlineStr"/>
       <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr"/>
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr"/>
+      <c r="X43" t="inlineStr"/>
+      <c r="Y43" t="inlineStr"/>
+      <c r="Z43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -3077,6 +3359,12 @@
       </c>
       <c r="S44" t="inlineStr"/>
       <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="inlineStr"/>
+      <c r="Z44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3137,6 +3425,12 @@
       </c>
       <c r="S45" t="inlineStr"/>
       <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr"/>
+      <c r="X45" t="inlineStr"/>
+      <c r="Y45" t="inlineStr"/>
+      <c r="Z45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3197,6 +3491,12 @@
       </c>
       <c r="S46" t="inlineStr"/>
       <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr"/>
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr"/>
+      <c r="X46" t="inlineStr"/>
+      <c r="Y46" t="inlineStr"/>
+      <c r="Z46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -3257,6 +3557,12 @@
       </c>
       <c r="S47" t="inlineStr"/>
       <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr"/>
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr"/>
+      <c r="X47" t="inlineStr"/>
+      <c r="Y47" t="inlineStr"/>
+      <c r="Z47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -3317,6 +3623,12 @@
       </c>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="inlineStr"/>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -3377,6 +3689,12 @@
       </c>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="inlineStr"/>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3437,6 +3755,12 @@
       </c>
       <c r="S50" t="inlineStr"/>
       <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="inlineStr"/>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -3497,6 +3821,12 @@
       </c>
       <c r="S51" t="inlineStr"/>
       <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3557,6 +3887,12 @@
       </c>
       <c r="S52" t="inlineStr"/>
       <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="inlineStr"/>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -3617,6 +3953,12 @@
       </c>
       <c r="S53" t="inlineStr"/>
       <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="inlineStr"/>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3677,6 +4019,12 @@
       </c>
       <c r="S54" t="inlineStr"/>
       <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3737,6 +4085,12 @@
       </c>
       <c r="S55" t="inlineStr"/>
       <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="inlineStr"/>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3797,6 +4151,12 @@
       </c>
       <c r="S56" t="inlineStr"/>
       <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -3857,6 +4217,12 @@
       </c>
       <c r="S57" t="inlineStr"/>
       <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3917,6 +4283,12 @@
       </c>
       <c r="S58" t="inlineStr"/>
       <c r="T58" t="inlineStr"/>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="inlineStr"/>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="inlineStr"/>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3977,6 +4349,12 @@
       </c>
       <c r="S59" t="inlineStr"/>
       <c r="T59" t="inlineStr"/>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="inlineStr"/>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="inlineStr"/>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -4037,6 +4415,12 @@
       </c>
       <c r="S60" t="inlineStr"/>
       <c r="T60" t="inlineStr"/>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="inlineStr"/>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="inlineStr"/>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -4097,6 +4481,12 @@
       </c>
       <c r="S61" t="inlineStr"/>
       <c r="T61" t="inlineStr"/>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="inlineStr"/>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="inlineStr"/>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4157,6 +4547,12 @@
       </c>
       <c r="S62" t="inlineStr"/>
       <c r="T62" t="inlineStr"/>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="inlineStr"/>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="inlineStr"/>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -4217,6 +4613,12 @@
       </c>
       <c r="S63" t="inlineStr"/>
       <c r="T63" t="inlineStr"/>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="inlineStr"/>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4277,6 +4679,12 @@
       </c>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="inlineStr"/>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="inlineStr"/>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -4337,6 +4745,12 @@
       </c>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
+      <c r="V65" t="inlineStr"/>
+      <c r="W65" t="inlineStr"/>
+      <c r="X65" t="inlineStr"/>
+      <c r="Y65" t="inlineStr"/>
+      <c r="Z65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4397,6 +4811,12 @@
       </c>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
+      <c r="U66" t="inlineStr"/>
+      <c r="V66" t="inlineStr"/>
+      <c r="W66" t="inlineStr"/>
+      <c r="X66" t="inlineStr"/>
+      <c r="Y66" t="inlineStr"/>
+      <c r="Z66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4457,6 +4877,12 @@
       </c>
       <c r="S67" t="inlineStr"/>
       <c r="T67" t="inlineStr"/>
+      <c r="U67" t="inlineStr"/>
+      <c r="V67" t="inlineStr"/>
+      <c r="W67" t="inlineStr"/>
+      <c r="X67" t="inlineStr"/>
+      <c r="Y67" t="inlineStr"/>
+      <c r="Z67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -4517,6 +4943,12 @@
       </c>
       <c r="S68" t="inlineStr"/>
       <c r="T68" t="inlineStr"/>
+      <c r="U68" t="inlineStr"/>
+      <c r="V68" t="inlineStr"/>
+      <c r="W68" t="inlineStr"/>
+      <c r="X68" t="inlineStr"/>
+      <c r="Y68" t="inlineStr"/>
+      <c r="Z68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -4577,6 +5009,12 @@
       </c>
       <c r="S69" t="inlineStr"/>
       <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
+      <c r="V69" t="inlineStr"/>
+      <c r="W69" t="inlineStr"/>
+      <c r="X69" t="inlineStr"/>
+      <c r="Y69" t="inlineStr"/>
+      <c r="Z69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4637,6 +5075,12 @@
       </c>
       <c r="S70" t="inlineStr"/>
       <c r="T70" t="inlineStr"/>
+      <c r="U70" t="inlineStr"/>
+      <c r="V70" t="inlineStr"/>
+      <c r="W70" t="inlineStr"/>
+      <c r="X70" t="inlineStr"/>
+      <c r="Y70" t="inlineStr"/>
+      <c r="Z70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4697,6 +5141,12 @@
       </c>
       <c r="S71" t="inlineStr"/>
       <c r="T71" t="inlineStr"/>
+      <c r="U71" t="inlineStr"/>
+      <c r="V71" t="inlineStr"/>
+      <c r="W71" t="inlineStr"/>
+      <c r="X71" t="inlineStr"/>
+      <c r="Y71" t="inlineStr"/>
+      <c r="Z71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -4757,6 +5207,12 @@
       </c>
       <c r="S72" t="inlineStr"/>
       <c r="T72" t="inlineStr"/>
+      <c r="U72" t="inlineStr"/>
+      <c r="V72" t="inlineStr"/>
+      <c r="W72" t="inlineStr"/>
+      <c r="X72" t="inlineStr"/>
+      <c r="Y72" t="inlineStr"/>
+      <c r="Z72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -4817,6 +5273,12 @@
       </c>
       <c r="S73" t="inlineStr"/>
       <c r="T73" t="inlineStr"/>
+      <c r="U73" t="inlineStr"/>
+      <c r="V73" t="inlineStr"/>
+      <c r="W73" t="inlineStr"/>
+      <c r="X73" t="inlineStr"/>
+      <c r="Y73" t="inlineStr"/>
+      <c r="Z73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4877,6 +5339,12 @@
       </c>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
+      <c r="U74" t="inlineStr"/>
+      <c r="V74" t="inlineStr"/>
+      <c r="W74" t="inlineStr"/>
+      <c r="X74" t="inlineStr"/>
+      <c r="Y74" t="inlineStr"/>
+      <c r="Z74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4937,6 +5405,12 @@
       </c>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
+      <c r="U75" t="inlineStr"/>
+      <c r="V75" t="inlineStr"/>
+      <c r="W75" t="inlineStr"/>
+      <c r="X75" t="inlineStr"/>
+      <c r="Y75" t="inlineStr"/>
+      <c r="Z75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -4997,6 +5471,12 @@
       </c>
       <c r="S76" t="inlineStr"/>
       <c r="T76" t="inlineStr"/>
+      <c r="U76" t="inlineStr"/>
+      <c r="V76" t="inlineStr"/>
+      <c r="W76" t="inlineStr"/>
+      <c r="X76" t="inlineStr"/>
+      <c r="Y76" t="inlineStr"/>
+      <c r="Z76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -5057,6 +5537,12 @@
       </c>
       <c r="S77" t="inlineStr"/>
       <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
+      <c r="V77" t="inlineStr"/>
+      <c r="W77" t="inlineStr"/>
+      <c r="X77" t="inlineStr"/>
+      <c r="Y77" t="inlineStr"/>
+      <c r="Z77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -5117,6 +5603,12 @@
       </c>
       <c r="S78" t="inlineStr"/>
       <c r="T78" t="inlineStr"/>
+      <c r="U78" t="inlineStr"/>
+      <c r="V78" t="inlineStr"/>
+      <c r="W78" t="inlineStr"/>
+      <c r="X78" t="inlineStr"/>
+      <c r="Y78" t="inlineStr"/>
+      <c r="Z78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5177,6 +5669,12 @@
       </c>
       <c r="S79" t="inlineStr"/>
       <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
+      <c r="V79" t="inlineStr"/>
+      <c r="W79" t="inlineStr"/>
+      <c r="X79" t="inlineStr"/>
+      <c r="Y79" t="inlineStr"/>
+      <c r="Z79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5237,6 +5735,12 @@
       </c>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
+      <c r="U80" t="inlineStr"/>
+      <c r="V80" t="inlineStr"/>
+      <c r="W80" t="inlineStr"/>
+      <c r="X80" t="inlineStr"/>
+      <c r="Y80" t="inlineStr"/>
+      <c r="Z80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5297,6 +5801,12 @@
       </c>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
+      <c r="V81" t="inlineStr"/>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr"/>
+      <c r="Y81" t="inlineStr"/>
+      <c r="Z81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5357,6 +5867,12 @@
       </c>
       <c r="S82" t="inlineStr"/>
       <c r="T82" t="inlineStr"/>
+      <c r="U82" t="inlineStr"/>
+      <c r="V82" t="inlineStr"/>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr"/>
+      <c r="Y82" t="inlineStr"/>
+      <c r="Z82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -5417,6 +5933,12 @@
       </c>
       <c r="S83" t="inlineStr"/>
       <c r="T83" t="inlineStr"/>
+      <c r="U83" t="inlineStr"/>
+      <c r="V83" t="inlineStr"/>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr"/>
+      <c r="Y83" t="inlineStr"/>
+      <c r="Z83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5477,6 +5999,12 @@
       </c>
       <c r="S84" t="inlineStr"/>
       <c r="T84" t="inlineStr"/>
+      <c r="U84" t="inlineStr"/>
+      <c r="V84" t="inlineStr"/>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr"/>
+      <c r="Y84" t="inlineStr"/>
+      <c r="Z84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -5537,6 +6065,12 @@
       </c>
       <c r="S85" t="inlineStr"/>
       <c r="T85" t="inlineStr"/>
+      <c r="U85" t="inlineStr"/>
+      <c r="V85" t="inlineStr"/>
+      <c r="W85" t="inlineStr"/>
+      <c r="X85" t="inlineStr"/>
+      <c r="Y85" t="inlineStr"/>
+      <c r="Z85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -5597,6 +6131,12 @@
       </c>
       <c r="S86" t="inlineStr"/>
       <c r="T86" t="inlineStr"/>
+      <c r="U86" t="inlineStr"/>
+      <c r="V86" t="inlineStr"/>
+      <c r="W86" t="inlineStr"/>
+      <c r="X86" t="inlineStr"/>
+      <c r="Y86" t="inlineStr"/>
+      <c r="Z86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5657,6 +6197,12 @@
       </c>
       <c r="S87" t="inlineStr"/>
       <c r="T87" t="inlineStr"/>
+      <c r="U87" t="inlineStr"/>
+      <c r="V87" t="inlineStr"/>
+      <c r="W87" t="inlineStr"/>
+      <c r="X87" t="inlineStr"/>
+      <c r="Y87" t="inlineStr"/>
+      <c r="Z87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5717,6 +6263,12 @@
       </c>
       <c r="S88" t="inlineStr"/>
       <c r="T88" t="inlineStr"/>
+      <c r="U88" t="inlineStr"/>
+      <c r="V88" t="inlineStr"/>
+      <c r="W88" t="inlineStr"/>
+      <c r="X88" t="inlineStr"/>
+      <c r="Y88" t="inlineStr"/>
+      <c r="Z88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -5777,6 +6329,12 @@
       </c>
       <c r="S89" t="inlineStr"/>
       <c r="T89" t="inlineStr"/>
+      <c r="U89" t="inlineStr"/>
+      <c r="V89" t="inlineStr"/>
+      <c r="W89" t="inlineStr"/>
+      <c r="X89" t="inlineStr"/>
+      <c r="Y89" t="inlineStr"/>
+      <c r="Z89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -5837,6 +6395,12 @@
       </c>
       <c r="S90" t="inlineStr"/>
       <c r="T90" t="inlineStr"/>
+      <c r="U90" t="inlineStr"/>
+      <c r="V90" t="inlineStr"/>
+      <c r="W90" t="inlineStr"/>
+      <c r="X90" t="inlineStr"/>
+      <c r="Y90" t="inlineStr"/>
+      <c r="Z90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -5897,6 +6461,12 @@
       </c>
       <c r="S91" t="inlineStr"/>
       <c r="T91" t="inlineStr"/>
+      <c r="U91" t="inlineStr"/>
+      <c r="V91" t="inlineStr"/>
+      <c r="W91" t="inlineStr"/>
+      <c r="X91" t="inlineStr"/>
+      <c r="Y91" t="inlineStr"/>
+      <c r="Z91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -5957,6 +6527,12 @@
       </c>
       <c r="S92" t="inlineStr"/>
       <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+      <c r="V92" t="inlineStr"/>
+      <c r="W92" t="inlineStr"/>
+      <c r="X92" t="inlineStr"/>
+      <c r="Y92" t="inlineStr"/>
+      <c r="Z92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -6017,6 +6593,12 @@
       </c>
       <c r="S93" t="inlineStr"/>
       <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+      <c r="V93" t="inlineStr"/>
+      <c r="W93" t="inlineStr"/>
+      <c r="X93" t="inlineStr"/>
+      <c r="Y93" t="inlineStr"/>
+      <c r="Z93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -6077,6 +6659,12 @@
       </c>
       <c r="S94" t="inlineStr"/>
       <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+      <c r="V94" t="inlineStr"/>
+      <c r="W94" t="inlineStr"/>
+      <c r="X94" t="inlineStr"/>
+      <c r="Y94" t="inlineStr"/>
+      <c r="Z94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -6137,6 +6725,12 @@
       </c>
       <c r="S95" t="inlineStr"/>
       <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+      <c r="V95" t="inlineStr"/>
+      <c r="W95" t="inlineStr"/>
+      <c r="X95" t="inlineStr"/>
+      <c r="Y95" t="inlineStr"/>
+      <c r="Z95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -6197,6 +6791,12 @@
       </c>
       <c r="S96" t="inlineStr"/>
       <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+      <c r="V96" t="inlineStr"/>
+      <c r="W96" t="inlineStr"/>
+      <c r="X96" t="inlineStr"/>
+      <c r="Y96" t="inlineStr"/>
+      <c r="Z96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6257,6 +6857,12 @@
       </c>
       <c r="S97" t="inlineStr"/>
       <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+      <c r="V97" t="inlineStr"/>
+      <c r="W97" t="inlineStr"/>
+      <c r="X97" t="inlineStr"/>
+      <c r="Y97" t="inlineStr"/>
+      <c r="Z97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6317,6 +6923,12 @@
       </c>
       <c r="S98" t="inlineStr"/>
       <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+      <c r="V98" t="inlineStr"/>
+      <c r="W98" t="inlineStr"/>
+      <c r="X98" t="inlineStr"/>
+      <c r="Y98" t="inlineStr"/>
+      <c r="Z98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6377,6 +6989,12 @@
       </c>
       <c r="S99" t="inlineStr"/>
       <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+      <c r="V99" t="inlineStr"/>
+      <c r="W99" t="inlineStr"/>
+      <c r="X99" t="inlineStr"/>
+      <c r="Y99" t="inlineStr"/>
+      <c r="Z99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6437,6 +7055,12 @@
       </c>
       <c r="S100" t="inlineStr"/>
       <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+      <c r="V100" t="inlineStr"/>
+      <c r="W100" t="inlineStr"/>
+      <c r="X100" t="inlineStr"/>
+      <c r="Y100" t="inlineStr"/>
+      <c r="Z100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -6497,6 +7121,12 @@
       </c>
       <c r="S101" t="inlineStr"/>
       <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+      <c r="V101" t="inlineStr"/>
+      <c r="W101" t="inlineStr"/>
+      <c r="X101" t="inlineStr"/>
+      <c r="Y101" t="inlineStr"/>
+      <c r="Z101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -6557,6 +7187,12 @@
       </c>
       <c r="S102" t="inlineStr"/>
       <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+      <c r="V102" t="inlineStr"/>
+      <c r="W102" t="inlineStr"/>
+      <c r="X102" t="inlineStr"/>
+      <c r="Y102" t="inlineStr"/>
+      <c r="Z102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6617,6 +7253,12 @@
       </c>
       <c r="S103" t="inlineStr"/>
       <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+      <c r="V103" t="inlineStr"/>
+      <c r="W103" t="inlineStr"/>
+      <c r="X103" t="inlineStr"/>
+      <c r="Y103" t="inlineStr"/>
+      <c r="Z103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -6677,6 +7319,12 @@
       </c>
       <c r="S104" t="inlineStr"/>
       <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+      <c r="V104" t="inlineStr"/>
+      <c r="W104" t="inlineStr"/>
+      <c r="X104" t="inlineStr"/>
+      <c r="Y104" t="inlineStr"/>
+      <c r="Z104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -6737,6 +7385,12 @@
       </c>
       <c r="S105" t="inlineStr"/>
       <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+      <c r="V105" t="inlineStr"/>
+      <c r="W105" t="inlineStr"/>
+      <c r="X105" t="inlineStr"/>
+      <c r="Y105" t="inlineStr"/>
+      <c r="Z105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6797,6 +7451,12 @@
       </c>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+      <c r="V106" t="inlineStr"/>
+      <c r="W106" t="inlineStr"/>
+      <c r="X106" t="inlineStr"/>
+      <c r="Y106" t="inlineStr"/>
+      <c r="Z106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -6857,6 +7517,12 @@
       </c>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+      <c r="V107" t="inlineStr"/>
+      <c r="W107" t="inlineStr"/>
+      <c r="X107" t="inlineStr"/>
+      <c r="Y107" t="inlineStr"/>
+      <c r="Z107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6917,6 +7583,12 @@
       </c>
       <c r="S108" t="inlineStr"/>
       <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+      <c r="V108" t="inlineStr"/>
+      <c r="W108" t="inlineStr"/>
+      <c r="X108" t="inlineStr"/>
+      <c r="Y108" t="inlineStr"/>
+      <c r="Z108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -6977,6 +7649,12 @@
       </c>
       <c r="S109" t="inlineStr"/>
       <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+      <c r="V109" t="inlineStr"/>
+      <c r="W109" t="inlineStr"/>
+      <c r="X109" t="inlineStr"/>
+      <c r="Y109" t="inlineStr"/>
+      <c r="Z109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -7037,6 +7715,12 @@
       </c>
       <c r="S110" t="inlineStr"/>
       <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+      <c r="V110" t="inlineStr"/>
+      <c r="W110" t="inlineStr"/>
+      <c r="X110" t="inlineStr"/>
+      <c r="Y110" t="inlineStr"/>
+      <c r="Z110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7097,6 +7781,12 @@
       </c>
       <c r="S111" t="inlineStr"/>
       <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+      <c r="V111" t="inlineStr"/>
+      <c r="W111" t="inlineStr"/>
+      <c r="X111" t="inlineStr"/>
+      <c r="Y111" t="inlineStr"/>
+      <c r="Z111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -7157,6 +7847,12 @@
       </c>
       <c r="S112" t="inlineStr"/>
       <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+      <c r="V112" t="inlineStr"/>
+      <c r="W112" t="inlineStr"/>
+      <c r="X112" t="inlineStr"/>
+      <c r="Y112" t="inlineStr"/>
+      <c r="Z112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -7217,6 +7913,12 @@
       </c>
       <c r="S113" t="inlineStr"/>
       <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+      <c r="V113" t="inlineStr"/>
+      <c r="W113" t="inlineStr"/>
+      <c r="X113" t="inlineStr"/>
+      <c r="Y113" t="inlineStr"/>
+      <c r="Z113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7277,6 +7979,12 @@
       </c>
       <c r="S114" t="inlineStr"/>
       <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+      <c r="V114" t="inlineStr"/>
+      <c r="W114" t="inlineStr"/>
+      <c r="X114" t="inlineStr"/>
+      <c r="Y114" t="inlineStr"/>
+      <c r="Z114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7337,6 +8045,12 @@
       </c>
       <c r="S115" t="inlineStr"/>
       <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+      <c r="V115" t="inlineStr"/>
+      <c r="W115" t="inlineStr"/>
+      <c r="X115" t="inlineStr"/>
+      <c r="Y115" t="inlineStr"/>
+      <c r="Z115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -7397,6 +8111,12 @@
       </c>
       <c r="S116" t="inlineStr"/>
       <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+      <c r="V116" t="inlineStr"/>
+      <c r="W116" t="inlineStr"/>
+      <c r="X116" t="inlineStr"/>
+      <c r="Y116" t="inlineStr"/>
+      <c r="Z116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -7457,6 +8177,12 @@
       </c>
       <c r="S117" t="inlineStr"/>
       <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
+      <c r="V117" t="inlineStr"/>
+      <c r="W117" t="inlineStr"/>
+      <c r="X117" t="inlineStr"/>
+      <c r="Y117" t="inlineStr"/>
+      <c r="Z117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7517,6 +8243,12 @@
       </c>
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+      <c r="V118" t="inlineStr"/>
+      <c r="W118" t="inlineStr"/>
+      <c r="X118" t="inlineStr"/>
+      <c r="Y118" t="inlineStr"/>
+      <c r="Z118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7577,6 +8309,12 @@
       </c>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
+      <c r="V119" t="inlineStr"/>
+      <c r="W119" t="inlineStr"/>
+      <c r="X119" t="inlineStr"/>
+      <c r="Y119" t="inlineStr"/>
+      <c r="Z119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -7637,6 +8375,12 @@
       </c>
       <c r="S120" t="inlineStr"/>
       <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
+      <c r="V120" t="inlineStr"/>
+      <c r="W120" t="inlineStr"/>
+      <c r="X120" t="inlineStr"/>
+      <c r="Y120" t="inlineStr"/>
+      <c r="Z120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -7697,6 +8441,12 @@
       </c>
       <c r="S121" t="inlineStr"/>
       <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+      <c r="V121" t="inlineStr"/>
+      <c r="W121" t="inlineStr"/>
+      <c r="X121" t="inlineStr"/>
+      <c r="Y121" t="inlineStr"/>
+      <c r="Z121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -7757,6 +8507,12 @@
       </c>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+      <c r="V122" t="inlineStr"/>
+      <c r="W122" t="inlineStr"/>
+      <c r="X122" t="inlineStr"/>
+      <c r="Y122" t="inlineStr"/>
+      <c r="Z122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -7817,6 +8573,12 @@
       </c>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
+      <c r="V123" t="inlineStr"/>
+      <c r="W123" t="inlineStr"/>
+      <c r="X123" t="inlineStr"/>
+      <c r="Y123" t="inlineStr"/>
+      <c r="Z123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7877,6 +8639,12 @@
       </c>
       <c r="S124" t="inlineStr"/>
       <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+      <c r="V124" t="inlineStr"/>
+      <c r="W124" t="inlineStr"/>
+      <c r="X124" t="inlineStr"/>
+      <c r="Y124" t="inlineStr"/>
+      <c r="Z124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -7937,6 +8705,12 @@
       </c>
       <c r="S125" t="inlineStr"/>
       <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+      <c r="V125" t="inlineStr"/>
+      <c r="W125" t="inlineStr"/>
+      <c r="X125" t="inlineStr"/>
+      <c r="Y125" t="inlineStr"/>
+      <c r="Z125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7997,6 +8771,12 @@
       </c>
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
+      <c r="V126" t="inlineStr"/>
+      <c r="W126" t="inlineStr"/>
+      <c r="X126" t="inlineStr"/>
+      <c r="Y126" t="inlineStr"/>
+      <c r="Z126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -8057,6 +8837,12 @@
       </c>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
+      <c r="V127" t="inlineStr"/>
+      <c r="W127" t="inlineStr"/>
+      <c r="X127" t="inlineStr"/>
+      <c r="Y127" t="inlineStr"/>
+      <c r="Z127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8117,6 +8903,12 @@
       </c>
       <c r="S128" t="inlineStr"/>
       <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
+      <c r="V128" t="inlineStr"/>
+      <c r="W128" t="inlineStr"/>
+      <c r="X128" t="inlineStr"/>
+      <c r="Y128" t="inlineStr"/>
+      <c r="Z128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -8180,6 +8972,330 @@
       </c>
       <c r="T129" t="n">
         <v>0.02029802562326791</v>
+      </c>
+      <c r="U129" t="inlineStr"/>
+      <c r="V129" t="inlineStr"/>
+      <c r="W129" t="inlineStr"/>
+      <c r="X129" t="inlineStr"/>
+      <c r="Y129" t="inlineStr"/>
+      <c r="Z129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Image_AdamW</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C130" t="n">
+        <v>22</v>
+      </c>
+      <c r="D130" t="n">
+        <v>3</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.7002780040105184</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.1004794016480446</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.009312865911568307</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.004187219149832431</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.6793345212936401</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.01682151478097068</v>
+      </c>
+      <c r="U130" t="inlineStr"/>
+      <c r="V130" t="inlineStr"/>
+      <c r="W130" t="inlineStr"/>
+      <c r="X130" t="inlineStr"/>
+      <c r="Y130" t="inlineStr"/>
+      <c r="Z130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Image_AdamW</t>
+        </is>
+      </c>
+      <c r="B131" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C131" t="n">
+        <v>22</v>
+      </c>
+      <c r="D131" t="n">
+        <v>3</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.7002780040105184</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.1004794016480446</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.009312865911568307</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.004187219149832431</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.6793345212936401</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.01682151478097068</v>
+      </c>
+      <c r="U131" t="inlineStr"/>
+      <c r="V131" t="inlineStr"/>
+      <c r="W131" t="inlineStr"/>
+      <c r="X131" t="inlineStr"/>
+      <c r="Y131" t="inlineStr"/>
+      <c r="Z131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Image_AdamW</t>
+        </is>
+      </c>
+      <c r="B132" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C132" t="n">
+        <v>22</v>
+      </c>
+      <c r="D132" t="n">
+        <v>3</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.7002780040105184</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.1004794016480446</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.009312865911568307</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.004187219149832431</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.6793345212936401</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.01682151478097068</v>
+      </c>
+      <c r="U132" t="inlineStr"/>
+      <c r="V132" t="inlineStr"/>
+      <c r="W132" t="inlineStr"/>
+      <c r="X132" t="inlineStr"/>
+      <c r="Y132" t="inlineStr"/>
+      <c r="Z132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Image_AdamW</t>
+        </is>
+      </c>
+      <c r="B133" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C133" t="n">
+        <v>22</v>
+      </c>
+      <c r="D133" t="n">
+        <v>3</v>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="n">
+        <v>0.5451099276542664</v>
+      </c>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="n">
+        <v>0.03473178239344775</v>
+      </c>
+      <c r="L133" t="inlineStr"/>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr"/>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="n">
+        <v>0.7090909083684286</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.03519738029761231</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4617283840974172</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.03844050514026306</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.2257349640130997</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.01144914901329451</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Simplified_version</t>
+        </is>
+      </c>
+      <c r="B134" t="n">
+        <v>0.0001</v>
+      </c>
+      <c r="C134" t="n">
+        <v>22</v>
+      </c>
+      <c r="D134" t="n">
+        <v>3</v>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="n">
+        <v>0.6707101464271545</v>
+      </c>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr"/>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="n">
+        <v>0.03639822570529609</v>
+      </c>
+      <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr"/>
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="n">
+        <v>0.5304191211859385</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.03537055092440696</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.6685185432434082</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.03051346113403411</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.1750116248925527</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.01105313603569366</v>
       </c>
     </row>
   </sheetData>
